--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -1145,7 +1145,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1167,12 +1167,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1194,9 +1188,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1213,9 +1204,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1578,103 +1566,103 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32">
+      <c r="B1" s="28">
         <v>46081</v>
       </c>
-      <c r="C1" s="32">
+      <c r="C1" s="28">
         <v>46082</v>
       </c>
-      <c r="D1" s="32">
+      <c r="D1" s="28">
         <v>46083</v>
       </c>
-      <c r="E1" s="32">
+      <c r="E1" s="28">
         <v>46084</v>
       </c>
-      <c r="F1" s="32">
+      <c r="F1" s="28">
         <v>46085</v>
       </c>
-      <c r="G1" s="32">
+      <c r="G1" s="28">
         <v>46086</v>
       </c>
-      <c r="H1" s="32">
+      <c r="H1" s="28">
         <v>46087</v>
       </c>
-      <c r="I1" s="32">
+      <c r="I1" s="28">
         <v>46088</v>
       </c>
-      <c r="J1" s="32">
+      <c r="J1" s="28">
         <v>46089</v>
       </c>
-      <c r="K1" s="32">
+      <c r="K1" s="28">
         <v>46090</v>
       </c>
-      <c r="L1" s="32">
+      <c r="L1" s="28">
         <v>46091</v>
       </c>
-      <c r="M1" s="32">
+      <c r="M1" s="28">
         <v>46092</v>
       </c>
-      <c r="N1" s="32">
+      <c r="N1" s="28">
         <v>46093</v>
       </c>
-      <c r="O1" s="32">
+      <c r="O1" s="28">
         <v>46094</v>
       </c>
-      <c r="P1" s="32">
+      <c r="P1" s="28">
         <v>46095</v>
       </c>
-      <c r="Q1" s="32">
+      <c r="Q1" s="28">
         <v>46096</v>
       </c>
-      <c r="R1" s="32">
+      <c r="R1" s="28">
         <v>46097</v>
       </c>
-      <c r="S1" s="32">
+      <c r="S1" s="28">
         <v>46098</v>
       </c>
-      <c r="T1" s="32">
+      <c r="T1" s="28">
         <v>46099</v>
       </c>
-      <c r="U1" s="32">
+      <c r="U1" s="28">
         <v>46100</v>
       </c>
-      <c r="V1" s="32">
+      <c r="V1" s="28">
         <v>46101</v>
       </c>
-      <c r="W1" s="32">
+      <c r="W1" s="28">
         <v>46102</v>
       </c>
-      <c r="X1" s="32">
+      <c r="X1" s="28">
         <v>46103</v>
       </c>
-      <c r="Y1" s="32">
+      <c r="Y1" s="28">
         <v>46104</v>
       </c>
-      <c r="Z1" s="32">
+      <c r="Z1" s="28">
         <v>46105</v>
       </c>
-      <c r="AA1" s="32">
+      <c r="AA1" s="28">
         <v>46106</v>
       </c>
-      <c r="AB1" s="32">
+      <c r="AB1" s="28">
         <v>46107</v>
       </c>
-      <c r="AC1" s="32">
+      <c r="AC1" s="28">
         <v>46108</v>
       </c>
-      <c r="AD1" s="32">
+      <c r="AD1" s="28">
         <v>46109</v>
       </c>
-      <c r="AE1" s="32">
+      <c r="AE1" s="28">
         <v>46110</v>
       </c>
-      <c r="AF1" s="32">
+      <c r="AF1" s="28">
         <v>46111</v>
       </c>
-      <c r="AG1" s="32">
+      <c r="AG1" s="28">
         <v>46112</v>
       </c>
-      <c r="AH1" s="32">
+      <c r="AH1" s="28">
         <v>46113</v>
       </c>
     </row>
@@ -1682,103 +1670,103 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33">
+      <c r="B2" s="29">
         <v>0.15436753577515</v>
       </c>
-      <c r="C2" s="33">
+      <c r="C2" s="29">
         <v>0.15436753577515</v>
       </c>
-      <c r="D2" s="33">
+      <c r="D2" s="29">
         <v>0.15436753577515</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="29">
         <v>0.15436753577515</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="29">
         <v>0.15436753577515</v>
       </c>
-      <c r="G2" s="34">
+      <c r="G2" s="30">
         <v>0.15436753577515</v>
       </c>
-      <c r="H2" s="33">
+      <c r="H2" s="29">
         <v>0.073794785349101</v>
       </c>
-      <c r="I2" s="34">
+      <c r="I2" s="30">
         <v>0.155080443958291</v>
       </c>
-      <c r="J2" s="34">
+      <c r="J2" s="30">
         <v>0.155080443958291</v>
       </c>
-      <c r="K2" s="33">
+      <c r="K2" s="29">
         <v>0.155080443958291</v>
       </c>
-      <c r="L2" s="33">
+      <c r="L2" s="29">
         <v>0.155080443958291</v>
       </c>
-      <c r="M2" s="33">
+      <c r="M2" s="29">
         <v>0.155080443958291</v>
       </c>
-      <c r="N2" s="33">
+      <c r="N2" s="29">
         <v>0.155080443958291</v>
       </c>
-      <c r="O2" s="33">
+      <c r="O2" s="29">
         <v>0.0695173362502559</v>
       </c>
-      <c r="P2" s="33">
+      <c r="P2" s="29">
         <v>0.159785932721713</v>
       </c>
-      <c r="Q2" s="33">
+      <c r="Q2" s="29">
         <v>0.159785932721713</v>
       </c>
-      <c r="R2" s="33">
+      <c r="R2" s="29">
         <v>0.159785932721713</v>
       </c>
-      <c r="S2" s="33">
+      <c r="S2" s="29">
         <v>0.159785932721713</v>
       </c>
-      <c r="T2" s="33">
+      <c r="T2" s="29">
         <v>0.159785932721713</v>
       </c>
-      <c r="U2" s="33">
+      <c r="U2" s="29">
         <v>0.159785932721713</v>
       </c>
-      <c r="V2" s="33">
+      <c r="V2" s="29">
         <v>0.0412844036697248</v>
       </c>
-      <c r="W2" s="33">
+      <c r="W2" s="29">
         <v>0.156031837360951</v>
       </c>
-      <c r="X2" s="33">
+      <c r="X2" s="29">
         <v>0.156031837360951</v>
       </c>
-      <c r="Y2" s="33">
+      <c r="Y2" s="29">
         <v>0.156031837360951</v>
       </c>
-      <c r="Z2" s="33">
+      <c r="Z2" s="29">
         <v>0.156031837360951</v>
       </c>
-      <c r="AA2" s="33">
+      <c r="AA2" s="29">
         <v>0.156031837360951</v>
       </c>
-      <c r="AB2" s="33">
+      <c r="AB2" s="29">
         <v>0.156031837360951</v>
       </c>
-      <c r="AC2" s="33">
+      <c r="AC2" s="29">
+        <v>0.0638089758342923</v>
+      </c>
+      <c r="AD2" s="29">
         <v>0</v>
       </c>
-      <c r="AD2" s="33">
+      <c r="AE2" s="29">
         <v>0</v>
       </c>
-      <c r="AE2" s="33">
+      <c r="AF2" s="29">
         <v>0</v>
       </c>
-      <c r="AF2" s="33">
+      <c r="AG2" s="29">
         <v>0</v>
       </c>
-      <c r="AG2" s="33">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="33">
+      <c r="AH2" s="29">
         <v>0</v>
       </c>
     </row>
@@ -1786,410 +1774,410 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="29">
         <f>SUM($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="29">
         <f>SUM($B2:C2)</f>
         <v>0.3087350715503</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="29">
         <f>SUM($B2:D2)</f>
         <v>0.463102607325449</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="29">
         <f>SUM($B2:E2)</f>
         <v>0.617470143100599</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="29">
         <f>SUM($B2:F2)</f>
         <v>0.771837678875749</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="29">
         <f>SUM($B2:G2)</f>
         <v>0.926205214650899</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="29">
         <f>SUM($B2:H2)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="33">
+      <c r="I3" s="29">
         <f>SUM($B2:I2)</f>
         <v>1.15508044395829</v>
       </c>
-      <c r="J3" s="33">
+      <c r="J3" s="29">
         <f>SUM($B2:J2)</f>
         <v>1.31016088791658</v>
       </c>
-      <c r="K3" s="33">
+      <c r="K3" s="29">
         <f>SUM($B2:K2)</f>
         <v>1.46524133187487</v>
       </c>
-      <c r="L3" s="33">
+      <c r="L3" s="29">
         <f>SUM($B2:L2)</f>
         <v>1.62032177583316</v>
       </c>
-      <c r="M3" s="33">
+      <c r="M3" s="29">
         <f>SUM($B2:M2)</f>
         <v>1.77540221979145</v>
       </c>
-      <c r="N3" s="33">
+      <c r="N3" s="29">
         <f>SUM($B2:N2)</f>
         <v>1.93048266374974</v>
       </c>
-      <c r="O3" s="33">
+      <c r="O3" s="29">
         <f>SUM($B2:O2)</f>
         <v>2</v>
       </c>
-      <c r="P3" s="33">
+      <c r="P3" s="29">
         <f>SUM($B2:P2)</f>
         <v>2.15978593272171</v>
       </c>
-      <c r="Q3" s="33">
+      <c r="Q3" s="29">
         <f>SUM($B2:Q2)</f>
         <v>2.31957186544343</v>
       </c>
-      <c r="R3" s="33">
+      <c r="R3" s="29">
         <f>SUM($B2:R2)</f>
         <v>2.47935779816514</v>
       </c>
-      <c r="S3" s="33">
+      <c r="S3" s="29">
         <f>SUM($B2:S2)</f>
         <v>2.63914373088685</v>
       </c>
-      <c r="T3" s="33">
+      <c r="T3" s="29">
         <f>SUM($B2:T2)</f>
         <v>2.79892966360857</v>
       </c>
-      <c r="U3" s="33">
+      <c r="U3" s="29">
         <f>SUM($B2:U2)</f>
         <v>2.95871559633028</v>
       </c>
-      <c r="V3" s="33">
+      <c r="V3" s="29">
         <f>SUM($B2:V2)</f>
         <v>3</v>
       </c>
-      <c r="W3" s="33">
+      <c r="W3" s="29">
         <f>SUM($B2:W2)</f>
         <v>3.15603183736095</v>
       </c>
-      <c r="X3" s="33">
+      <c r="X3" s="29">
         <f>SUM($B2:X2)</f>
         <v>3.31206367472191</v>
       </c>
-      <c r="Y3" s="33">
+      <c r="Y3" s="29">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208286</v>
       </c>
-      <c r="Z3" s="33">
+      <c r="Z3" s="29">
         <f>SUM($B2:Z2)</f>
         <v>3.62412734944381</v>
       </c>
-      <c r="AA3" s="33">
+      <c r="AA3" s="29">
         <f>SUM($B2:AA2)</f>
         <v>3.78015918680476</v>
       </c>
-      <c r="AB3" s="33">
+      <c r="AB3" s="29">
         <f>SUM($B2:AB2)</f>
         <v>3.93619102416571</v>
       </c>
-      <c r="AC3" s="33">
+      <c r="AC3" s="29">
         <f>SUM($B2:AC2)</f>
-        <v>3.93619102416571</v>
-      </c>
-      <c r="AD3" s="33">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="29">
         <f>SUM($B2:AD2)</f>
-        <v>3.93619102416571</v>
-      </c>
-      <c r="AE3" s="33">
+        <v>4</v>
+      </c>
+      <c r="AE3" s="29">
         <f>SUM($B2:AE2)</f>
-        <v>3.93619102416571</v>
-      </c>
-      <c r="AF3" s="33">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="29">
         <f>SUM($B2:AF2)</f>
-        <v>3.93619102416571</v>
-      </c>
-      <c r="AG3" s="33">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="29">
         <f>SUM($B2:AG2)</f>
-        <v>3.93619102416571</v>
-      </c>
-      <c r="AH3" s="33">
+        <v>4</v>
+      </c>
+      <c r="AH3" s="29">
         <f>SUM($B2:AH2)</f>
-        <v>3.93619102416571</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:34">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="29">
         <f>AVERAGE($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="29">
         <f>AVERAGE($B2:C2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="29">
         <f>AVERAGE($B2:D2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="29">
         <f>AVERAGE($B2:E2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="29">
         <f>AVERAGE($B2:F2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="29">
         <f>AVERAGE($B2:G2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="H4" s="33">
+      <c r="H4" s="29">
         <f>AVERAGE($B2:H2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="29">
         <f>AVERAGE($B2:I2)</f>
         <v>0.144385055494786</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="29">
         <f>AVERAGE($B2:J2)</f>
         <v>0.145573431990731</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="29">
         <f>AVERAGE($B2:K2)</f>
         <v>0.146524133187487</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="29">
         <f>AVERAGE($B2:L2)</f>
         <v>0.147301979621197</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="29">
         <f>AVERAGE($B2:M2)</f>
         <v>0.147950184982621</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="29">
         <f>AVERAGE($B2:N2)</f>
         <v>0.148498666442288</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="29">
         <f>AVERAGE($B2:O2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="29">
         <f>AVERAGE($B2:P2)</f>
         <v>0.143985728848114</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="29">
         <f>AVERAGE($B2:Q2)</f>
         <v>0.144973241590214</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="29">
         <f>AVERAGE($B2:R2)</f>
         <v>0.145844576362655</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="29">
         <f>AVERAGE($B2:S2)</f>
         <v>0.146619096160381</v>
       </c>
-      <c r="T4" s="33">
+      <c r="T4" s="29">
         <f>AVERAGE($B2:T2)</f>
         <v>0.147312087558346</v>
       </c>
-      <c r="U4" s="33">
+      <c r="U4" s="29">
         <f>AVERAGE($B2:U2)</f>
         <v>0.147935779816514</v>
       </c>
-      <c r="V4" s="33">
+      <c r="V4" s="29">
         <f>AVERAGE($B2:V2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="W4" s="33">
+      <c r="W4" s="29">
         <f>AVERAGE($B2:W2)</f>
         <v>0.143455992607316</v>
       </c>
-      <c r="X4" s="33">
+      <c r="X4" s="29">
         <f>AVERAGE($B2:X2)</f>
         <v>0.14400276846617</v>
       </c>
-      <c r="Y4" s="33">
+      <c r="Y4" s="29">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="Z4" s="33">
+      <c r="Z4" s="29">
         <f>AVERAGE($B2:Z2)</f>
         <v>0.144965093977752</v>
       </c>
-      <c r="AA4" s="33">
+      <c r="AA4" s="29">
         <f>AVERAGE($B2:AA2)</f>
         <v>0.145390737954029</v>
       </c>
-      <c r="AB4" s="33">
+      <c r="AB4" s="29">
         <f>AVERAGE($B2:AB2)</f>
         <v>0.145784852746878</v>
       </c>
-      <c r="AC4" s="33">
+      <c r="AC4" s="29">
         <f>AVERAGE($B2:AC2)</f>
-        <v>0.140578250863061</v>
-      </c>
-      <c r="AD4" s="33">
+        <v>0.142857142857143</v>
+      </c>
+      <c r="AD4" s="29">
         <f>AVERAGE($B2:AD2)</f>
-        <v>0.135730724971231</v>
-      </c>
-      <c r="AE4" s="33">
+        <v>0.137931034482759</v>
+      </c>
+      <c r="AE4" s="29">
         <f>AVERAGE($B2:AE2)</f>
-        <v>0.13120636747219</v>
-      </c>
-      <c r="AF4" s="33">
+        <v>0.133333333333333</v>
+      </c>
+      <c r="AF4" s="29">
         <f>AVERAGE($B2:AF2)</f>
-        <v>0.126973904005346</v>
-      </c>
-      <c r="AG4" s="33">
+        <v>0.129032258064516</v>
+      </c>
+      <c r="AG4" s="29">
         <f>AVERAGE($B2:AG2)</f>
-        <v>0.123005969505178</v>
-      </c>
-      <c r="AH4" s="33">
+        <v>0.125</v>
+      </c>
+      <c r="AH4" s="29">
         <f>AVERAGE($B2:AH2)</f>
-        <v>0.119278515883809</v>
+        <v>0.121212121212121</v>
       </c>
     </row>
     <row r="5" spans="1:34">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="29">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="C5" s="33">
-        <f t="shared" ref="C5:S5" si="0">B5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D5" s="33">
+      <c r="C5" s="29">
+        <f t="shared" ref="C5:AH5" si="0">B5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="H5" s="33">
+      <c r="H5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="I5" s="33">
+      <c r="I5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="M5" s="33">
+      <c r="M5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="N5" s="33">
+      <c r="N5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="O5" s="33">
+      <c r="O5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="P5" s="33">
+      <c r="P5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Q5" s="33">
+      <c r="Q5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="R5" s="33">
+      <c r="R5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="S5" s="33">
+      <c r="S5" s="29">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="T5" s="33">
-        <f>S5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="U5" s="33">
-        <f>T5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="V5" s="33">
-        <f>U5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="W5" s="33">
-        <f>V5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="X5" s="33">
-        <f>W5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="Y5" s="33">
-        <f>X5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="Z5" s="33">
-        <f>Y5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AA5" s="33">
-        <f>Z5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AB5" s="33">
-        <f>AA5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AC5" s="33">
-        <f>AB5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AD5" s="33">
-        <f>AC5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AE5" s="33">
-        <f>AD5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AF5" s="33">
-        <f>AE5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AG5" s="33">
-        <f>AF5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AH5" s="33">
-        <f>AG5</f>
+      <c r="T5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="U5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="V5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="W5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="X5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="Y5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="Z5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AA5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AB5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AC5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AD5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AE5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AF5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AG5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AH5" s="29">
+        <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
     </row>
@@ -2197,136 +2185,136 @@
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="33">
-        <f t="shared" ref="B6:S6" si="1">B5-B2</f>
+      <c r="B6" s="29">
+        <f t="shared" ref="B6:AH6" si="1">B5-B2</f>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="29">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="29">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="29">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="29">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="29">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="H6" s="33">
+      <c r="H6" s="29">
         <f t="shared" si="1"/>
         <v>0.080051368497053</v>
       </c>
-      <c r="I6" s="33">
+      <c r="I6" s="29">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="29">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="K6" s="33">
+      <c r="K6" s="29">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="L6" s="33">
+      <c r="L6" s="29">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="M6" s="33">
+      <c r="M6" s="29">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="29">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="O6" s="33">
+      <c r="O6" s="29">
         <f t="shared" si="1"/>
         <v>0.0843288175958981</v>
       </c>
-      <c r="P6" s="33">
+      <c r="P6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555855</v>
-      </c>
-      <c r="Q6" s="33">
+        <v>-0.00593977887555899</v>
+      </c>
+      <c r="Q6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555855</v>
-      </c>
-      <c r="R6" s="33">
+        <v>-0.00593977887555899</v>
+      </c>
+      <c r="R6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555855</v>
-      </c>
-      <c r="S6" s="33">
+        <v>-0.00593977887555899</v>
+      </c>
+      <c r="S6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555855</v>
-      </c>
-      <c r="T6" s="33">
-        <f>T5-T2</f>
-        <v>-0.00593977887555855</v>
-      </c>
-      <c r="U6" s="33">
-        <f>U5-U2</f>
-        <v>-0.00593977887555855</v>
-      </c>
-      <c r="V6" s="33">
-        <f>V5-V2</f>
+        <v>-0.00593977887555899</v>
+      </c>
+      <c r="T6" s="29">
+        <f t="shared" si="1"/>
+        <v>-0.00593977887555899</v>
+      </c>
+      <c r="U6" s="29">
+        <f t="shared" si="1"/>
+        <v>-0.00593977887555899</v>
+      </c>
+      <c r="V6" s="29">
+        <f t="shared" si="1"/>
         <v>0.112561750176429</v>
       </c>
-      <c r="W6" s="33">
-        <f>W5-W2</f>
-        <v>-0.00218568351479728</v>
-      </c>
-      <c r="X6" s="33">
-        <f>X5-X2</f>
-        <v>-0.00218568351479728</v>
-      </c>
-      <c r="Y6" s="33">
-        <f>Y5-Y2</f>
-        <v>-0.00218568351479728</v>
-      </c>
-      <c r="Z6" s="33">
-        <f>Z5-Z2</f>
-        <v>-0.00218568351479728</v>
-      </c>
-      <c r="AA6" s="33">
-        <f>AA5-AA2</f>
-        <v>-0.00218568351479728</v>
-      </c>
-      <c r="AB6" s="33">
-        <f>AB5-AB2</f>
-        <v>-0.00218568351479728</v>
-      </c>
-      <c r="AC6" s="33">
-        <f>AC5-AC2</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AD6" s="33">
-        <f>AD5-AD2</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AE6" s="33">
-        <f>AE5-AE2</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AF6" s="33">
-        <f>AF5-AF2</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AG6" s="33">
-        <f>AG5-AG2</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AH6" s="33">
-        <f>AH5-AH2</f>
+      <c r="W6" s="29">
+        <f t="shared" si="1"/>
+        <v>-0.002185683514797</v>
+      </c>
+      <c r="X6" s="29">
+        <f t="shared" si="1"/>
+        <v>-0.002185683514797</v>
+      </c>
+      <c r="Y6" s="29">
+        <f t="shared" si="1"/>
+        <v>-0.002185683514797</v>
+      </c>
+      <c r="Z6" s="29">
+        <f t="shared" si="1"/>
+        <v>-0.002185683514797</v>
+      </c>
+      <c r="AA6" s="29">
+        <f t="shared" si="1"/>
+        <v>-0.002185683514797</v>
+      </c>
+      <c r="AB6" s="29">
+        <f t="shared" si="1"/>
+        <v>-0.002185683514797</v>
+      </c>
+      <c r="AC6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.0900371780118617</v>
+      </c>
+      <c r="AD6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AE6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AF6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AG6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AH6" s="29">
+        <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
     </row>
@@ -2371,18 +2359,18 @@
       <c r="B10" s="1">
         <v>100</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="29">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D10" s="1">
         <v>50</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="29">
         <f>AVERAGE(F$10:F10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="29">
         <f t="shared" ref="F10:F20" si="2">G10/B10</f>
         <v>0</v>
       </c>
@@ -2404,18 +2392,18 @@
       <c r="B11" s="1">
         <v>50</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="29">
         <f>C10</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D11" s="1">
         <v>25</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="29">
         <f>AVERAGE(F$10:F11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2474,7 +2462,7 @@
       <c r="B15" s="1">
         <v>257</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="29">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -2482,11 +2470,11 @@
         <f t="shared" ref="D10:D20" si="4">ROUND(B15*C15,0)</f>
         <v>40</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="29">
         <f>AVERAGE(F$15:F15)</f>
         <v>0.066147859922179</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="29">
         <f t="shared" si="2"/>
         <v>0.066147859922179</v>
       </c>
@@ -2497,7 +2485,7 @@
       <c r="H15" s="1">
         <v>240</v>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="31">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
@@ -2512,7 +2500,7 @@
       <c r="B16" s="1">
         <v>390</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="29">
         <f t="shared" ref="C16:C20" si="6">C15</f>
         <v>0.153846153846154</v>
       </c>
@@ -2520,11 +2508,11 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="29">
         <f>AVERAGE(F$15:F16)</f>
         <v>0.071535468422628</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="29">
         <f t="shared" si="2"/>
         <v>0.0769230769230769</v>
       </c>
@@ -2535,7 +2523,7 @@
       <c r="H16" s="1">
         <v>360</v>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="31">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
@@ -2550,7 +2538,7 @@
       <c r="B17" s="1">
         <v>484</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="29">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -2558,11 +2546,11 @@
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="29">
         <f>AVERAGE(F$15:F17)</f>
         <v>0.0752385216481432</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="29">
         <f t="shared" si="2"/>
         <v>0.0826446280991736</v>
       </c>
@@ -2573,7 +2561,7 @@
       <c r="H17" s="1">
         <v>444</v>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="31">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
@@ -2588,7 +2576,7 @@
       <c r="B18" s="1">
         <v>240</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="29">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -2596,11 +2584,11 @@
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="29">
         <f>AVERAGE(F$15:F18)</f>
         <v>0.0751788912361074</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="29">
         <f t="shared" si="2"/>
         <v>0.075</v>
       </c>
@@ -2611,7 +2599,7 @@
       <c r="H18" s="1">
         <v>222</v>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="31">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
@@ -2626,7 +2614,7 @@
       <c r="B19" s="1">
         <v>271</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="29">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -2634,11 +2622,11 @@
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="29">
         <f>AVERAGE(F$15:F19)</f>
         <v>0.0741652532102881</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="29">
         <f t="shared" si="2"/>
         <v>0.0701107011070111</v>
       </c>
@@ -2649,7 +2637,7 @@
       <c r="H19" s="1">
         <v>252</v>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="31">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
@@ -2664,7 +2652,7 @@
       <c r="B20" s="1">
         <v>278</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="29">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -2672,11 +2660,11 @@
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="29">
         <f>AVERAGE(F$15:F20)</f>
         <v>0.073794785349101</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="29">
         <f t="shared" si="2"/>
         <v>0.0719424460431655</v>
       </c>
@@ -2687,7 +2675,7 @@
       <c r="H20" s="1">
         <v>258</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="31">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
@@ -2696,17 +2684,17 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="C21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
+      <c r="C21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
+      <c r="C22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1" t="s">
@@ -2747,7 +2735,7 @@
       <c r="B24" s="1">
         <v>440</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="29">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -2755,11 +2743,11 @@
         <f t="shared" ref="D24:D28" si="7">ROUND(B24*C24,0)</f>
         <v>68</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="29">
         <f>AVERAGE(F$24:F24)</f>
         <v>0.0727272727272727</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="29">
         <f t="shared" ref="F24:F28" si="8">G24/B24</f>
         <v>0.0727272727272727</v>
       </c>
@@ -2770,7 +2758,7 @@
       <c r="H24" s="1">
         <v>408</v>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="31">
         <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
         <v>440</v>
       </c>
@@ -2785,7 +2773,7 @@
       <c r="B25" s="1">
         <v>378</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="29">
         <f t="shared" ref="C25:C28" si="11">C24</f>
         <v>0.153846153846154</v>
       </c>
@@ -2793,11 +2781,11 @@
         <f t="shared" si="7"/>
         <v>58</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="29">
         <f>AVERAGE(F$24:F25)</f>
         <v>0.076046176046176</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="29">
         <f t="shared" si="8"/>
         <v>0.0793650793650794</v>
       </c>
@@ -2808,7 +2796,7 @@
       <c r="H25" s="1">
         <v>348</v>
       </c>
-      <c r="I25" s="35">
+      <c r="I25" s="31">
         <f t="shared" si="10"/>
         <v>378</v>
       </c>
@@ -2823,7 +2811,7 @@
       <c r="B26" s="1">
         <v>209</v>
       </c>
-      <c r="C26" s="33">
+      <c r="C26" s="29">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -2831,11 +2819,11 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="29">
         <f>AVERAGE(F$24:F26)</f>
         <v>0.0778106883370041</v>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="29">
         <f t="shared" si="8"/>
         <v>0.0813397129186603</v>
       </c>
@@ -2846,7 +2834,7 @@
       <c r="H26" s="1">
         <v>192</v>
       </c>
-      <c r="I26" s="35">
+      <c r="I26" s="31">
         <f t="shared" si="10"/>
         <v>209</v>
       </c>
@@ -2861,7 +2849,7 @@
       <c r="B27" s="1">
         <v>62</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="29">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -2869,11 +2857,11 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="29">
         <f>AVERAGE(F$24:F27)</f>
         <v>0.0664225323817854</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="29">
         <f t="shared" si="8"/>
         <v>0.032258064516129</v>
       </c>
@@ -2884,7 +2872,7 @@
       <c r="H27" s="1">
         <v>60</v>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="31">
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
@@ -2899,7 +2887,7 @@
       <c r="B28" s="1">
         <v>464</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="29">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -2907,11 +2895,11 @@
         <f t="shared" si="7"/>
         <v>71</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="29">
         <f>AVERAGE(F$24:F28)</f>
         <v>0.0695173362502559</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="29">
         <f t="shared" si="8"/>
         <v>0.0818965517241379</v>
       </c>
@@ -2922,7 +2910,7 @@
       <c r="H28" s="1">
         <v>426</v>
       </c>
-      <c r="I28" s="35">
+      <c r="I28" s="31">
         <f t="shared" si="10"/>
         <v>464</v>
       </c>
@@ -2931,9 +2919,9 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="C29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
+      <c r="C29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
@@ -2979,7 +2967,7 @@
       <c r="B32" s="1">
         <v>132</v>
       </c>
-      <c r="C32" s="33">
+      <c r="C32" s="29">
         <f t="shared" ref="C32:C35" si="12">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -2987,27 +2975,27 @@
         <f t="shared" ref="D32:D35" si="13">ROUND(B32*C32,0)</f>
         <v>20</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="29">
         <f>AVERAGE(F$32:F32)</f>
-        <v>0.0151515151515152</v>
-      </c>
-      <c r="F32" s="33">
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="F32" s="29">
         <f t="shared" ref="F32:F35" si="14">G32/B32</f>
-        <v>0.0151515151515152</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="G32" s="1">
         <f t="shared" ref="G32:G35" si="15">I32-H32</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H32" s="1">
         <v>120</v>
       </c>
-      <c r="I32" s="36">
+      <c r="I32" s="31">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="J32" s="1">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -3017,7 +3005,7 @@
       <c r="B33" s="1">
         <v>30</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="29">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -3025,11 +3013,11 @@
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="29">
         <f>AVERAGE(F$32:F33)</f>
-        <v>0.00757575757575758</v>
-      </c>
-      <c r="F33" s="33">
+        <v>0.0454545454545455</v>
+      </c>
+      <c r="F33" s="29">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -3040,7 +3028,7 @@
       <c r="H33" s="1">
         <v>30</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="31">
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
@@ -3055,7 +3043,7 @@
       <c r="B34" s="1">
         <v>395</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="29">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -3063,11 +3051,11 @@
         <f t="shared" si="13"/>
         <v>61</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="29">
         <f>AVERAGE(F$32:F34)</f>
-        <v>0.0295230788901675</v>
-      </c>
-      <c r="F34" s="33">
+        <v>0.0547756041426928</v>
+      </c>
+      <c r="F34" s="29">
         <f t="shared" si="14"/>
         <v>0.0734177215189873</v>
       </c>
@@ -3078,7 +3066,7 @@
       <c r="H34" s="1">
         <v>366</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="31">
         <f t="shared" si="16"/>
         <v>395</v>
       </c>
@@ -3093,7 +3081,7 @@
       <c r="B35" s="1">
         <v>66</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="29">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -3101,11 +3089,11 @@
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="29">
         <f>AVERAGE(F$32:F35)</f>
-        <v>0.0448695818948984</v>
-      </c>
-      <c r="F35" s="33">
+        <v>0.0638089758342923</v>
+      </c>
+      <c r="F35" s="29">
         <f t="shared" si="14"/>
         <v>0.0909090909090909</v>
       </c>
@@ -3116,7 +3104,7 @@
       <c r="H35" s="1">
         <v>60</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="31">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
@@ -3128,9 +3116,9 @@
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
+      <c r="C37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
@@ -3171,7 +3159,7 @@
       <c r="B39" s="1">
         <v>100</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="29">
         <f t="shared" ref="C39:C41" si="17">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3179,11 +3167,11 @@
         <f>ROUND(B39*C39,0)</f>
         <v>15</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="29">
         <f>AVERAGE(F$39:F39)</f>
         <v>0.15</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="29">
         <f>G39/B39</f>
         <v>0.15</v>
       </c>
@@ -3191,7 +3179,7 @@
         <f>I39-H39</f>
         <v>15</v>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="31">
         <f t="shared" ref="I39:I41" si="18">MIN($J$38*D39,J39)</f>
         <v>15</v>
       </c>
@@ -3207,7 +3195,7 @@
         <f>26+83</f>
         <v>109</v>
       </c>
-      <c r="C40" s="33">
+      <c r="C40" s="29">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
@@ -3215,11 +3203,11 @@
         <f>ROUND(B40*C40,0)</f>
         <v>17</v>
       </c>
-      <c r="E40" s="33">
+      <c r="E40" s="29">
         <f>AVERAGE(F$39:F40)</f>
         <v>0.152981651376147</v>
       </c>
-      <c r="F40" s="33">
+      <c r="F40" s="29">
         <f>G40/B40</f>
         <v>0.155963302752294</v>
       </c>
@@ -3227,7 +3215,7 @@
         <f>I40-H40</f>
         <v>17</v>
       </c>
-      <c r="I40" s="35">
+      <c r="I40" s="31">
         <f t="shared" si="18"/>
         <v>17</v>
       </c>
@@ -3242,7 +3230,7 @@
       <c r="B41" s="1">
         <v>148</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="29">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
@@ -3250,11 +3238,11 @@
         <f>ROUND(B41*C41,0)</f>
         <v>23</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="29">
         <f>AVERAGE(F$39:F41)</f>
         <v>0.101987767584098</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="29">
         <f>G41/B41</f>
         <v>0</v>
       </c>
@@ -3262,7 +3250,7 @@
         <f>I41-H41</f>
         <v>0</v>
       </c>
-      <c r="I41" s="36">
+      <c r="I41" s="32">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -3274,9 +3262,9 @@
       <c r="A43" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
+      <c r="C43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
@@ -3318,7 +3306,7 @@
         <f>212+52+63</f>
         <v>327</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="29">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3326,11 +3314,11 @@
         <f>ROUND(B45*C45,0)</f>
         <v>50</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="29">
         <f>AVERAGE(F$45:F45)</f>
         <v>0.0825688073394495</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="29">
         <f>G45/B45</f>
         <v>0.0825688073394495</v>
       </c>
@@ -3341,7 +3329,7 @@
       <c r="H45" s="1">
         <v>300</v>
       </c>
-      <c r="I45" s="35">
+      <c r="I45" s="31">
         <f>MIN($J$44*D45,J45)</f>
         <v>327</v>
       </c>
@@ -3357,7 +3345,7 @@
         <f>16+14</f>
         <v>30</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="29">
         <f>C45</f>
         <v>0.153846153846154</v>
       </c>
@@ -3365,11 +3353,11 @@
         <f>ROUND(B46*C46,0)</f>
         <v>5</v>
       </c>
-      <c r="E46" s="33">
+      <c r="E46" s="29">
         <f>AVERAGE(F$45:F46)</f>
         <v>0.0412844036697248</v>
       </c>
-      <c r="F46" s="33">
+      <c r="F46" s="29">
         <f>G46/B46</f>
         <v>0</v>
       </c>
@@ -3380,7 +3368,7 @@
       <c r="H46" s="1">
         <v>30</v>
       </c>
-      <c r="I46" s="35">
+      <c r="I46" s="31">
         <f>MIN($J$44*D46,J46)</f>
         <v>30</v>
       </c>
@@ -3392,9 +3380,9 @@
       <c r="A48" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
+      <c r="C48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
@@ -3435,7 +3423,7 @@
       <c r="B50" s="1">
         <v>523</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="29">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3443,11 +3431,11 @@
         <f>ROUND(B50*C50,0)</f>
         <v>80</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="29">
         <f>AVERAGE(F$50:F50)</f>
         <v>0.0611854684512428</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="29">
         <f>G50/B50</f>
         <v>0.0611854684512428</v>
       </c>
@@ -3455,7 +3443,7 @@
         <f>I50-H50</f>
         <v>32</v>
       </c>
-      <c r="I50" s="36">
+      <c r="I50" s="32">
         <f>MIN($J$49*D50,J50)</f>
         <v>32</v>
       </c>
@@ -3468,7 +3456,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AH1 A2:AA2 AC2 A3:AH30 A31:I31 K31:AH35 A32:G35 I32:I35 A36:AH50" formulaRange="1"/>
+    <ignoredError sqref="A36:AH39 A40 C40:AH40 A41:AH50 I32:I35 A32:G35 K31:AH35 A31:I31 A3:AH30 A2:AA2 A1:AH1" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3506,7 +3494,7 @@
       <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="26" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3520,7 +3508,7 @@
       <c r="D3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="26" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3534,7 +3522,7 @@
       <c r="D4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="26" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3548,7 +3536,7 @@
       <c r="D5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="26" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3562,7 +3550,7 @@
       <c r="D6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="26" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3576,7 +3564,7 @@
       <c r="D7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="26" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3584,7 +3572,7 @@
       <c r="D8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="26" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3598,7 +3586,7 @@
       <c r="D9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="26" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3612,7 +3600,7 @@
       <c r="D10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="26" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3626,7 +3614,7 @@
       <c r="D11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="26" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3640,7 +3628,7 @@
       <c r="D12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="26" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3654,7 +3642,7 @@
       <c r="D13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="26" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3662,7 +3650,7 @@
       <c r="D14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="26" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3671,12 +3659,12 @@
         <v>32</v>
       </c>
       <c r="B15" s="1">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="26" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3690,7 +3678,7 @@
       <c r="D16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="30"/>
+      <c r="E16" s="26"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
@@ -3779,7 +3767,7 @@
       <c r="E24" s="1">
         <v>63</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="27" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3856,21 +3844,21 @@
       <c r="A2" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="5" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" ht="15.15" spans="1:4">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>92</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -3881,14 +3869,14 @@
       </c>
     </row>
     <row r="4" ht="15.15" spans="1:4">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3896,57 +3884,57 @@
       <c r="A5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:4">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="14" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:4">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="21"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
     <row r="8" ht="15.15" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="19" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="9" ht="15.15" spans="1:4">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="20" t="s">
         <v>90</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -3957,30 +3945,30 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="10"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="10"/>
+    <row r="11" ht="15.15" spans="1:4">
+      <c r="A11" s="8"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" ht="15.15" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="24" t="s">
         <v>110</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -3991,16 +3979,16 @@
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:4">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="12" t="s">
         <v>113</v>
       </c>
     </row>

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -3220,7 +3220,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -3456,7 +3456,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A36:AH39 A40 C40:AH40 A41:AH50 I32:I35 A32:G35 K31:AH35 A31:I31 A3:AH30 A2:AA2 A1:AH1" formulaRange="1"/>
+    <ignoredError sqref="A1:AH1 A2:AA2 A3:AH30 A31:I31 K31:AH35 A32:G35 I32:I35 A41:AH50 C40:I40 K40:AH40 A40 A36:AH39" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3719,13 +3719,13 @@
       </c>
       <c r="B21" s="1">
         <f>C21+D21</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
       </c>
       <c r="D21" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6">

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -157,10 +157,10 @@
     <t>农大辅导</t>
   </si>
   <si>
-    <t>面试准备</t>
-  </si>
-  <si>
     <t>库的实现</t>
+  </si>
+  <si>
+    <t>数据系统</t>
   </si>
   <si>
     <t>页码</t>
@@ -1145,7 +1145,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1237,6 +1237,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1712,26 +1715,26 @@
       <c r="O2" s="29">
         <v>0.0695173362502559</v>
       </c>
-      <c r="P2" s="29">
-        <v>0.159785932721713</v>
+      <c r="P2" s="31">
+        <v>0.15406162464986</v>
       </c>
       <c r="Q2" s="29">
-        <v>0.159785932721713</v>
+        <v>0.15406162464986</v>
       </c>
       <c r="R2" s="29">
-        <v>0.159785932721713</v>
+        <v>0.15406162464986</v>
       </c>
       <c r="S2" s="29">
-        <v>0.159785932721713</v>
+        <v>0.15406162464986</v>
       </c>
       <c r="T2" s="29">
-        <v>0.159785932721713</v>
+        <v>0.15406162464986</v>
       </c>
       <c r="U2" s="29">
-        <v>0.159785932721713</v>
+        <v>0.15406162464986</v>
       </c>
       <c r="V2" s="29">
-        <v>0.0412844036697248</v>
+        <v>0.0756302521008403</v>
       </c>
       <c r="W2" s="29">
         <v>0.156031837360951</v>
@@ -1832,47 +1835,47 @@
       </c>
       <c r="P3" s="29">
         <f>SUM($B2:P2)</f>
-        <v>2.15978593272171</v>
+        <v>2.15406162464986</v>
       </c>
       <c r="Q3" s="29">
         <f>SUM($B2:Q2)</f>
-        <v>2.31957186544343</v>
+        <v>2.30812324929972</v>
       </c>
       <c r="R3" s="29">
         <f>SUM($B2:R2)</f>
-        <v>2.47935779816514</v>
+        <v>2.46218487394958</v>
       </c>
       <c r="S3" s="29">
         <f>SUM($B2:S2)</f>
-        <v>2.63914373088685</v>
+        <v>2.61624649859944</v>
       </c>
       <c r="T3" s="29">
         <f>SUM($B2:T2)</f>
-        <v>2.79892966360857</v>
+        <v>2.7703081232493</v>
       </c>
       <c r="U3" s="29">
         <f>SUM($B2:U2)</f>
-        <v>2.95871559633028</v>
+        <v>2.92436974789916</v>
       </c>
       <c r="V3" s="29">
         <f>SUM($B2:V2)</f>
         <v>3</v>
       </c>
       <c r="W3" s="29">
-        <f>SUM($B2:W2)</f>
-        <v>3.15603183736095</v>
+        <f>SUM($B2:Y2)</f>
+        <v>3.46809551208285</v>
       </c>
       <c r="X3" s="29">
-        <f>SUM($B2:X2)</f>
-        <v>3.31206367472191</v>
+        <f>SUM($B2:Y2)</f>
+        <v>3.46809551208285</v>
       </c>
       <c r="Y3" s="29">
         <f>SUM($B2:Y2)</f>
-        <v>3.46809551208286</v>
+        <v>3.46809551208285</v>
       </c>
       <c r="Z3" s="29">
         <f>SUM($B2:Z2)</f>
-        <v>3.62412734944381</v>
+        <v>3.6241273494438</v>
       </c>
       <c r="AA3" s="29">
         <f>SUM($B2:AA2)</f>
@@ -1969,39 +1972,39 @@
       </c>
       <c r="P4" s="29">
         <f>AVERAGE($B2:P2)</f>
-        <v>0.143985728848114</v>
+        <v>0.143604108309991</v>
       </c>
       <c r="Q4" s="29">
         <f>AVERAGE($B2:Q2)</f>
-        <v>0.144973241590214</v>
+        <v>0.144257703081233</v>
       </c>
       <c r="R4" s="29">
         <f>AVERAGE($B2:R2)</f>
-        <v>0.145844576362655</v>
+        <v>0.144834404349975</v>
       </c>
       <c r="S4" s="29">
         <f>AVERAGE($B2:S2)</f>
-        <v>0.146619096160381</v>
+        <v>0.145347027699969</v>
       </c>
       <c r="T4" s="29">
         <f>AVERAGE($B2:T2)</f>
-        <v>0.147312087558346</v>
+        <v>0.145805690697332</v>
       </c>
       <c r="U4" s="29">
         <f>AVERAGE($B2:U2)</f>
-        <v>0.147935779816514</v>
+        <v>0.146218487394958</v>
       </c>
       <c r="V4" s="29">
         <f>AVERAGE($B2:V2)</f>
         <v>0.142857142857143</v>
       </c>
       <c r="W4" s="29">
-        <f>AVERAGE($B2:W2)</f>
-        <v>0.143455992607316</v>
+        <f>AVERAGE($B2:Y2)</f>
+        <v>0.144503979670119</v>
       </c>
       <c r="X4" s="29">
-        <f>AVERAGE($B2:X2)</f>
-        <v>0.14400276846617</v>
+        <f>AVERAGE($B2:Y2)</f>
+        <v>0.144503979670119</v>
       </c>
       <c r="Y4" s="29">
         <f>AVERAGE($B2:Y2)</f>
@@ -2243,78 +2246,78 @@
       </c>
       <c r="P6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555899</v>
+        <v>-0.000215470803705958</v>
       </c>
       <c r="Q6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555899</v>
+        <v>-0.000215470803705958</v>
       </c>
       <c r="R6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555899</v>
+        <v>-0.000215470803705958</v>
       </c>
       <c r="S6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555899</v>
+        <v>-0.000215470803705958</v>
       </c>
       <c r="T6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555899</v>
+        <v>-0.000215470803705958</v>
       </c>
       <c r="U6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.00593977887555899</v>
+        <v>-0.000215470803705958</v>
       </c>
       <c r="V6" s="29">
         <f t="shared" si="1"/>
-        <v>0.112561750176429</v>
+        <v>0.0782159017453137</v>
       </c>
       <c r="W6" s="29">
-        <f t="shared" si="1"/>
+        <f>W5-W2</f>
         <v>-0.002185683514797</v>
       </c>
       <c r="X6" s="29">
-        <f t="shared" si="1"/>
+        <f>X5-X2</f>
         <v>-0.002185683514797</v>
       </c>
       <c r="Y6" s="29">
-        <f t="shared" si="1"/>
+        <f>Y5-Y2</f>
         <v>-0.002185683514797</v>
       </c>
       <c r="Z6" s="29">
-        <f t="shared" si="1"/>
+        <f>Z5-Z2</f>
         <v>-0.002185683514797</v>
       </c>
       <c r="AA6" s="29">
-        <f t="shared" si="1"/>
+        <f>AA5-AA2</f>
         <v>-0.002185683514797</v>
       </c>
       <c r="AB6" s="29">
-        <f t="shared" si="1"/>
+        <f>AB5-AB2</f>
         <v>-0.002185683514797</v>
       </c>
       <c r="AC6" s="29">
-        <f t="shared" si="1"/>
+        <f>AC5-AC2</f>
         <v>0.0900371780118617</v>
       </c>
       <c r="AD6" s="29">
-        <f t="shared" si="1"/>
+        <f>AD5-AD2</f>
         <v>0.153846153846154</v>
       </c>
       <c r="AE6" s="29">
-        <f t="shared" si="1"/>
+        <f>AE5-AE2</f>
         <v>0.153846153846154</v>
       </c>
       <c r="AF6" s="29">
-        <f t="shared" si="1"/>
+        <f>AF5-AF2</f>
         <v>0.153846153846154</v>
       </c>
       <c r="AG6" s="29">
-        <f t="shared" si="1"/>
+        <f>AG5-AG2</f>
         <v>0.153846153846154</v>
       </c>
       <c r="AH6" s="29">
-        <f t="shared" si="1"/>
+        <f>AH5-AH2</f>
         <v>0.153846153846154</v>
       </c>
     </row>
@@ -2485,7 +2488,7 @@
       <c r="H15" s="1">
         <v>240</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="32">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
@@ -2523,7 +2526,7 @@
       <c r="H16" s="1">
         <v>360</v>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="32">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
@@ -2561,7 +2564,7 @@
       <c r="H17" s="1">
         <v>444</v>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="32">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
@@ -2599,7 +2602,7 @@
       <c r="H18" s="1">
         <v>222</v>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="32">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
@@ -2637,7 +2640,7 @@
       <c r="H19" s="1">
         <v>252</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="32">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
@@ -2675,7 +2678,7 @@
       <c r="H20" s="1">
         <v>258</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="32">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
@@ -2758,7 +2761,7 @@
       <c r="H24" s="1">
         <v>408</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
         <v>440</v>
       </c>
@@ -2796,7 +2799,7 @@
       <c r="H25" s="1">
         <v>348</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <f t="shared" si="10"/>
         <v>378</v>
       </c>
@@ -2834,7 +2837,7 @@
       <c r="H26" s="1">
         <v>192</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="32">
         <f t="shared" si="10"/>
         <v>209</v>
       </c>
@@ -2872,7 +2875,7 @@
       <c r="H27" s="1">
         <v>60</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
@@ -2910,7 +2913,7 @@
       <c r="H28" s="1">
         <v>426</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="32">
         <f t="shared" si="10"/>
         <v>464</v>
       </c>
@@ -2990,7 +2993,7 @@
       <c r="H32" s="1">
         <v>120</v>
       </c>
-      <c r="I32" s="31">
+      <c r="I32" s="32">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
         <v>132</v>
       </c>
@@ -3028,7 +3031,7 @@
       <c r="H33" s="1">
         <v>30</v>
       </c>
-      <c r="I33" s="31">
+      <c r="I33" s="32">
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
@@ -3066,7 +3069,7 @@
       <c r="H34" s="1">
         <v>366</v>
       </c>
-      <c r="I34" s="31">
+      <c r="I34" s="32">
         <f t="shared" si="16"/>
         <v>395</v>
       </c>
@@ -3104,7 +3107,7 @@
       <c r="H35" s="1">
         <v>60</v>
       </c>
-      <c r="I35" s="31">
+      <c r="I35" s="32">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
@@ -3179,7 +3182,7 @@
         <f>I39-H39</f>
         <v>15</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="32">
         <f t="shared" ref="I39:I41" si="18">MIN($J$38*D39,J39)</f>
         <v>15</v>
       </c>
@@ -3215,7 +3218,7 @@
         <f>I40-H40</f>
         <v>17</v>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="32">
         <f t="shared" si="18"/>
         <v>17</v>
       </c>
@@ -3250,7 +3253,7 @@
         <f>I41-H41</f>
         <v>0</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="33">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -3303,117 +3306,114 @@
         <v>41</v>
       </c>
       <c r="B45" s="1">
-        <f>212+52+63</f>
-        <v>327</v>
+        <f>212+52+63+30</f>
+        <v>357</v>
       </c>
       <c r="C45" s="29">
-        <f>4/26</f>
+        <f t="shared" ref="C45:C50" si="19">4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D45" s="1">
         <f>ROUND(B45*C45,0)</f>
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E45" s="29">
         <f>AVERAGE(F$45:F45)</f>
-        <v>0.0825688073394495</v>
+        <v>0.0756302521008403</v>
       </c>
       <c r="F45" s="29">
         <f>G45/B45</f>
-        <v>0.0825688073394495</v>
+        <v>0.0756302521008403</v>
       </c>
       <c r="G45" s="1">
         <f>I45-H45</f>
         <v>27</v>
       </c>
       <c r="H45" s="1">
-        <v>300</v>
-      </c>
-      <c r="I45" s="31">
+        <v>330</v>
+      </c>
+      <c r="I45" s="32">
         <f>MIN($J$44*D45,J45)</f>
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="J45" s="1">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="1">
-        <f>16+14</f>
-        <v>30</v>
-      </c>
-      <c r="C46" s="29">
-        <f>C45</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D46" s="1">
-        <f>ROUND(B46*C46,0)</f>
-        <v>5</v>
-      </c>
-      <c r="E46" s="29">
-        <f>AVERAGE(F$45:F46)</f>
-        <v>0.0412844036697248</v>
-      </c>
-      <c r="F46" s="29">
-        <f>G46/B46</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="1">
-        <f>I46-H46</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="1">
-        <v>30</v>
-      </c>
-      <c r="I46" s="31">
-        <f>MIN($J$44*D46,J46)</f>
-        <v>30</v>
-      </c>
-      <c r="J46" s="1">
-        <v>30</v>
-      </c>
+        <f>327+30</f>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
+        <v>7</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
+      </c>
+      <c r="B49" s="1">
+        <v>523</v>
+      </c>
+      <c r="C49" s="29">
+        <f t="shared" si="19"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D49" s="1">
+        <f>ROUND(B49*C49,0)</f>
+        <v>80</v>
+      </c>
+      <c r="E49" s="29">
+        <f>AVERAGE(F$49:F49)</f>
+        <v>0.0611854684512428</v>
+      </c>
+      <c r="F49" s="29">
+        <f>G49/B49</f>
+        <v>0.0611854684512428</v>
+      </c>
+      <c r="G49" s="1">
+        <f>I49-H49</f>
+        <v>32</v>
+      </c>
+      <c r="I49" s="33">
+        <f>MIN($J$48*D49,J49)</f>
+        <v>32</v>
       </c>
       <c r="J49" s="1">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3421,34 +3421,34 @@
         <v>43</v>
       </c>
       <c r="B50" s="1">
-        <v>523</v>
+        <v>434</v>
       </c>
       <c r="C50" s="29">
-        <f>4/26</f>
+        <f t="shared" si="19"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D50" s="1">
         <f>ROUND(B50*C50,0)</f>
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E50" s="29">
-        <f>AVERAGE(F$50:F50)</f>
-        <v>0.0611854684512428</v>
+        <f>AVERAGE(F$49:F50)</f>
+        <v>0.0305927342256214</v>
       </c>
       <c r="F50" s="29">
         <f>G50/B50</f>
-        <v>0.0611854684512428</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
         <f>I50-H50</f>
-        <v>32</v>
-      </c>
-      <c r="I50" s="32">
-        <f>MIN($J$49*D50,J50)</f>
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="I50" s="33">
+        <f>MIN($J$48*D50,J50)</f>
+        <v>0</v>
       </c>
       <c r="J50" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3456,7 +3456,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AH1 A2:AA2 A3:AH30 A31:I31 K31:AH35 A32:G35 I32:I35 A41:AH50 C40:I40 K40:AH40 A40 A36:AH39" formulaRange="1"/>
+    <ignoredError sqref="I45 C45:G45 K44:AH45 A44:I44 A41:AH43 A46:AH49 A45 A1:AH1 A2:O2 A3:AH30 A31:I31 K31:AH35 A32:G35 I32:I35 C40:I40 K40:AH40 A40 A36:AH39" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="1">
         <v>32</v>

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="121">
   <si>
     <t>日期</t>
   </si>
@@ -145,22 +145,46 @@
     <t>华为认证</t>
   </si>
   <si>
+    <t>通信原理</t>
+  </si>
+  <si>
+    <t>复试针对</t>
+  </si>
+  <si>
+    <t>农大辅导</t>
+  </si>
+  <si>
+    <t>库的实现</t>
+  </si>
+  <si>
+    <t>数据系统</t>
+  </si>
+  <si>
     <t>控制信号</t>
   </si>
   <si>
-    <t>通信原理</t>
-  </si>
-  <si>
-    <t>复试针对</t>
-  </si>
-  <si>
-    <t>农大辅导</t>
-  </si>
-  <si>
-    <t>库的实现</t>
-  </si>
-  <si>
-    <t>数据系统</t>
+    <t>青岛科技</t>
+  </si>
+  <si>
+    <t>矩阵理论</t>
+  </si>
+  <si>
+    <t>人工智能</t>
+  </si>
+  <si>
+    <t>算法设计</t>
+  </si>
+  <si>
+    <t>高级密码</t>
+  </si>
+  <si>
+    <t>数据科学</t>
+  </si>
+  <si>
+    <t>边缘智能</t>
+  </si>
+  <si>
+    <t>软件系统</t>
   </si>
   <si>
     <t>页码</t>
@@ -265,28 +289,25 @@
     <t>三论概述</t>
   </si>
   <si>
+    <t>面试</t>
+  </si>
+  <si>
+    <t>上机</t>
+  </si>
+  <si>
+    <t>视频</t>
+  </si>
+  <si>
+    <t>视频#</t>
+  </si>
+  <si>
+    <t>3-8</t>
+  </si>
+  <si>
     <t>信号</t>
   </si>
   <si>
     <t>控制</t>
-  </si>
-  <si>
-    <t>面试</t>
-  </si>
-  <si>
-    <t>上机</t>
-  </si>
-  <si>
-    <t>视频</t>
-  </si>
-  <si>
-    <t>视频#</t>
-  </si>
-  <si>
-    <t>3-8</t>
-  </si>
-  <si>
-    <t>农大准备</t>
   </si>
   <si>
     <t>正常电脑</t>
@@ -383,7 +404,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,6 +414,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1015,133 +1044,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="17">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="18">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1239,13 +1268,13 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1559,7 +1588,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH50"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="15.7777777777778" style="1" customWidth="1"/>
@@ -1715,7 +1744,7 @@
       <c r="O2" s="29">
         <v>0.0695173362502559</v>
       </c>
-      <c r="P2" s="31">
+      <c r="P2" s="30">
         <v>0.15406162464986</v>
       </c>
       <c r="Q2" s="29">
@@ -2273,51 +2302,51 @@
         <v>0.0782159017453137</v>
       </c>
       <c r="W6" s="29">
-        <f>W5-W2</f>
+        <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
       <c r="X6" s="29">
-        <f>X5-X2</f>
+        <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
       <c r="Y6" s="29">
-        <f>Y5-Y2</f>
+        <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
       <c r="Z6" s="29">
-        <f>Z5-Z2</f>
+        <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
       <c r="AA6" s="29">
-        <f>AA5-AA2</f>
+        <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
       <c r="AB6" s="29">
-        <f>AB5-AB2</f>
+        <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
       <c r="AC6" s="29">
-        <f>AC5-AC2</f>
+        <f t="shared" si="1"/>
         <v>0.0900371780118617</v>
       </c>
       <c r="AD6" s="29">
-        <f>AD5-AD2</f>
+        <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
       <c r="AE6" s="29">
-        <f>AE5-AE2</f>
+        <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
       <c r="AF6" s="29">
-        <f>AF5-AF2</f>
+        <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
       <c r="AG6" s="29">
-        <f>AG5-AG2</f>
+        <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
       <c r="AH6" s="29">
-        <f>AH5-AH2</f>
+        <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
     </row>
@@ -2488,7 +2517,7 @@
       <c r="H15" s="1">
         <v>240</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="31">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
@@ -2526,7 +2555,7 @@
       <c r="H16" s="1">
         <v>360</v>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="31">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
@@ -2564,7 +2593,7 @@
       <c r="H17" s="1">
         <v>444</v>
       </c>
-      <c r="I17" s="32">
+      <c r="I17" s="31">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
@@ -2602,7 +2631,7 @@
       <c r="H18" s="1">
         <v>222</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="31">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
@@ -2640,7 +2669,7 @@
       <c r="H19" s="1">
         <v>252</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="31">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
@@ -2678,7 +2707,7 @@
       <c r="H20" s="1">
         <v>258</v>
       </c>
-      <c r="I20" s="32">
+      <c r="I20" s="31">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
@@ -2761,7 +2790,7 @@
       <c r="H24" s="1">
         <v>408</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="31">
         <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
         <v>440</v>
       </c>
@@ -2799,7 +2828,7 @@
       <c r="H25" s="1">
         <v>348</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="31">
         <f t="shared" si="10"/>
         <v>378</v>
       </c>
@@ -2837,7 +2866,7 @@
       <c r="H26" s="1">
         <v>192</v>
       </c>
-      <c r="I26" s="32">
+      <c r="I26" s="31">
         <f t="shared" si="10"/>
         <v>209</v>
       </c>
@@ -2875,7 +2904,7 @@
       <c r="H27" s="1">
         <v>60</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="31">
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
@@ -2913,7 +2942,7 @@
       <c r="H28" s="1">
         <v>426</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="31">
         <f t="shared" si="10"/>
         <v>464</v>
       </c>
@@ -2993,7 +3022,7 @@
       <c r="H32" s="1">
         <v>120</v>
       </c>
-      <c r="I32" s="32">
+      <c r="I32" s="31">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
         <v>132</v>
       </c>
@@ -3031,7 +3060,7 @@
       <c r="H33" s="1">
         <v>30</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="31">
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
@@ -3069,7 +3098,7 @@
       <c r="H34" s="1">
         <v>366</v>
       </c>
-      <c r="I34" s="32">
+      <c r="I34" s="31">
         <f t="shared" si="16"/>
         <v>395</v>
       </c>
@@ -3107,7 +3136,7 @@
       <c r="H35" s="1">
         <v>60</v>
       </c>
-      <c r="I35" s="32">
+      <c r="I35" s="31">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
@@ -3116,7 +3145,7 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="32" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="29"/>
@@ -3124,7 +3153,7 @@
       <c r="F37" s="29"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="32" t="s">
         <v>7</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -3156,14 +3185,14 @@
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="32" t="s">
         <v>37</v>
       </c>
       <c r="B39" s="1">
         <v>100</v>
       </c>
       <c r="C39" s="29">
-        <f t="shared" ref="C39:C41" si="17">4/26</f>
+        <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D39" s="1">
@@ -3182,8 +3211,8 @@
         <f>I39-H39</f>
         <v>15</v>
       </c>
-      <c r="I39" s="32">
-        <f t="shared" ref="I39:I41" si="18">MIN($J$38*D39,J39)</f>
+      <c r="I39" s="31">
+        <f>MIN($J$38*D39,J39)</f>
         <v>15</v>
       </c>
       <c r="J39" s="1">
@@ -3191,194 +3220,193 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="32" t="s">
         <v>38</v>
       </c>
       <c r="B40" s="1">
-        <f>26+83</f>
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="C40" s="29">
-        <f t="shared" si="17"/>
+        <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D40" s="1">
         <f>ROUND(B40*C40,0)</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E40" s="29">
         <f>AVERAGE(F$39:F40)</f>
-        <v>0.152981651376147</v>
+        <v>0.075</v>
       </c>
       <c r="F40" s="29">
         <f>G40/B40</f>
-        <v>0.155963302752294</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
         <f>I40-H40</f>
-        <v>17</v>
-      </c>
-      <c r="I40" s="32">
-        <f t="shared" si="18"/>
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I40" s="33">
+        <f>MIN($J$38*D40,J40)</f>
+        <v>0</v>
       </c>
       <c r="J40" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="1">
-        <v>148</v>
-      </c>
-      <c r="C41" s="29">
-        <f t="shared" si="17"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D41" s="1">
-        <f>ROUND(B41*C41,0)</f>
-        <v>23</v>
-      </c>
-      <c r="E41" s="29">
-        <f>AVERAGE(F$39:F41)</f>
-        <v>0.101987767584098</v>
-      </c>
-      <c r="F41" s="29">
-        <f>G41/B41</f>
-        <v>0</v>
-      </c>
-      <c r="G41" s="1">
-        <f>I41-H41</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="33">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0</v>
-      </c>
+      <c r="C42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
+        <v>7</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J44" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="1">
+        <v>40</v>
+      </c>
+      <c r="B44" s="1">
         <f>212+52+63+30</f>
         <v>357</v>
       </c>
-      <c r="C45" s="29">
-        <f t="shared" ref="C45:C50" si="19">4/26</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D45" s="1">
-        <f>ROUND(B45*C45,0)</f>
+      <c r="C44" s="29">
+        <f t="shared" ref="C44:C49" si="17">4/26</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D44" s="1">
+        <f>ROUND(B44*C44,0)</f>
         <v>55</v>
       </c>
-      <c r="E45" s="29">
-        <f>AVERAGE(F$45:F45)</f>
+      <c r="E44" s="29">
+        <f>AVERAGE(F$44:F44)</f>
         <v>0.0756302521008403</v>
       </c>
-      <c r="F45" s="29">
-        <f>G45/B45</f>
+      <c r="F44" s="29">
+        <f>G44/B44</f>
         <v>0.0756302521008403</v>
       </c>
-      <c r="G45" s="1">
-        <f>I45-H45</f>
+      <c r="G44" s="1">
+        <f>I44-H44</f>
         <v>27</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H44" s="1">
         <v>330</v>
       </c>
-      <c r="I45" s="32">
-        <f>MIN($J$44*D45,J45)</f>
+      <c r="I44" s="31">
+        <f>MIN($J$43*D44,J44)</f>
         <v>357</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J44" s="1">
         <f>327+30</f>
         <v>357</v>
       </c>
     </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+    </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
+        <v>7</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
+      </c>
+      <c r="B48" s="1">
+        <v>523</v>
+      </c>
+      <c r="C48" s="29">
+        <f t="shared" si="17"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D48" s="1">
+        <f t="shared" ref="D48:D54" si="18">ROUND(B48*C48,0)</f>
+        <v>80</v>
+      </c>
+      <c r="E48" s="29">
+        <f>AVERAGE(F$48:F48)</f>
+        <v>0.0611854684512428</v>
+      </c>
+      <c r="F48" s="29">
+        <f t="shared" ref="F48:F54" si="19">G48/B48</f>
+        <v>0.0611854684512428</v>
+      </c>
+      <c r="G48" s="1">
+        <f t="shared" ref="G48:G54" si="20">I48-H48</f>
+        <v>32</v>
+      </c>
+      <c r="I48" s="33">
+        <f t="shared" ref="I48:I54" si="21">MIN($J$47*D48,J48)</f>
+        <v>32</v>
       </c>
       <c r="J48" s="1">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -3386,34 +3414,34 @@
         <v>42</v>
       </c>
       <c r="B49" s="1">
-        <v>523</v>
+        <v>434</v>
       </c>
       <c r="C49" s="29">
+        <f t="shared" si="17"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D49" s="1">
+        <f t="shared" si="18"/>
+        <v>67</v>
+      </c>
+      <c r="E49" s="29">
+        <f>AVERAGE(F$48:F49)</f>
+        <v>0.106629600585068</v>
+      </c>
+      <c r="F49" s="29">
         <f t="shared" si="19"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D49" s="1">
-        <f>ROUND(B49*C49,0)</f>
-        <v>80</v>
-      </c>
-      <c r="E49" s="29">
-        <f>AVERAGE(F$49:F49)</f>
-        <v>0.0611854684512428</v>
-      </c>
-      <c r="F49" s="29">
-        <f>G49/B49</f>
-        <v>0.0611854684512428</v>
+        <v>0.152073732718894</v>
       </c>
       <c r="G49" s="1">
-        <f>I49-H49</f>
-        <v>32</v>
+        <f t="shared" si="20"/>
+        <v>66</v>
       </c>
       <c r="I49" s="33">
-        <f>MIN($J$48*D49,J49)</f>
-        <v>32</v>
+        <f t="shared" si="21"/>
+        <v>66</v>
       </c>
       <c r="J49" s="1">
-        <v>32</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3421,33 +3449,329 @@
         <v>43</v>
       </c>
       <c r="B50" s="1">
-        <v>434</v>
+        <f>26+83</f>
+        <v>109</v>
       </c>
       <c r="C50" s="29">
+        <f t="shared" ref="C50:C60" si="22">4/26</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D50" s="1">
+        <f t="shared" si="18"/>
+        <v>17</v>
+      </c>
+      <c r="E50" s="29">
+        <f>AVERAGE(F$48:F50)</f>
+        <v>0.123074167974143</v>
+      </c>
+      <c r="F50" s="29">
         <f t="shared" si="19"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D50" s="1">
-        <f>ROUND(B50*C50,0)</f>
-        <v>67</v>
-      </c>
-      <c r="E50" s="29">
-        <f>AVERAGE(F$49:F50)</f>
-        <v>0.0305927342256214</v>
-      </c>
-      <c r="F50" s="29">
-        <f>G50/B50</f>
+        <v>0.155963302752294</v>
+      </c>
+      <c r="G50" s="1">
+        <f t="shared" si="20"/>
+        <v>17</v>
+      </c>
+      <c r="I50" s="31">
+        <f t="shared" si="21"/>
+        <v>17</v>
+      </c>
+      <c r="J50" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="C51" s="29"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="1"/>
+      <c r="I51" s="33"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="1">
+        <v>999</v>
+      </c>
+      <c r="C54" s="29">
+        <f t="shared" si="22"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D54" s="1">
+        <f t="shared" ref="D54:D60" si="23">ROUND(B54*C54,0)</f>
+        <v>154</v>
+      </c>
+      <c r="E54" s="29">
+        <f>AVERAGE(F$54:F54)</f>
+        <v>0.032032032032032</v>
+      </c>
+      <c r="F54" s="29">
+        <f t="shared" ref="F54:F60" si="24">G54/B54</f>
+        <v>0.032032032032032</v>
+      </c>
+      <c r="G54" s="1">
+        <f t="shared" ref="G54:G60" si="25">I54-H54</f>
+        <v>32</v>
+      </c>
+      <c r="I54" s="33">
+        <f t="shared" ref="I54:I60" si="26">MIN($J$53*D54,J54)</f>
+        <v>32</v>
+      </c>
+      <c r="J54" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="1">
+        <v>999</v>
+      </c>
+      <c r="C55" s="29">
+        <f t="shared" si="22"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D55" s="1">
+        <f t="shared" si="23"/>
+        <v>154</v>
+      </c>
+      <c r="E55" s="29">
+        <f>AVERAGE(F$54:F55)</f>
+        <v>0.049049049049049</v>
+      </c>
+      <c r="F55" s="29">
+        <f t="shared" si="24"/>
+        <v>0.0660660660660661</v>
+      </c>
+      <c r="G55" s="1">
+        <f t="shared" si="25"/>
+        <v>66</v>
+      </c>
+      <c r="I55" s="33">
+        <f t="shared" si="26"/>
+        <v>66</v>
+      </c>
+      <c r="J55" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B56" s="1">
+        <v>999</v>
+      </c>
+      <c r="C56" s="29">
+        <f t="shared" si="22"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D56" s="1">
+        <f t="shared" si="23"/>
+        <v>154</v>
+      </c>
+      <c r="E56" s="29">
+        <f>AVERAGE(F$54:F56)</f>
+        <v>0.042042042042042</v>
+      </c>
+      <c r="F56" s="29">
+        <f t="shared" si="24"/>
+        <v>0.028028028028028</v>
+      </c>
+      <c r="G56" s="1">
+        <f t="shared" si="25"/>
+        <v>28</v>
+      </c>
+      <c r="I56" s="33">
+        <f t="shared" si="26"/>
+        <v>28</v>
+      </c>
+      <c r="J56" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" s="1">
+        <v>999</v>
+      </c>
+      <c r="C57" s="29">
+        <f t="shared" si="22"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D57" s="1">
+        <f t="shared" si="23"/>
+        <v>154</v>
+      </c>
+      <c r="E57" s="29">
+        <f>AVERAGE(F$54:F57)</f>
+        <v>0.0315315315315315</v>
+      </c>
+      <c r="F57" s="29">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G50" s="1">
-        <f>I50-H50</f>
+      <c r="G57" s="1">
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I50" s="33">
-        <f>MIN($J$48*D50,J50)</f>
+      <c r="I57" s="33">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B58" s="1">
+        <v>999</v>
+      </c>
+      <c r="C58" s="29">
+        <f t="shared" si="22"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D58" s="1">
+        <f t="shared" si="23"/>
+        <v>154</v>
+      </c>
+      <c r="E58" s="29">
+        <f>AVERAGE(F$54:F58)</f>
+        <v>0.0252252252252252</v>
+      </c>
+      <c r="F58" s="29">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="33">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59" s="1">
+        <v>999</v>
+      </c>
+      <c r="C59" s="29">
+        <f t="shared" si="22"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D59" s="1">
+        <f t="shared" si="23"/>
+        <v>154</v>
+      </c>
+      <c r="E59" s="29">
+        <f>AVERAGE(F$54:F59)</f>
+        <v>0.021021021021021</v>
+      </c>
+      <c r="F59" s="29">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="33">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" s="1">
+        <v>999</v>
+      </c>
+      <c r="C60" s="29">
+        <f t="shared" si="22"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D60" s="1">
+        <f t="shared" si="23"/>
+        <v>154</v>
+      </c>
+      <c r="E60" s="29">
+        <f>AVERAGE(F$54:F60)</f>
+        <v>0.018018018018018</v>
+      </c>
+      <c r="F60" s="29">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="33">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3456,7 +3780,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="I45 C45:G45 K44:AH45 A44:I44 A41:AH43 A46:AH49 A45 A1:AH1 A2:O2 A3:AH30 A31:I31 K31:AH35 A32:G35 I32:I35 C40:I40 K40:AH40 A40 A36:AH39" formulaRange="1"/>
+    <ignoredError sqref="A36:AH39 K40:AH41 I32:I35 A32:G35 K31:AH35 A31:I31 A3:AH30 A2:O2 A1:AH1 A44 A45:AH48 A42:AH42 A43:I43 K43:AH44 C44:G44 I44" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3464,8 +3788,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="10.7777777777778" style="1" customWidth="1"/>
   </cols>
@@ -3475,13 +3799,13 @@
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3492,10 +3816,10 @@
         <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3506,10 +3830,10 @@
         <v>390</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3520,10 +3844,10 @@
         <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3534,10 +3858,10 @@
         <v>240</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3548,10 +3872,10 @@
         <v>271</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3562,18 +3886,18 @@
         <v>278</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3584,10 +3908,10 @@
         <v>440</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3598,10 +3922,10 @@
         <v>378</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3612,10 +3936,10 @@
         <v>209</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3626,10 +3950,10 @@
         <v>62</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3640,18 +3964,18 @@
         <v>464</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3662,10 +3986,10 @@
         <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3676,11 +4000,11 @@
         <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E16" s="26"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -3688,118 +4012,115 @@
         <v>395</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B18" s="1">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="19" spans="1:8">
+      <c r="C19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1">
+        <f>SUM(C20:H20)</f>
+        <v>357</v>
+      </c>
+      <c r="C20" s="1">
+        <v>212</v>
+      </c>
+      <c r="D20" s="1">
+        <v>52</v>
+      </c>
+      <c r="E20" s="1">
+        <v>63</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="1">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="1">
+        <v>66</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="1">
+        <f>C24+D24</f>
+        <v>28</v>
+      </c>
+      <c r="C24" s="1">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B26" s="1">
         <v>23</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1" t="s">
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="1">
-        <f>C21+D21</f>
-        <v>28</v>
-      </c>
-      <c r="C21" s="1">
-        <v>10</v>
-      </c>
-      <c r="D21" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="1">
+      <c r="B27" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="C23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="1">
-        <f>SUM(C24:E24)</f>
-        <v>327</v>
-      </c>
-      <c r="C24" s="1">
-        <v>212</v>
-      </c>
-      <c r="D24" s="1">
-        <v>52</v>
-      </c>
-      <c r="E24" s="1">
-        <v>63</v>
-      </c>
-      <c r="F24" s="27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(C25:D25)</f>
-        <v>30</v>
-      </c>
-      <c r="C25" s="1">
-        <v>16</v>
-      </c>
-      <c r="D25" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="C26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="1">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3828,89 +4149,89 @@
   <sheetData>
     <row r="1" ht="15.15" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" ht="15.15" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" ht="15.15" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:4">
       <c r="A6" s="8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:4">
       <c r="A7" s="16" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -3918,44 +4239,44 @@
     </row>
     <row r="8" ht="15.15" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" ht="15.15" spans="1:4">
       <c r="A9" s="20" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:4">
@@ -3966,30 +4287,30 @@
     </row>
     <row r="12" ht="15.15" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:4">
       <c r="A13" s="8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -1588,13 +1588,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AR60"/>
   <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="15.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:44">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1697,8 +1697,38 @@
       <c r="AH1" s="28">
         <v>46113</v>
       </c>
-    </row>
-    <row r="2" spans="1:34">
+      <c r="AI1" s="28">
+        <v>46114</v>
+      </c>
+      <c r="AJ1" s="28">
+        <v>46115</v>
+      </c>
+      <c r="AK1" s="28">
+        <v>46116</v>
+      </c>
+      <c r="AL1" s="28">
+        <v>46117</v>
+      </c>
+      <c r="AM1" s="28">
+        <v>46118</v>
+      </c>
+      <c r="AN1" s="28">
+        <v>46119</v>
+      </c>
+      <c r="AO1" s="28">
+        <v>46120</v>
+      </c>
+      <c r="AP1" s="28">
+        <v>46121</v>
+      </c>
+      <c r="AQ1" s="28">
+        <v>46122</v>
+      </c>
+      <c r="AR1" s="28">
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1787,7 +1817,7 @@
         <v>0.0638089758342923</v>
       </c>
       <c r="AD2" s="29">
-        <v>0</v>
+        <v>0.154434951354911</v>
       </c>
       <c r="AE2" s="29">
         <v>0</v>
@@ -1801,8 +1831,38 @@
       <c r="AH2" s="29">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:34">
+      <c r="AI2" s="29">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="29">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="29">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="29">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="29">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="29">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="29">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="29">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="29">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1920,26 +1980,66 @@
       </c>
       <c r="AD3" s="29">
         <f>SUM($B2:AD2)</f>
-        <v>4</v>
+        <v>4.15443495135491</v>
       </c>
       <c r="AE3" s="29">
         <f>SUM($B2:AE2)</f>
-        <v>4</v>
+        <v>4.15443495135491</v>
       </c>
       <c r="AF3" s="29">
         <f>SUM($B2:AF2)</f>
-        <v>4</v>
+        <v>4.15443495135491</v>
       </c>
       <c r="AG3" s="29">
         <f>SUM($B2:AG2)</f>
-        <v>4</v>
+        <v>4.15443495135491</v>
       </c>
       <c r="AH3" s="29">
         <f>SUM($B2:AH2)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34">
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AI3" s="29">
+        <f>SUM($B2:AI2)</f>
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AJ3" s="29">
+        <f>SUM($B2:AJ2)</f>
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AK3" s="29">
+        <f>SUM($B2:AK2)</f>
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AL3" s="29">
+        <f>SUM($B2:AL2)</f>
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AM3" s="29">
+        <f>SUM($B2:AM2)</f>
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AN3" s="29">
+        <f>SUM($B2:AN2)</f>
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AO3" s="29">
+        <f>SUM($B2:AO2)</f>
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AP3" s="29">
+        <f>SUM($B2:AP2)</f>
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AQ3" s="29">
+        <f>SUM($B2:AQ2)</f>
+        <v>4.15443495135491</v>
+      </c>
+      <c r="AR3" s="29">
+        <f>SUM($B2:AR2)</f>
+        <v>4.15443495135491</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2057,26 +2157,66 @@
       </c>
       <c r="AD4" s="29">
         <f>AVERAGE($B2:AD2)</f>
-        <v>0.137931034482759</v>
+        <v>0.143256377632928</v>
       </c>
       <c r="AE4" s="29">
         <f>AVERAGE($B2:AE2)</f>
-        <v>0.133333333333333</v>
+        <v>0.138481165045164</v>
       </c>
       <c r="AF4" s="29">
         <f>AVERAGE($B2:AF2)</f>
-        <v>0.129032258064516</v>
+        <v>0.134014030688868</v>
       </c>
       <c r="AG4" s="29">
         <f>AVERAGE($B2:AG2)</f>
-        <v>0.125</v>
+        <v>0.129826092229841</v>
       </c>
       <c r="AH4" s="29">
         <f>AVERAGE($B2:AH2)</f>
-        <v>0.121212121212121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34">
+        <v>0.125891968222876</v>
+      </c>
+      <c r="AI4" s="29">
+        <f>AVERAGE($B2:AI2)</f>
+        <v>0.122189263275144</v>
+      </c>
+      <c r="AJ4" s="29">
+        <f>AVERAGE($B2:AJ2)</f>
+        <v>0.118698141467283</v>
+      </c>
+      <c r="AK4" s="29">
+        <f>AVERAGE($B2:AK2)</f>
+        <v>0.11540097087097</v>
+      </c>
+      <c r="AL4" s="29">
+        <f>AVERAGE($B2:AL2)</f>
+        <v>0.112282025712295</v>
+      </c>
+      <c r="AM4" s="29">
+        <f>AVERAGE($B2:AM2)</f>
+        <v>0.109327235561971</v>
+      </c>
+      <c r="AN4" s="29">
+        <f>AVERAGE($B2:AN2)</f>
+        <v>0.106523973111664</v>
+      </c>
+      <c r="AO4" s="29">
+        <f>AVERAGE($B2:AO2)</f>
+        <v>0.103860873783873</v>
+      </c>
+      <c r="AP4" s="29">
+        <f>AVERAGE($B2:AP2)</f>
+        <v>0.101327681740364</v>
+      </c>
+      <c r="AQ4" s="29">
+        <f>AVERAGE($B2:AQ2)</f>
+        <v>0.0989151178894026</v>
+      </c>
+      <c r="AR4" s="29">
+        <f>AVERAGE($B2:AR2)</f>
+        <v>0.0966147663105793</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -2085,7 +2225,7 @@
         <v>0.153846153846154</v>
       </c>
       <c r="C5" s="29">
-        <f t="shared" ref="C5:AH5" si="0">B5</f>
+        <f t="shared" ref="C5:AR5" si="0">B5</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D5" s="29">
@@ -2212,13 +2352,53 @@
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-    </row>
-    <row r="6" spans="1:34">
+      <c r="AI5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AJ5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AK5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AL5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AM5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AN5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AO5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AP5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AQ5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AR5" s="29">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="29">
-        <f t="shared" ref="B6:AH6" si="1">B5-B2</f>
+        <f t="shared" ref="B6:AR6" si="1">B5-B2</f>
         <v>-0.000521381928996006</v>
       </c>
       <c r="C6" s="29">
@@ -2275,27 +2455,27 @@
       </c>
       <c r="P6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.000215470803705958</v>
+        <v>-0.000215470803706014</v>
       </c>
       <c r="Q6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.000215470803705958</v>
+        <v>-0.000215470803706014</v>
       </c>
       <c r="R6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.000215470803705958</v>
+        <v>-0.000215470803706014</v>
       </c>
       <c r="S6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.000215470803705958</v>
+        <v>-0.000215470803706014</v>
       </c>
       <c r="T6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.000215470803705958</v>
+        <v>-0.000215470803706014</v>
       </c>
       <c r="U6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.000215470803705958</v>
+        <v>-0.000215470803706014</v>
       </c>
       <c r="V6" s="29">
         <f t="shared" si="1"/>
@@ -2331,7 +2511,7 @@
       </c>
       <c r="AD6" s="29">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>-0.000588797508756844</v>
       </c>
       <c r="AE6" s="29">
         <f t="shared" si="1"/>
@@ -2349,13 +2529,54 @@
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-    </row>
-    <row r="8" spans="1:34">
+      <c r="AI6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AJ6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AK6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AL6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AM6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AN6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AO6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AP6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AQ6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AR6" s="29">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+    </row>
+    <row r="7" hidden="1"/>
+    <row r="8" hidden="1" spans="1:44">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" hidden="1" spans="1:44">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2384,7 +2605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" hidden="1" spans="1:44">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -2417,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" hidden="1" spans="1:44">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -2450,12 +2671,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="12" hidden="1"/>
+    <row r="13" hidden="1" spans="1:44">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" hidden="1" spans="1:44">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -2487,7 +2709,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" hidden="1" spans="1:44">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -2525,7 +2747,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" hidden="1" spans="1:44">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
@@ -2563,7 +2785,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" hidden="1" spans="1:10">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -2601,7 +2823,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" hidden="1" spans="1:10">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -2639,7 +2861,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" hidden="1" spans="1:10">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -2677,7 +2899,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" hidden="1" spans="1:10">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -2715,12 +2937,12 @@
         <v>278</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" hidden="1" spans="1:10">
       <c r="C21" s="29"/>
       <c r="E21" s="29"/>
       <c r="F21" s="29"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" hidden="1" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,7 +2950,7 @@
       <c r="E22" s="29"/>
       <c r="F22" s="29"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" hidden="1" spans="1:10">
       <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
@@ -2760,7 +2982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" hidden="1" spans="1:10">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,7 +3020,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" hidden="1" spans="1:10">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -2836,7 +3058,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" hidden="1" spans="1:10">
       <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
@@ -2874,7 +3096,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" hidden="1" spans="1:10">
       <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
@@ -2912,7 +3134,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" hidden="1" spans="1:10">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
@@ -2950,17 +3172,17 @@
         <v>464</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" hidden="1" spans="1:10">
       <c r="C29" s="29"/>
       <c r="E29" s="29"/>
       <c r="F29" s="29"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" hidden="1" spans="1:10">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" hidden="1" spans="1:10">
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
@@ -2992,7 +3214,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" hidden="1" spans="1:10">
       <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
@@ -3030,7 +3252,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" hidden="1" spans="1:10">
       <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
@@ -3068,7 +3290,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" hidden="1" spans="1:10">
       <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
@@ -3106,7 +3328,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" hidden="1" spans="1:10">
       <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
@@ -3254,7 +3476,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="41" hidden="1"/>
+    <row r="42" hidden="1" spans="1:10">
       <c r="A42" s="1" t="s">
         <v>39</v>
       </c>
@@ -3262,7 +3485,7 @@
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" hidden="1" spans="1:10">
       <c r="A43" s="1" t="s">
         <v>7</v>
       </c>
@@ -3294,7 +3517,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" hidden="1" spans="1:10">
       <c r="A44" s="1" t="s">
         <v>40</v>
       </c>
@@ -3371,7 +3594,7 @@
         <v>15</v>
       </c>
       <c r="J47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -3391,22 +3614,25 @@
       </c>
       <c r="E48" s="29">
         <f>AVERAGE(F$48:F48)</f>
-        <v>0.0611854684512428</v>
+        <v>0.152963671128107</v>
       </c>
       <c r="F48" s="29">
         <f t="shared" ref="F48:F54" si="19">G48/B48</f>
-        <v>0.0611854684512428</v>
+        <v>0.152963671128107</v>
       </c>
       <c r="G48" s="1">
         <f t="shared" ref="G48:G54" si="20">I48-H48</f>
-        <v>32</v>
-      </c>
-      <c r="I48" s="33">
+        <v>80</v>
+      </c>
+      <c r="H48" s="1">
+        <v>80</v>
+      </c>
+      <c r="I48" s="31">
         <f t="shared" ref="I48:I54" si="21">MIN($J$47*D48,J48)</f>
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="J48" s="1">
-        <v>32</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -3426,22 +3652,25 @@
       </c>
       <c r="E49" s="29">
         <f>AVERAGE(F$48:F49)</f>
-        <v>0.106629600585068</v>
+        <v>0.104131605149307</v>
       </c>
       <c r="F49" s="29">
         <f t="shared" si="19"/>
-        <v>0.152073732718894</v>
+        <v>0.0552995391705069</v>
       </c>
       <c r="G49" s="1">
         <f t="shared" si="20"/>
-        <v>66</v>
+        <v>24</v>
+      </c>
+      <c r="H49" s="1">
+        <v>67</v>
       </c>
       <c r="I49" s="33">
         <f t="shared" si="21"/>
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="J49" s="1">
-        <v>66</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3462,19 +3691,22 @@
       </c>
       <c r="E50" s="29">
         <f>AVERAGE(F$48:F50)</f>
-        <v>0.123074167974143</v>
+        <v>0.103060213830425</v>
       </c>
       <c r="F50" s="29">
         <f t="shared" si="19"/>
-        <v>0.155963302752294</v>
+        <v>0.100917431192661</v>
       </c>
       <c r="G50" s="1">
         <f t="shared" si="20"/>
+        <v>11</v>
+      </c>
+      <c r="H50" s="1">
         <v>17</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="33">
         <f t="shared" si="21"/>
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J50" s="1">
         <v>28</v>
@@ -3780,7 +4012,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A36:AH39 K40:AH41 I32:I35 A32:G35 K31:AH35 A31:I31 A3:AH30 A2:O2 A1:AH1 A44 A45:AH48 A42:AH42 A43:I43 K43:AH44 C44:G44 I44" formulaRange="1"/>
+    <ignoredError sqref="A45:AH46 A47:I47 K47:AH48 A48:G48 I48 A36:AH39 K40:AH41 I32:I35 A32:G35 K31:AH35 A31:I31 A3:AG6 A7:AH30 A2:O2 A1:AG1 A44 A42:AH42 A43:I43 K43:AH44 C44:G44 I44" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4075,7 +4307,7 @@
         <v>41</v>
       </c>
       <c r="B22" s="1">
-        <v>32</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4083,7 +4315,7 @@
         <v>42</v>
       </c>
       <c r="B23" s="1">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>91</v>

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -1820,7 +1820,7 @@
         <v>0.154434951354911</v>
       </c>
       <c r="AE2" s="29">
-        <v>0</v>
+        <v>0.154434951354911</v>
       </c>
       <c r="AF2" s="29">
         <v>0</v>
@@ -1984,59 +1984,59 @@
       </c>
       <c r="AE3" s="29">
         <f>SUM($B2:AE2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AF3" s="29">
         <f>SUM($B2:AF2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AG3" s="29">
         <f>SUM($B2:AG2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AH3" s="29">
         <f>SUM($B2:AH2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AI3" s="29">
         <f>SUM($B2:AI2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AJ3" s="29">
         <f>SUM($B2:AJ2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AK3" s="29">
         <f>SUM($B2:AK2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AL3" s="29">
         <f>SUM($B2:AL2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AM3" s="29">
         <f>SUM($B2:AM2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AN3" s="29">
         <f>SUM($B2:AN2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AO3" s="29">
         <f>SUM($B2:AO2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AP3" s="29">
         <f>SUM($B2:AP2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AQ3" s="29">
         <f>SUM($B2:AQ2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
       <c r="AR3" s="29">
         <f>SUM($B2:AR2)</f>
-        <v>4.15443495135491</v>
+        <v>4.30886990270982</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -2161,59 +2161,59 @@
       </c>
       <c r="AE4" s="29">
         <f>AVERAGE($B2:AE2)</f>
-        <v>0.138481165045164</v>
+        <v>0.143628996756994</v>
       </c>
       <c r="AF4" s="29">
         <f>AVERAGE($B2:AF2)</f>
-        <v>0.134014030688868</v>
+        <v>0.13899580331322</v>
       </c>
       <c r="AG4" s="29">
         <f>AVERAGE($B2:AG2)</f>
-        <v>0.129826092229841</v>
+        <v>0.134652184459682</v>
       </c>
       <c r="AH4" s="29">
         <f>AVERAGE($B2:AH2)</f>
-        <v>0.125891968222876</v>
+        <v>0.130571815233631</v>
       </c>
       <c r="AI4" s="29">
         <f>AVERAGE($B2:AI2)</f>
-        <v>0.122189263275144</v>
+        <v>0.126731467726759</v>
       </c>
       <c r="AJ4" s="29">
         <f>AVERAGE($B2:AJ2)</f>
-        <v>0.118698141467283</v>
+        <v>0.123110568648852</v>
       </c>
       <c r="AK4" s="29">
         <f>AVERAGE($B2:AK2)</f>
-        <v>0.11540097087097</v>
+        <v>0.119690830630828</v>
       </c>
       <c r="AL4" s="29">
         <f>AVERAGE($B2:AL2)</f>
-        <v>0.112282025712295</v>
+        <v>0.116455943316482</v>
       </c>
       <c r="AM4" s="29">
         <f>AVERAGE($B2:AM2)</f>
-        <v>0.109327235561971</v>
+        <v>0.113391313229206</v>
       </c>
       <c r="AN4" s="29">
         <f>AVERAGE($B2:AN2)</f>
-        <v>0.106523973111664</v>
+        <v>0.110483843659226</v>
       </c>
       <c r="AO4" s="29">
         <f>AVERAGE($B2:AO2)</f>
-        <v>0.103860873783873</v>
+        <v>0.107721747567746</v>
       </c>
       <c r="AP4" s="29">
         <f>AVERAGE($B2:AP2)</f>
-        <v>0.101327681740364</v>
+        <v>0.105094387870971</v>
       </c>
       <c r="AQ4" s="29">
         <f>AVERAGE($B2:AQ2)</f>
-        <v>0.0989151178894026</v>
+        <v>0.10259214054071</v>
       </c>
       <c r="AR4" s="29">
         <f>AVERAGE($B2:AR2)</f>
-        <v>0.0966147663105793</v>
+        <v>0.100206276807205</v>
       </c>
     </row>
     <row r="5" spans="1:44">
@@ -2511,11 +2511,11 @@
       </c>
       <c r="AD6" s="29">
         <f t="shared" si="1"/>
-        <v>-0.000588797508756844</v>
+        <v>-0.000588797508757011</v>
       </c>
       <c r="AE6" s="29">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>-0.000588797508756844</v>
       </c>
       <c r="AF6" s="29">
         <f t="shared" si="1"/>
@@ -3594,7 +3594,7 @@
         <v>15</v>
       </c>
       <c r="J47" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="E48" s="29">
         <f>AVERAGE(F$48:F48)</f>
-        <v>0.152963671128107</v>
+        <v>0.0267686424474187</v>
       </c>
       <c r="F48" s="29">
         <f t="shared" ref="F48:F54" si="19">G48/B48</f>
-        <v>0.152963671128107</v>
+        <v>0.0267686424474187</v>
       </c>
       <c r="G48" s="1">
         <f t="shared" ref="G48:G54" si="20">I48-H48</f>
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="H48" s="1">
-        <v>80</v>
-      </c>
-      <c r="I48" s="31">
+        <v>160</v>
+      </c>
+      <c r="I48" s="33">
         <f t="shared" ref="I48:I54" si="21">MIN($J$47*D48,J48)</f>
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="J48" s="1">
         <v>174</v>
@@ -3652,25 +3652,25 @@
       </c>
       <c r="E49" s="29">
         <f>AVERAGE(F$48:F49)</f>
-        <v>0.104131605149307</v>
+        <v>0.0237529848181794</v>
       </c>
       <c r="F49" s="29">
         <f t="shared" si="19"/>
-        <v>0.0552995391705069</v>
+        <v>0.0207373271889401</v>
       </c>
       <c r="G49" s="1">
         <f t="shared" si="20"/>
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H49" s="1">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="I49" s="33">
         <f t="shared" si="21"/>
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="J49" s="1">
-        <v>91</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -3691,42 +3691,38 @@
       </c>
       <c r="E50" s="29">
         <f>AVERAGE(F$48:F50)</f>
-        <v>0.103060213830425</v>
+        <v>0.040300155016401</v>
       </c>
       <c r="F50" s="29">
         <f t="shared" si="19"/>
-        <v>0.100917431192661</v>
+        <v>0.073394495412844</v>
       </c>
       <c r="G50" s="1">
         <f t="shared" si="20"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H50" s="1">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I50" s="33">
         <f t="shared" si="21"/>
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J50" s="1">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="C51" s="29"/>
-      <c r="D51" s="1"/>
       <c r="E51" s="29"/>
       <c r="F51" s="29"/>
-      <c r="G51" s="1"/>
       <c r="I51" s="33"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B52" s="1"/>
       <c r="C52" s="29"/>
-      <c r="D52" s="1"/>
       <c r="E52" s="29"/>
       <c r="F52" s="29"/>
     </row>
@@ -4012,7 +4008,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A45:AH46 A47:I47 K47:AH48 A48:G48 I48 A36:AH39 K40:AH41 I32:I35 A32:G35 K31:AH35 A31:I31 A3:AG6 A7:AH30 A2:O2 A1:AG1 A44 A42:AH42 A43:I43 K43:AH44 C44:G44 I44" formulaRange="1"/>
+    <ignoredError sqref="I44 C44:G44 K43:AH44 A43:I43 A42:AH42 A44 A1:AG1 A2:O2 A7:AH30 A3:AG6 A31:I31 K31:AH35 A32:G35 I32:I35 K40:AH41 A36:AH39 I48 A48:G48 K47:AH48 A47:I47 A45:AH46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4026,7 +4022,7 @@
     <col min="1" max="16384" width="10.7777777777778" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" hidden="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -4040,7 +4036,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" hidden="1" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -4054,7 +4050,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" hidden="1" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -4068,7 +4064,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" hidden="1" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -4082,7 +4078,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" hidden="1" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -4096,7 +4092,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" hidden="1" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -4110,7 +4106,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" hidden="1" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -4124,7 +4120,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" hidden="1" spans="1:5">
       <c r="D8" s="1" t="s">
         <v>67</v>
       </c>
@@ -4132,7 +4128,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" hidden="1" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -4146,7 +4142,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" hidden="1" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -4160,7 +4156,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" hidden="1" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -4174,7 +4170,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" hidden="1" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -4188,7 +4184,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" hidden="1" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -4202,7 +4198,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" hidden="1" spans="1:5">
       <c r="D14" s="1" t="s">
         <v>79</v>
       </c>
@@ -4210,7 +4206,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" hidden="1" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
@@ -4224,7 +4220,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" hidden="1" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
@@ -4236,7 +4232,7 @@
       </c>
       <c r="E16" s="26"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" hidden="1" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -4247,7 +4243,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" hidden="1" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>85</v>
       </c>
@@ -4255,7 +4251,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" hidden="1" spans="1:8">
       <c r="C19" s="1" t="s">
         <v>86</v>
       </c>
@@ -4275,7 +4271,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" hidden="1" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -4302,6 +4298,7 @@
         <v>14</v>
       </c>
     </row>
+    <row r="21" hidden="1"/>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>41</v>
@@ -4315,7 +4312,7 @@
         <v>42</v>
       </c>
       <c r="B23" s="1">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>91</v>
@@ -4330,13 +4327,13 @@
       </c>
       <c r="B24" s="1">
         <f>C24+D24</f>
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C24" s="1">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D24" s="1">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:8">

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -3691,25 +3691,25 @@
       </c>
       <c r="E50" s="29">
         <f>AVERAGE(F$48:F50)</f>
-        <v>0.040300155016401</v>
+        <v>0.0678230907962175</v>
       </c>
       <c r="F50" s="29">
         <f t="shared" si="19"/>
-        <v>0.073394495412844</v>
+        <v>0.155963302752294</v>
       </c>
       <c r="G50" s="1">
         <f t="shared" si="20"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H50" s="1">
         <v>34</v>
       </c>
       <c r="I50" s="33">
         <f t="shared" si="21"/>
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J50" s="1">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -4008,7 +4008,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="I44 C44:G44 K43:AH44 A43:I43 A42:AH42 A44 A1:AG1 A2:O2 A7:AH30 A3:AG6 A31:I31 K31:AH35 A32:G35 I32:I35 K40:AH41 A36:AH39 I48 A48:G48 K47:AH48 A47:I47 A45:AH46" formulaRange="1"/>
+    <ignoredError sqref="A45:AH46 A47:I47 K47:AH48 A48:G48 I48 A36:AH39 K40:AH41 I32:I35 A32:G35 K31:AH35 A31:I31 A3:AG6 A7:AH30 A2:O2 A1:AG1 A44 A42:AH42 A43:I43 K43:AH44 C44:G44 I44" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4327,13 +4327,13 @@
       </c>
       <c r="B24" s="1">
         <f>C24+D24</f>
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C24" s="1">
         <v>17</v>
       </c>
       <c r="D24" s="1">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:8">

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -10,6 +10,7 @@
     <sheet name="进度" sheetId="1" r:id="rId1"/>
     <sheet name="书签" sheetId="2" r:id="rId2"/>
     <sheet name="虚拟" sheetId="3" r:id="rId3"/>
+    <sheet name="面容" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="209">
   <si>
     <t>日期</t>
   </si>
@@ -142,10 +143,10 @@
     <t>网络安全</t>
   </si>
   <si>
-    <t>华为认证</t>
-  </si>
-  <si>
-    <t>通信原理</t>
+    <t>网络通信</t>
+  </si>
+  <si>
+    <t>导师研究</t>
   </si>
   <si>
     <t>复试针对</t>
@@ -178,13 +179,13 @@
     <t>高级密码</t>
   </si>
   <si>
-    <t>数据科学</t>
-  </si>
-  <si>
-    <t>边缘智能</t>
-  </si>
-  <si>
-    <t>软件系统</t>
+    <t>深度学习</t>
+  </si>
+  <si>
+    <t>机器学习</t>
+  </si>
+  <si>
+    <t>语言处理</t>
   </si>
   <si>
     <t>页码</t>
@@ -304,12 +305,84 @@
     <t>3-8</t>
   </si>
   <si>
+    <t>姜也</t>
+  </si>
+  <si>
+    <t>刘勇</t>
+  </si>
+  <si>
+    <t>周艳平</t>
+  </si>
+  <si>
+    <t>陈双敏</t>
+  </si>
+  <si>
     <t>信号</t>
   </si>
   <si>
     <t>控制</t>
   </si>
   <si>
+    <t>论文1</t>
+  </si>
+  <si>
+    <t>AMPLE_Emotion-Aware_Multimodal_Fusion_Prompt_Learn</t>
+  </si>
+  <si>
+    <t>DMFI-YOLO_dynamic_multi-scale_feature_interaction_</t>
+  </si>
+  <si>
+    <t>融合字词增强语义多注意力的医疗自动问答</t>
+  </si>
+  <si>
+    <t>论文2</t>
+  </si>
+  <si>
+    <t>Instruction_Tuning_Vs_In-Context_Learning_Revisiti</t>
+  </si>
+  <si>
+    <t>DSE-FCOS_dilated_and_SE_block-reinforced_FCOS_for_</t>
+  </si>
+  <si>
+    <t>基于强化学习的多策略HHO求解分布式混合流水车间调度</t>
+  </si>
+  <si>
+    <t>网络</t>
+  </si>
+  <si>
+    <t>通信</t>
+  </si>
+  <si>
+    <t>论文3</t>
+  </si>
+  <si>
+    <t>Learn_to_Select_Exploring_Label_Distribution_Diver</t>
+  </si>
+  <si>
+    <t>ERS_Enhancing_representation_supervision_for_contr</t>
+  </si>
+  <si>
+    <t>基于改进人工蜂群算法的混合约束流水车间调度</t>
+  </si>
+  <si>
+    <t>论文4</t>
+  </si>
+  <si>
+    <t>QUST_NLP_at_SemEval-2025_Task_7_A_Three-Stage_Retr</t>
+  </si>
+  <si>
+    <t>Optimizing_feature_map_matching_for_marine_benthic</t>
+  </si>
+  <si>
+    <t>论文5</t>
+  </si>
+  <si>
+    <t>Team_QUST_at_SemEval-2025_Task_10_Evaluating_Large</t>
+  </si>
+  <si>
+    <t>Semi-supervised_medical_image_segmentation_with_di</t>
+  </si>
+  <si>
     <t>正常电脑</t>
   </si>
   <si>
@@ -392,6 +465,198 @@
   </si>
   <si>
     <t>用户程序（虚拟内核）</t>
+  </si>
+  <si>
+    <t>分级</t>
+  </si>
+  <si>
+    <t>英文描述</t>
+  </si>
+  <si>
+    <t>中文释义</t>
+  </si>
+  <si>
+    <t>Class 0</t>
+  </si>
+  <si>
+    <t>Any part of the epiglottis is visible</t>
+  </si>
+  <si>
+    <t>可见部分会厌</t>
+  </si>
+  <si>
+    <t>Class I</t>
+  </si>
+  <si>
+    <t>Soft palate, uvula, and pillars are visible</t>
+  </si>
+  <si>
+    <t>可见软腭、悬雍垂、腭咽弓</t>
+  </si>
+  <si>
+    <t>Class II</t>
+  </si>
+  <si>
+    <t>Soft palate and uvula are visible</t>
+  </si>
+  <si>
+    <t>可见软腭、悬雍垂</t>
+  </si>
+  <si>
+    <t>Class III</t>
+  </si>
+  <si>
+    <t>Only the soft palate and base of the uvula are visible</t>
+  </si>
+  <si>
+    <t>仅可见软腭、悬雍垂根部</t>
+  </si>
+  <si>
+    <t>Class IV</t>
+  </si>
+  <si>
+    <t>Only the hard palate is visible</t>
+  </si>
+  <si>
+    <t>仅可见硬腭</t>
+  </si>
+  <si>
+    <t>检测指标</t>
+  </si>
+  <si>
+    <t>分组</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>Mean±SD</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>P 值</t>
+  </si>
+  <si>
+    <t>腭宽度 Palatal width</t>
+  </si>
+  <si>
+    <t>对照组 Control</t>
+  </si>
+  <si>
+    <t>35.5160±2.87078</t>
+  </si>
+  <si>
+    <t>0.003*</t>
+  </si>
+  <si>
+    <t>习惯性口呼吸 Habitual mouth breathers</t>
+  </si>
+  <si>
+    <t>35.9680±2.18836</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>阻塞性口呼吸 Obstructive mouth breathers</t>
+  </si>
+  <si>
+    <t>33.2560±3.42419</t>
+  </si>
+  <si>
+    <t>总计 Total</t>
+  </si>
+  <si>
+    <t>34.9133±3.07493</t>
+  </si>
+  <si>
+    <t>腭高度 Palatal height</t>
+  </si>
+  <si>
+    <t>13.2760±2.18466</t>
+  </si>
+  <si>
+    <t>13.6560±1.62200</t>
+  </si>
+  <si>
+    <t>14.1480±1.86416</t>
+  </si>
+  <si>
+    <t>13.6933±1.91243</t>
+  </si>
+  <si>
+    <t>Palatal index（腭指数）</t>
+  </si>
+  <si>
+    <t>Control（对照组）</t>
+  </si>
+  <si>
+    <t>37.5508±6.26327</t>
+  </si>
+  <si>
+    <t>0.0003*</t>
+  </si>
+  <si>
+    <t>Habitual mouth breathers（习惯性口呼吸）</t>
+  </si>
+  <si>
+    <t>38.0384±4.55434</t>
+  </si>
+  <si>
+    <t>Obstructive mouth breathers（阻塞性口呼吸）</t>
+  </si>
+  <si>
+    <t>42.8592±6.33936</t>
+  </si>
+  <si>
+    <t>Total（总计）</t>
+  </si>
+  <si>
+    <t>39.4828±6.18877</t>
+  </si>
+  <si>
+    <t>因变量 Dependent variable</t>
+  </si>
+  <si>
+    <t>I 分组</t>
+  </si>
+  <si>
+    <t>J 分组</t>
+  </si>
+  <si>
+    <t>均值差 Mean difference (I-J)</t>
+  </si>
+  <si>
+    <t>SE（标准误）</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Habitual mouth breathers</t>
+  </si>
+  <si>
+    <t>Obstructive mouth breathers</t>
+  </si>
+  <si>
+    <t>0.002*</t>
+  </si>
+  <si>
+    <t>0.004*</t>
+  </si>
+  <si>
+    <t>Palatal width（腭宽度）</t>
+  </si>
+  <si>
+    <t>0.007*</t>
+  </si>
+  <si>
+    <t>0.001*</t>
   </si>
 </sst>
 </file>
@@ -404,7 +669,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,7 +678,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -428,7 +695,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -578,12 +859,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -778,12 +1065,64 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1044,155 +1383,158 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="17">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="16">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="20">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="18">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="21">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="20">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="22">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1202,79 +1544,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1591,2415 +1954,2425 @@
   <dimension ref="A1:AR60"/>
   <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16384" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="1" max="10" width="15.7777777777778" style="6" customWidth="1"/>
+    <col min="11" max="36" width="15.7777777777778" style="6" hidden="1" customWidth="1"/>
+    <col min="37" max="16384" width="15.7777777777778" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28">
+      <c r="B1" s="35">
         <v>46081</v>
       </c>
-      <c r="C1" s="28">
+      <c r="C1" s="35">
         <v>46082</v>
       </c>
-      <c r="D1" s="28">
+      <c r="D1" s="35">
         <v>46083</v>
       </c>
-      <c r="E1" s="28">
+      <c r="E1" s="35">
         <v>46084</v>
       </c>
-      <c r="F1" s="28">
+      <c r="F1" s="35">
         <v>46085</v>
       </c>
-      <c r="G1" s="28">
+      <c r="G1" s="35">
         <v>46086</v>
       </c>
-      <c r="H1" s="28">
+      <c r="H1" s="35">
         <v>46087</v>
       </c>
-      <c r="I1" s="28">
+      <c r="I1" s="35">
         <v>46088</v>
       </c>
-      <c r="J1" s="28">
+      <c r="J1" s="35">
         <v>46089</v>
       </c>
-      <c r="K1" s="28">
+      <c r="K1" s="35">
         <v>46090</v>
       </c>
-      <c r="L1" s="28">
+      <c r="L1" s="35">
         <v>46091</v>
       </c>
-      <c r="M1" s="28">
+      <c r="M1" s="35">
         <v>46092</v>
       </c>
-      <c r="N1" s="28">
+      <c r="N1" s="35">
         <v>46093</v>
       </c>
-      <c r="O1" s="28">
+      <c r="O1" s="35">
         <v>46094</v>
       </c>
-      <c r="P1" s="28">
+      <c r="P1" s="35">
         <v>46095</v>
       </c>
-      <c r="Q1" s="28">
+      <c r="Q1" s="35">
         <v>46096</v>
       </c>
-      <c r="R1" s="28">
+      <c r="R1" s="35">
         <v>46097</v>
       </c>
-      <c r="S1" s="28">
+      <c r="S1" s="35">
         <v>46098</v>
       </c>
-      <c r="T1" s="28">
+      <c r="T1" s="35">
         <v>46099</v>
       </c>
-      <c r="U1" s="28">
+      <c r="U1" s="35">
         <v>46100</v>
       </c>
-      <c r="V1" s="28">
+      <c r="V1" s="35">
         <v>46101</v>
       </c>
-      <c r="W1" s="28">
+      <c r="W1" s="35">
         <v>46102</v>
       </c>
-      <c r="X1" s="28">
+      <c r="X1" s="35">
         <v>46103</v>
       </c>
-      <c r="Y1" s="28">
+      <c r="Y1" s="35">
         <v>46104</v>
       </c>
-      <c r="Z1" s="28">
+      <c r="Z1" s="35">
         <v>46105</v>
       </c>
-      <c r="AA1" s="28">
+      <c r="AA1" s="35">
         <v>46106</v>
       </c>
-      <c r="AB1" s="28">
+      <c r="AB1" s="35">
         <v>46107</v>
       </c>
-      <c r="AC1" s="28">
+      <c r="AC1" s="35">
         <v>46108</v>
       </c>
-      <c r="AD1" s="28">
+      <c r="AD1" s="35">
         <v>46109</v>
       </c>
-      <c r="AE1" s="28">
+      <c r="AE1" s="35">
         <v>46110</v>
       </c>
-      <c r="AF1" s="28">
+      <c r="AF1" s="35">
         <v>46111</v>
       </c>
-      <c r="AG1" s="28">
+      <c r="AG1" s="35">
         <v>46112</v>
       </c>
-      <c r="AH1" s="28">
+      <c r="AH1" s="35">
         <v>46113</v>
       </c>
-      <c r="AI1" s="28">
+      <c r="AI1" s="35">
         <v>46114</v>
       </c>
-      <c r="AJ1" s="28">
+      <c r="AJ1" s="35">
         <v>46115</v>
       </c>
-      <c r="AK1" s="28">
+      <c r="AK1" s="35">
         <v>46116</v>
       </c>
-      <c r="AL1" s="28">
+      <c r="AL1" s="35">
         <v>46117</v>
       </c>
-      <c r="AM1" s="28">
+      <c r="AM1" s="35">
         <v>46118</v>
       </c>
-      <c r="AN1" s="28">
+      <c r="AN1" s="35">
         <v>46119</v>
       </c>
-      <c r="AO1" s="28">
+      <c r="AO1" s="35">
         <v>46120</v>
       </c>
-      <c r="AP1" s="28">
+      <c r="AP1" s="35">
         <v>46121</v>
       </c>
-      <c r="AQ1" s="28">
+      <c r="AQ1" s="35">
         <v>46122</v>
       </c>
-      <c r="AR1" s="28">
+      <c r="AR1" s="35">
         <v>46123</v>
       </c>
     </row>
     <row r="2" spans="1:44">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="36">
         <v>0.15436753577515</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="36">
         <v>0.15436753577515</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="36">
         <v>0.15436753577515</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="36">
         <v>0.15436753577515</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="36">
         <v>0.15436753577515</v>
       </c>
-      <c r="G2" s="30">
+      <c r="G2" s="37">
         <v>0.15436753577515</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="36">
         <v>0.073794785349101</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="37">
         <v>0.155080443958291</v>
       </c>
-      <c r="J2" s="30">
+      <c r="J2" s="37">
         <v>0.155080443958291</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="36">
         <v>0.155080443958291</v>
       </c>
-      <c r="L2" s="29">
+      <c r="L2" s="36">
         <v>0.155080443958291</v>
       </c>
-      <c r="M2" s="29">
+      <c r="M2" s="36">
         <v>0.155080443958291</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="36">
         <v>0.155080443958291</v>
       </c>
-      <c r="O2" s="29">
+      <c r="O2" s="36">
         <v>0.0695173362502559</v>
       </c>
-      <c r="P2" s="30">
+      <c r="P2" s="37">
         <v>0.15406162464986</v>
       </c>
-      <c r="Q2" s="29">
+      <c r="Q2" s="36">
         <v>0.15406162464986</v>
       </c>
-      <c r="R2" s="29">
+      <c r="R2" s="36">
         <v>0.15406162464986</v>
       </c>
-      <c r="S2" s="29">
+      <c r="S2" s="36">
         <v>0.15406162464986</v>
       </c>
-      <c r="T2" s="29">
+      <c r="T2" s="36">
         <v>0.15406162464986</v>
       </c>
-      <c r="U2" s="29">
+      <c r="U2" s="36">
         <v>0.15406162464986</v>
       </c>
-      <c r="V2" s="29">
+      <c r="V2" s="36">
         <v>0.0756302521008403</v>
       </c>
-      <c r="W2" s="29">
+      <c r="W2" s="36">
         <v>0.156031837360951</v>
       </c>
-      <c r="X2" s="29">
+      <c r="X2" s="36">
         <v>0.156031837360951</v>
       </c>
-      <c r="Y2" s="29">
+      <c r="Y2" s="36">
         <v>0.156031837360951</v>
       </c>
-      <c r="Z2" s="29">
+      <c r="Z2" s="36">
         <v>0.156031837360951</v>
       </c>
-      <c r="AA2" s="29">
+      <c r="AA2" s="36">
         <v>0.156031837360951</v>
       </c>
-      <c r="AB2" s="29">
+      <c r="AB2" s="36">
         <v>0.156031837360951</v>
       </c>
-      <c r="AC2" s="29">
+      <c r="AC2" s="36">
         <v>0.0638089758342923</v>
       </c>
-      <c r="AD2" s="29">
+      <c r="AD2" s="36">
         <v>0.154434951354911</v>
       </c>
-      <c r="AE2" s="29">
+      <c r="AE2" s="36">
         <v>0.154434951354911</v>
       </c>
-      <c r="AF2" s="29">
+      <c r="AF2" s="36">
+        <v>0.154434951354911</v>
+      </c>
+      <c r="AG2" s="36">
+        <v>0.154434951354911</v>
+      </c>
+      <c r="AH2" s="36">
+        <v>0.154434951354911</v>
+      </c>
+      <c r="AI2" s="36">
+        <v>0.154434951354911</v>
+      </c>
+      <c r="AJ2" s="36">
+        <v>0.0733902918705351</v>
+      </c>
+      <c r="AK2" s="36">
+        <v>0.151612903225806</v>
+      </c>
+      <c r="AL2" s="36">
         <v>0</v>
       </c>
-      <c r="AG2" s="29">
+      <c r="AM2" s="36">
         <v>0</v>
       </c>
-      <c r="AH2" s="29">
+      <c r="AN2" s="36">
         <v>0</v>
       </c>
-      <c r="AI2" s="29">
+      <c r="AO2" s="36">
         <v>0</v>
       </c>
-      <c r="AJ2" s="29">
+      <c r="AP2" s="36">
         <v>0</v>
       </c>
-      <c r="AK2" s="29">
+      <c r="AQ2" s="36">
         <v>0</v>
       </c>
-      <c r="AL2" s="29">
+      <c r="AR2" s="36">
         <v>0</v>
       </c>
-      <c r="AM2" s="29">
-        <v>0</v>
-      </c>
-      <c r="AN2" s="29">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="29">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="29">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="29">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="29">
-        <v>0</v>
-      </c>
     </row>
     <row r="3" spans="1:44">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="36">
         <f>SUM($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="36">
         <f>SUM($B2:C2)</f>
         <v>0.3087350715503</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="36">
         <f>SUM($B2:D2)</f>
         <v>0.463102607325449</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="36">
         <f>SUM($B2:E2)</f>
         <v>0.617470143100599</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="36">
         <f>SUM($B2:F2)</f>
         <v>0.771837678875749</v>
       </c>
-      <c r="G3" s="29">
+      <c r="G3" s="36">
         <f>SUM($B2:G2)</f>
         <v>0.926205214650899</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="36">
         <f>SUM($B2:H2)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="36">
         <f>SUM($B2:I2)</f>
         <v>1.15508044395829</v>
       </c>
-      <c r="J3" s="29">
+      <c r="J3" s="36">
         <f>SUM($B2:J2)</f>
         <v>1.31016088791658</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="36">
         <f>SUM($B2:K2)</f>
         <v>1.46524133187487</v>
       </c>
-      <c r="L3" s="29">
+      <c r="L3" s="36">
         <f>SUM($B2:L2)</f>
         <v>1.62032177583316</v>
       </c>
-      <c r="M3" s="29">
+      <c r="M3" s="36">
         <f>SUM($B2:M2)</f>
         <v>1.77540221979145</v>
       </c>
-      <c r="N3" s="29">
+      <c r="N3" s="36">
         <f>SUM($B2:N2)</f>
         <v>1.93048266374974</v>
       </c>
-      <c r="O3" s="29">
+      <c r="O3" s="36">
         <f>SUM($B2:O2)</f>
         <v>2</v>
       </c>
-      <c r="P3" s="29">
+      <c r="P3" s="36">
         <f>SUM($B2:P2)</f>
         <v>2.15406162464986</v>
       </c>
-      <c r="Q3" s="29">
+      <c r="Q3" s="36">
         <f>SUM($B2:Q2)</f>
         <v>2.30812324929972</v>
       </c>
-      <c r="R3" s="29">
+      <c r="R3" s="36">
         <f>SUM($B2:R2)</f>
         <v>2.46218487394958</v>
       </c>
-      <c r="S3" s="29">
+      <c r="S3" s="36">
         <f>SUM($B2:S2)</f>
         <v>2.61624649859944</v>
       </c>
-      <c r="T3" s="29">
+      <c r="T3" s="36">
         <f>SUM($B2:T2)</f>
         <v>2.7703081232493</v>
       </c>
-      <c r="U3" s="29">
+      <c r="U3" s="36">
         <f>SUM($B2:U2)</f>
         <v>2.92436974789916</v>
       </c>
-      <c r="V3" s="29">
+      <c r="V3" s="36">
         <f>SUM($B2:V2)</f>
         <v>3</v>
       </c>
-      <c r="W3" s="29">
+      <c r="W3" s="36">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208285</v>
       </c>
-      <c r="X3" s="29">
+      <c r="X3" s="36">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208285</v>
       </c>
-      <c r="Y3" s="29">
+      <c r="Y3" s="36">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208285</v>
       </c>
-      <c r="Z3" s="29">
+      <c r="Z3" s="36">
         <f>SUM($B2:Z2)</f>
         <v>3.6241273494438</v>
       </c>
-      <c r="AA3" s="29">
+      <c r="AA3" s="36">
         <f>SUM($B2:AA2)</f>
         <v>3.78015918680476</v>
       </c>
-      <c r="AB3" s="29">
+      <c r="AB3" s="36">
         <f>SUM($B2:AB2)</f>
         <v>3.93619102416571</v>
       </c>
-      <c r="AC3" s="29">
+      <c r="AC3" s="36">
         <f>SUM($B2:AC2)</f>
         <v>4</v>
       </c>
-      <c r="AD3" s="29">
+      <c r="AD3" s="36">
         <f>SUM($B2:AD2)</f>
         <v>4.15443495135491</v>
       </c>
-      <c r="AE3" s="29">
+      <c r="AE3" s="36">
         <f>SUM($B2:AE2)</f>
         <v>4.30886990270982</v>
       </c>
-      <c r="AF3" s="29">
+      <c r="AF3" s="36">
         <f>SUM($B2:AF2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AG3" s="29">
+        <v>4.46330485406473</v>
+      </c>
+      <c r="AG3" s="36">
         <f>SUM($B2:AG2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AH3" s="29">
+        <v>4.61773980541964</v>
+      </c>
+      <c r="AH3" s="36">
         <f>SUM($B2:AH2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AI3" s="29">
+        <v>4.77217475677455</v>
+      </c>
+      <c r="AI3" s="36">
         <f>SUM($B2:AI2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AJ3" s="29">
+        <v>4.92660970812946</v>
+      </c>
+      <c r="AJ3" s="36">
         <f>SUM($B2:AJ2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AK3" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK3" s="36">
         <f>SUM($B2:AK2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AL3" s="29">
+        <v>5.1516129032258</v>
+      </c>
+      <c r="AL3" s="36">
         <f>SUM($B2:AL2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AM3" s="29">
+        <v>5.1516129032258</v>
+      </c>
+      <c r="AM3" s="36">
         <f>SUM($B2:AM2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AN3" s="29">
+        <v>5.1516129032258</v>
+      </c>
+      <c r="AN3" s="36">
         <f>SUM($B2:AN2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AO3" s="29">
+        <v>5.1516129032258</v>
+      </c>
+      <c r="AO3" s="36">
         <f>SUM($B2:AO2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AP3" s="29">
+        <v>5.1516129032258</v>
+      </c>
+      <c r="AP3" s="36">
         <f>SUM($B2:AP2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AQ3" s="29">
+        <v>5.1516129032258</v>
+      </c>
+      <c r="AQ3" s="36">
         <f>SUM($B2:AQ2)</f>
-        <v>4.30886990270982</v>
-      </c>
-      <c r="AR3" s="29">
+        <v>5.1516129032258</v>
+      </c>
+      <c r="AR3" s="36">
         <f>SUM($B2:AR2)</f>
-        <v>4.30886990270982</v>
+        <v>5.1516129032258</v>
       </c>
     </row>
     <row r="4" spans="1:44">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="36">
         <f>AVERAGE($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="36">
         <f>AVERAGE($B2:C2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="36">
         <f>AVERAGE($B2:D2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="36">
         <f>AVERAGE($B2:E2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="36">
         <f>AVERAGE($B2:F2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="36">
         <f>AVERAGE($B2:G2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="36">
         <f>AVERAGE($B2:H2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="36">
         <f>AVERAGE($B2:I2)</f>
         <v>0.144385055494786</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="36">
         <f>AVERAGE($B2:J2)</f>
         <v>0.145573431990731</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="36">
         <f>AVERAGE($B2:K2)</f>
         <v>0.146524133187487</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="36">
         <f>AVERAGE($B2:L2)</f>
         <v>0.147301979621197</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="36">
         <f>AVERAGE($B2:M2)</f>
         <v>0.147950184982621</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="36">
         <f>AVERAGE($B2:N2)</f>
         <v>0.148498666442288</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="36">
         <f>AVERAGE($B2:O2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="36">
         <f>AVERAGE($B2:P2)</f>
         <v>0.143604108309991</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="36">
         <f>AVERAGE($B2:Q2)</f>
         <v>0.144257703081233</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="36">
         <f>AVERAGE($B2:R2)</f>
         <v>0.144834404349975</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="36">
         <f>AVERAGE($B2:S2)</f>
         <v>0.145347027699969</v>
       </c>
-      <c r="T4" s="29">
+      <c r="T4" s="36">
         <f>AVERAGE($B2:T2)</f>
         <v>0.145805690697332</v>
       </c>
-      <c r="U4" s="29">
+      <c r="U4" s="36">
         <f>AVERAGE($B2:U2)</f>
         <v>0.146218487394958</v>
       </c>
-      <c r="V4" s="29">
+      <c r="V4" s="36">
         <f>AVERAGE($B2:V2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="W4" s="29">
+      <c r="W4" s="36">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="X4" s="29">
+      <c r="X4" s="36">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="Y4" s="29">
+      <c r="Y4" s="36">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="Z4" s="29">
+      <c r="Z4" s="36">
         <f>AVERAGE($B2:Z2)</f>
         <v>0.144965093977752</v>
       </c>
-      <c r="AA4" s="29">
+      <c r="AA4" s="36">
         <f>AVERAGE($B2:AA2)</f>
         <v>0.145390737954029</v>
       </c>
-      <c r="AB4" s="29">
+      <c r="AB4" s="36">
         <f>AVERAGE($B2:AB2)</f>
         <v>0.145784852746878</v>
       </c>
-      <c r="AC4" s="29">
+      <c r="AC4" s="36">
         <f>AVERAGE($B2:AC2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="AD4" s="29">
+      <c r="AD4" s="36">
         <f>AVERAGE($B2:AD2)</f>
         <v>0.143256377632928</v>
       </c>
-      <c r="AE4" s="29">
+      <c r="AE4" s="36">
         <f>AVERAGE($B2:AE2)</f>
         <v>0.143628996756994</v>
       </c>
-      <c r="AF4" s="29">
+      <c r="AF4" s="36">
         <f>AVERAGE($B2:AF2)</f>
-        <v>0.13899580331322</v>
-      </c>
-      <c r="AG4" s="29">
+        <v>0.143977575937572</v>
+      </c>
+      <c r="AG4" s="36">
         <f>AVERAGE($B2:AG2)</f>
-        <v>0.134652184459682</v>
-      </c>
-      <c r="AH4" s="29">
+        <v>0.144304368919364</v>
+      </c>
+      <c r="AH4" s="36">
         <f>AVERAGE($B2:AH2)</f>
-        <v>0.130571815233631</v>
-      </c>
-      <c r="AI4" s="29">
+        <v>0.144611356265896</v>
+      </c>
+      <c r="AI4" s="36">
         <f>AVERAGE($B2:AI2)</f>
-        <v>0.126731467726759</v>
-      </c>
-      <c r="AJ4" s="29">
+        <v>0.144900285533219</v>
+      </c>
+      <c r="AJ4" s="36">
         <f>AVERAGE($B2:AJ2)</f>
-        <v>0.123110568648852</v>
-      </c>
-      <c r="AK4" s="29">
+        <v>0.142857142857143</v>
+      </c>
+      <c r="AK4" s="36">
         <f>AVERAGE($B2:AK2)</f>
-        <v>0.119690830630828</v>
-      </c>
-      <c r="AL4" s="29">
+        <v>0.143100358422939</v>
+      </c>
+      <c r="AL4" s="36">
         <f>AVERAGE($B2:AL2)</f>
-        <v>0.116455943316482</v>
-      </c>
-      <c r="AM4" s="29">
+        <v>0.139232781168265</v>
+      </c>
+      <c r="AM4" s="36">
         <f>AVERAGE($B2:AM2)</f>
-        <v>0.113391313229206</v>
-      </c>
-      <c r="AN4" s="29">
+        <v>0.135568760611205</v>
+      </c>
+      <c r="AN4" s="36">
         <f>AVERAGE($B2:AN2)</f>
-        <v>0.110483843659226</v>
-      </c>
-      <c r="AO4" s="29">
+        <v>0.132092638544251</v>
+      </c>
+      <c r="AO4" s="36">
         <f>AVERAGE($B2:AO2)</f>
-        <v>0.107721747567746</v>
-      </c>
-      <c r="AP4" s="29">
+        <v>0.128790322580645</v>
+      </c>
+      <c r="AP4" s="36">
         <f>AVERAGE($B2:AP2)</f>
-        <v>0.105094387870971</v>
-      </c>
-      <c r="AQ4" s="29">
+        <v>0.125649095200629</v>
+      </c>
+      <c r="AQ4" s="36">
         <f>AVERAGE($B2:AQ2)</f>
-        <v>0.10259214054071</v>
-      </c>
-      <c r="AR4" s="29">
+        <v>0.122657450076805</v>
+      </c>
+      <c r="AR4" s="36">
         <f>AVERAGE($B2:AR2)</f>
-        <v>0.100206276807205</v>
+        <v>0.119804951237809</v>
       </c>
     </row>
     <row r="5" spans="1:44">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="36">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="36">
         <f t="shared" ref="C5:AR5" si="0">B5</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="J5" s="29">
+      <c r="J5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="K5" s="29">
+      <c r="K5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="L5" s="29">
+      <c r="L5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="N5" s="29">
+      <c r="N5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="P5" s="29">
+      <c r="P5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="R5" s="29">
+      <c r="R5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="S5" s="29">
+      <c r="S5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="T5" s="29">
+      <c r="T5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="V5" s="29">
+      <c r="V5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="W5" s="29">
+      <c r="W5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Z5" s="29">
+      <c r="Z5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AA5" s="29">
+      <c r="AA5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AB5" s="29">
+      <c r="AB5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AC5" s="29">
+      <c r="AC5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AD5" s="29">
+      <c r="AD5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AE5" s="29">
+      <c r="AE5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AF5" s="29">
+      <c r="AF5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AG5" s="29">
+      <c r="AG5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AH5" s="29">
+      <c r="AH5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AI5" s="29">
+      <c r="AI5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AJ5" s="29">
+      <c r="AJ5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AK5" s="29">
+      <c r="AK5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AL5" s="29">
+      <c r="AL5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AM5" s="29">
+      <c r="AM5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AN5" s="29">
+      <c r="AN5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AO5" s="29">
+      <c r="AO5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AP5" s="29">
+      <c r="AP5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AQ5" s="29">
+      <c r="AQ5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AR5" s="29">
+      <c r="AR5" s="36">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
     </row>
     <row r="6" spans="1:44">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="36">
         <f t="shared" ref="B6:AR6" si="1">B5-B2</f>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="36">
         <f t="shared" si="1"/>
         <v>0.080051368497053</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="36">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="J6" s="29">
+      <c r="J6" s="36">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="K6" s="29">
+      <c r="K6" s="36">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="L6" s="29">
+      <c r="L6" s="36">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="M6" s="29">
+      <c r="M6" s="36">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="N6" s="29">
+      <c r="N6" s="36">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="36">
         <f t="shared" si="1"/>
         <v>0.0843288175958981</v>
       </c>
-      <c r="P6" s="29">
+      <c r="P6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="R6" s="29">
+      <c r="R6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="S6" s="29">
+      <c r="S6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="T6" s="29">
+      <c r="T6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="V6" s="29">
+      <c r="V6" s="36">
         <f t="shared" si="1"/>
         <v>0.0782159017453137</v>
       </c>
-      <c r="W6" s="29">
+      <c r="W6" s="36">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="X6" s="29">
+      <c r="X6" s="36">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="36">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="Z6" s="29">
+      <c r="Z6" s="36">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="AA6" s="29">
+      <c r="AA6" s="36">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="AB6" s="29">
+      <c r="AB6" s="36">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="36">
         <f t="shared" si="1"/>
         <v>0.0900371780118617</v>
       </c>
-      <c r="AD6" s="29">
+      <c r="AD6" s="36">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AE6" s="29">
+      <c r="AE6" s="36">
         <f t="shared" si="1"/>
-        <v>-0.000588797508756844</v>
-      </c>
-      <c r="AF6" s="29">
+        <v>-0.000588797508757011</v>
+      </c>
+      <c r="AF6" s="36">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AG6" s="29">
+        <v>-0.000588797508757011</v>
+      </c>
+      <c r="AG6" s="36">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AH6" s="29">
+        <v>-0.000588797508757011</v>
+      </c>
+      <c r="AH6" s="36">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AI6" s="29">
+        <v>-0.000588797508757011</v>
+      </c>
+      <c r="AI6" s="36">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AJ6" s="29">
+        <v>-0.000588797508757011</v>
+      </c>
+      <c r="AJ6" s="36">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AK6" s="29">
+        <v>0.0804558619756189</v>
+      </c>
+      <c r="AK6" s="36">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AL6" s="29">
+        <v>0.00223325062034754</v>
+      </c>
+      <c r="AL6" s="36">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AM6" s="29">
+      <c r="AM6" s="36">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AN6" s="29">
+      <c r="AN6" s="36">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AO6" s="29">
+      <c r="AO6" s="36">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AP6" s="29">
+      <c r="AP6" s="36">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AQ6" s="29">
+      <c r="AQ6" s="36">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AR6" s="29">
+      <c r="AR6" s="36">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
     </row>
     <row r="7" hidden="1"/>
     <row r="8" hidden="1" spans="1:44">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" hidden="1" spans="1:44">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" hidden="1" spans="1:44">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="36">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="6">
         <v>50</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="36">
         <f>AVERAGE(F$10:F10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="36">
         <f t="shared" ref="F10:F20" si="2">G10/B10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="6">
         <f t="shared" ref="G10:G20" si="3">I10-H10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="6">
         <v>0</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="11" hidden="1" spans="1:44">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="6">
         <v>50</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="36">
         <f>C10</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="6">
         <v>25</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="36">
         <f>AVERAGE(F$10:F11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="6">
         <v>0</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="12" hidden="1"/>
     <row r="13" hidden="1" spans="1:44">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" hidden="1" spans="1:44">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="15" hidden="1" spans="1:44">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="6">
         <v>257</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="36">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="6">
         <f t="shared" ref="D10:D20" si="4">ROUND(B15*C15,0)</f>
         <v>40</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="36">
         <f>AVERAGE(F$15:F15)</f>
         <v>0.066147859922179</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="36">
         <f t="shared" si="2"/>
         <v>0.066147859922179</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="6">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="6">
         <v>240</v>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="38">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="6">
         <v>257</v>
       </c>
     </row>
     <row r="16" hidden="1" spans="1:44">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="6">
         <v>390</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="36">
         <f t="shared" ref="C16:C20" si="6">C15</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="6">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="36">
         <f>AVERAGE(F$15:F16)</f>
         <v>0.071535468422628</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="36">
         <f t="shared" si="2"/>
         <v>0.0769230769230769</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="6">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="6">
         <v>360</v>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="38">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="6">
         <v>390</v>
       </c>
     </row>
     <row r="17" hidden="1" spans="1:10">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="6">
         <v>484</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="36">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="6">
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="36">
         <f>AVERAGE(F$15:F17)</f>
         <v>0.0752385216481432</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="36">
         <f t="shared" si="2"/>
         <v>0.0826446280991736</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="6">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="6">
         <v>444</v>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="38">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="6">
         <v>484</v>
       </c>
     </row>
     <row r="18" hidden="1" spans="1:10">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="6">
         <v>240</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="36">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="6">
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="36">
         <f>AVERAGE(F$15:F18)</f>
         <v>0.0751788912361074</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="36">
         <f t="shared" si="2"/>
         <v>0.075</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="6">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="6">
         <v>222</v>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="38">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="6">
         <v>240</v>
       </c>
     </row>
     <row r="19" hidden="1" spans="1:10">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="6">
         <v>271</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="36">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="6">
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="36">
         <f>AVERAGE(F$15:F19)</f>
         <v>0.0741652532102881</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="36">
         <f t="shared" si="2"/>
         <v>0.0701107011070111</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="6">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="6">
         <v>252</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="38">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="6">
         <v>271</v>
       </c>
     </row>
     <row r="20" hidden="1" spans="1:10">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="6">
         <v>278</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="36">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="6">
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="36">
         <f>AVERAGE(F$15:F20)</f>
         <v>0.073794785349101</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="36">
         <f t="shared" si="2"/>
         <v>0.0719424460431655</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="6">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="6">
         <v>258</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="38">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="6">
         <v>278</v>
       </c>
     </row>
     <row r="21" hidden="1" spans="1:10">
-      <c r="C21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
+      <c r="C21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
     </row>
     <row r="22" hidden="1" spans="1:10">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
+      <c r="C22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
     </row>
     <row r="23" hidden="1" spans="1:10">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="24" hidden="1" spans="1:10">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="6">
         <v>440</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="36">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="6">
         <f t="shared" ref="D24:D28" si="7">ROUND(B24*C24,0)</f>
         <v>68</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="36">
         <f>AVERAGE(F$24:F24)</f>
         <v>0.0727272727272727</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="36">
         <f t="shared" ref="F24:F28" si="8">G24/B24</f>
         <v>0.0727272727272727</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="6">
         <f t="shared" ref="G24:G28" si="9">I24-H24</f>
         <v>32</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="6">
         <v>408</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="38">
         <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
         <v>440</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="6">
         <v>440</v>
       </c>
     </row>
     <row r="25" hidden="1" spans="1:10">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="6">
         <v>378</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="36">
         <f t="shared" ref="C25:C28" si="11">C24</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="6">
         <f t="shared" si="7"/>
         <v>58</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="36">
         <f>AVERAGE(F$24:F25)</f>
         <v>0.076046176046176</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="36">
         <f t="shared" si="8"/>
         <v>0.0793650793650794</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="6">
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="6">
         <v>348</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="38">
         <f t="shared" si="10"/>
         <v>378</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="6">
         <v>378</v>
       </c>
     </row>
     <row r="26" hidden="1" spans="1:10">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="6">
         <v>209</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="36">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="6">
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="36">
         <f>AVERAGE(F$24:F26)</f>
         <v>0.0778106883370041</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="36">
         <f t="shared" si="8"/>
         <v>0.0813397129186603</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="6">
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26" s="6">
         <v>192</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="38">
         <f t="shared" si="10"/>
         <v>209</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="6">
         <v>209</v>
       </c>
     </row>
     <row r="27" hidden="1" spans="1:10">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="6">
         <v>62</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="36">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="6">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="36">
         <f>AVERAGE(F$24:F27)</f>
         <v>0.0664225323817854</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="36">
         <f t="shared" si="8"/>
         <v>0.032258064516129</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="6">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="6">
         <v>60</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="38">
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="6">
         <v>62</v>
       </c>
     </row>
     <row r="28" hidden="1" spans="1:10">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="6">
         <v>464</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="36">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="6">
         <f t="shared" si="7"/>
         <v>71</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="36">
         <f>AVERAGE(F$24:F28)</f>
         <v>0.0695173362502559</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="36">
         <f t="shared" si="8"/>
         <v>0.0818965517241379</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="6">
         <f t="shared" si="9"/>
         <v>38</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="6">
         <v>426</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="38">
         <f t="shared" si="10"/>
         <v>464</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="6">
         <v>464</v>
       </c>
     </row>
     <row r="29" hidden="1" spans="1:10">
-      <c r="C29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
+      <c r="C29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
     </row>
     <row r="30" hidden="1" spans="1:10">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="31" hidden="1" spans="1:10">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="32" hidden="1" spans="1:10">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="6">
         <v>132</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="36">
         <f t="shared" ref="C32:C35" si="12">4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="6">
         <f t="shared" ref="D32:D35" si="13">ROUND(B32*C32,0)</f>
         <v>20</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="36">
         <f>AVERAGE(F$32:F32)</f>
         <v>0.0909090909090909</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="36">
         <f t="shared" ref="F32:F35" si="14">G32/B32</f>
         <v>0.0909090909090909</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="6">
         <f t="shared" ref="G32:G35" si="15">I32-H32</f>
         <v>12</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="6">
         <v>120</v>
       </c>
-      <c r="I32" s="31">
+      <c r="I32" s="38">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
         <v>132</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="6">
         <v>132</v>
       </c>
     </row>
     <row r="33" hidden="1" spans="1:10">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="6">
         <v>30</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="36">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="6">
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="36">
         <f>AVERAGE(F$32:F33)</f>
         <v>0.0454545454545455</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="36">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" s="6">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H33" s="6">
         <v>30</v>
       </c>
-      <c r="I33" s="31">
+      <c r="I33" s="38">
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="6">
         <v>30</v>
       </c>
     </row>
     <row r="34" hidden="1" spans="1:10">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="6">
         <v>395</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="36">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="6">
         <f t="shared" si="13"/>
         <v>61</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="36">
         <f>AVERAGE(F$32:F34)</f>
         <v>0.0547756041426928</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F34" s="36">
         <f t="shared" si="14"/>
         <v>0.0734177215189873</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="6">
         <f t="shared" si="15"/>
         <v>29</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="6">
         <v>366</v>
       </c>
-      <c r="I34" s="31">
+      <c r="I34" s="38">
         <f t="shared" si="16"/>
         <v>395</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="6">
         <v>395</v>
       </c>
     </row>
     <row r="35" hidden="1" spans="1:10">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="6">
         <v>66</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="36">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="6">
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="36">
         <f>AVERAGE(F$32:F35)</f>
         <v>0.0638089758342923</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="36">
         <f t="shared" si="14"/>
         <v>0.0909090909090909</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" s="6">
         <f t="shared" si="15"/>
         <v>6</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="6">
         <v>60</v>
       </c>
-      <c r="I35" s="31">
+      <c r="I35" s="38">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="6">
         <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
+      <c r="C37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="1">
-        <v>1</v>
+      <c r="J38" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="1">
-        <v>100</v>
-      </c>
-      <c r="C39" s="29">
+      <c r="B39" s="6">
+        <f>100+148</f>
+        <v>248</v>
+      </c>
+      <c r="C39" s="36">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="6">
         <f>ROUND(B39*C39,0)</f>
-        <v>15</v>
-      </c>
-      <c r="E39" s="29">
+        <v>38</v>
+      </c>
+      <c r="E39" s="36">
         <f>AVERAGE(F$39:F39)</f>
+        <v>0.0725806451612903</v>
+      </c>
+      <c r="F39" s="36">
+        <f>G39/B39</f>
+        <v>0.0725806451612903</v>
+      </c>
+      <c r="G39" s="6">
+        <f>I39-H39</f>
+        <v>18</v>
+      </c>
+      <c r="H39" s="6">
+        <v>38</v>
+      </c>
+      <c r="I39" s="39">
+        <f>MIN($J$38*D39,J39)</f>
+        <v>56</v>
+      </c>
+      <c r="J39" s="6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="6">
+        <v>40</v>
+      </c>
+      <c r="C40" s="36">
+        <f>4/26</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D40" s="6">
+        <f>ROUND(B40*C40,0)</f>
+        <v>6</v>
+      </c>
+      <c r="E40" s="36">
+        <f>AVERAGE(F$39:F40)</f>
+        <v>0.111290322580645</v>
+      </c>
+      <c r="F40" s="36">
+        <f>G40/B40</f>
         <v>0.15</v>
       </c>
-      <c r="F39" s="29">
-        <f>G39/B39</f>
-        <v>0.15</v>
-      </c>
-      <c r="G39" s="1">
-        <f>I39-H39</f>
-        <v>15</v>
-      </c>
-      <c r="I39" s="31">
-        <f>MIN($J$38*D39,J39)</f>
-        <v>15</v>
-      </c>
-      <c r="J39" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="1">
-        <v>148</v>
-      </c>
-      <c r="C40" s="29">
-        <f>4/26</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D40" s="1">
-        <f>ROUND(B40*C40,0)</f>
-        <v>23</v>
-      </c>
-      <c r="E40" s="29">
-        <f>AVERAGE(F$39:F40)</f>
-        <v>0.075</v>
-      </c>
-      <c r="F40" s="29">
-        <f>G40/B40</f>
-        <v>0</v>
-      </c>
-      <c r="G40" s="1">
+      <c r="G40" s="6">
         <f>I40-H40</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="33">
+        <v>6</v>
+      </c>
+      <c r="H40" s="6">
+        <v>6</v>
+      </c>
+      <c r="I40" s="38">
         <f>MIN($J$38*D40,J40)</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="1">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="J40" s="6">
+        <v>13</v>
       </c>
     </row>
     <row r="41" hidden="1"/>
     <row r="42" hidden="1" spans="1:10">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
+      <c r="C42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
     </row>
     <row r="43" hidden="1" spans="1:10">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="44" hidden="1" spans="1:10">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="6">
         <f>212+52+63+30</f>
         <v>357</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="36">
         <f t="shared" ref="C44:C49" si="17">4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="6">
         <f>ROUND(B44*C44,0)</f>
         <v>55</v>
       </c>
-      <c r="E44" s="29">
+      <c r="E44" s="36">
         <f>AVERAGE(F$44:F44)</f>
         <v>0.0756302521008403</v>
       </c>
-      <c r="F44" s="29">
+      <c r="F44" s="36">
         <f>G44/B44</f>
         <v>0.0756302521008403</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G44" s="6">
         <f>I44-H44</f>
         <v>27</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H44" s="6">
         <v>330</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="38">
         <f>MIN($J$43*D44,J44)</f>
         <v>357</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="6">
         <f>327+30</f>
         <v>357</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="1" t="s">
+    <row r="45" hidden="1"/>
+    <row r="46" hidden="1" spans="1:10">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="1" t="s">
+      <c r="C46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+    </row>
+    <row r="47" hidden="1" spans="1:10">
+      <c r="A47" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J47" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="1" t="s">
+      <c r="J47" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" hidden="1" spans="1:10">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="6">
         <v>523</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="36">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="6">
         <f t="shared" ref="D48:D54" si="18">ROUND(B48*C48,0)</f>
         <v>80</v>
       </c>
-      <c r="E48" s="29">
+      <c r="E48" s="36">
         <f>AVERAGE(F$48:F48)</f>
-        <v>0.0267686424474187</v>
-      </c>
-      <c r="F48" s="29">
+        <v>0.0822179732313576</v>
+      </c>
+      <c r="F48" s="36">
         <f t="shared" ref="F48:F54" si="19">G48/B48</f>
-        <v>0.0267686424474187</v>
-      </c>
-      <c r="G48" s="1">
+        <v>0.0822179732313576</v>
+      </c>
+      <c r="G48" s="6">
         <f t="shared" ref="G48:G54" si="20">I48-H48</f>
-        <v>14</v>
-      </c>
-      <c r="H48" s="1">
-        <v>160</v>
-      </c>
-      <c r="I48" s="33">
+        <v>43</v>
+      </c>
+      <c r="H48" s="6">
+        <v>480</v>
+      </c>
+      <c r="I48" s="38">
         <f t="shared" ref="I48:I54" si="21">MIN($J$47*D48,J48)</f>
-        <v>174</v>
-      </c>
-      <c r="J48" s="1">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="J48" s="6">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" spans="1:10">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="6">
         <v>434</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="36">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="6">
         <f t="shared" si="18"/>
         <v>67</v>
       </c>
-      <c r="E49" s="29">
+      <c r="E49" s="36">
         <f>AVERAGE(F$48:F49)</f>
-        <v>0.0237529848181794</v>
-      </c>
-      <c r="F49" s="29">
+        <v>0.0779753460626834</v>
+      </c>
+      <c r="F49" s="36">
         <f t="shared" si="19"/>
-        <v>0.0207373271889401</v>
-      </c>
-      <c r="G49" s="1">
+        <v>0.0737327188940092</v>
+      </c>
+      <c r="G49" s="6">
         <f t="shared" si="20"/>
-        <v>9</v>
-      </c>
-      <c r="H49" s="1">
-        <v>134</v>
-      </c>
-      <c r="I49" s="33">
+        <v>32</v>
+      </c>
+      <c r="H49" s="6">
+        <v>402</v>
+      </c>
+      <c r="I49" s="38">
         <f t="shared" si="21"/>
-        <v>143</v>
-      </c>
-      <c r="J49" s="1">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J49" s="6">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="1:10">
+      <c r="A50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="6">
         <f>26+83</f>
         <v>109</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="36">
         <f t="shared" ref="C50:C60" si="22">4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="6">
         <f t="shared" si="18"/>
         <v>17</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="36">
         <f>AVERAGE(F$48:F50)</f>
-        <v>0.0678230907962175</v>
-      </c>
-      <c r="F50" s="29">
+        <v>0.0733902918705351</v>
+      </c>
+      <c r="F50" s="36">
         <f t="shared" si="19"/>
-        <v>0.155963302752294</v>
-      </c>
-      <c r="G50" s="1">
+        <v>0.0642201834862385</v>
+      </c>
+      <c r="G50" s="6">
         <f t="shared" si="20"/>
-        <v>17</v>
-      </c>
-      <c r="H50" s="1">
-        <v>34</v>
-      </c>
-      <c r="I50" s="33">
+        <v>7</v>
+      </c>
+      <c r="H50" s="6">
+        <v>102</v>
+      </c>
+      <c r="I50" s="38">
         <f t="shared" si="21"/>
-        <v>51</v>
-      </c>
-      <c r="J50" s="1">
-        <v>51</v>
+        <v>109</v>
+      </c>
+      <c r="J50" s="6">
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="C51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="I51" s="33"/>
+      <c r="C51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
+      <c r="I51" s="39"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
+      <c r="C52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="6">
         <v>999</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="36">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="6">
         <f t="shared" ref="D54:D60" si="23">ROUND(B54*C54,0)</f>
         <v>154</v>
       </c>
-      <c r="E54" s="29">
+      <c r="E54" s="36">
         <f>AVERAGE(F$54:F54)</f>
-        <v>0.032032032032032</v>
-      </c>
-      <c r="F54" s="29">
+        <v>0</v>
+      </c>
+      <c r="F54" s="36">
         <f t="shared" ref="F54:F60" si="24">G54/B54</f>
-        <v>0.032032032032032</v>
-      </c>
-      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6">
         <f t="shared" ref="G54:G60" si="25">I54-H54</f>
-        <v>32</v>
-      </c>
-      <c r="I54" s="33">
+        <v>0</v>
+      </c>
+      <c r="I54" s="39">
         <f t="shared" ref="I54:I60" si="26">MIN($J$53*D54,J54)</f>
-        <v>32</v>
-      </c>
-      <c r="J54" s="1">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="J54" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="6">
         <v>999</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="36">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="6">
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E55" s="29">
+      <c r="E55" s="36">
         <f>AVERAGE(F$54:F55)</f>
-        <v>0.049049049049049</v>
-      </c>
-      <c r="F55" s="29">
+        <v>0</v>
+      </c>
+      <c r="F55" s="36">
         <f t="shared" si="24"/>
-        <v>0.0660660660660661</v>
-      </c>
-      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6">
         <f t="shared" si="25"/>
-        <v>66</v>
-      </c>
-      <c r="I55" s="33">
+        <v>0</v>
+      </c>
+      <c r="I55" s="39">
         <f t="shared" si="26"/>
-        <v>66</v>
-      </c>
-      <c r="J55" s="1">
-        <v>66</v>
+        <v>0</v>
+      </c>
+      <c r="J55" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="6">
         <v>999</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="36">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="6">
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E56" s="29">
+      <c r="E56" s="36">
         <f>AVERAGE(F$54:F56)</f>
-        <v>0.042042042042042</v>
-      </c>
-      <c r="F56" s="29">
+        <v>0</v>
+      </c>
+      <c r="F56" s="36">
         <f t="shared" si="24"/>
-        <v>0.028028028028028</v>
-      </c>
-      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6">
         <f t="shared" si="25"/>
-        <v>28</v>
-      </c>
-      <c r="I56" s="33">
+        <v>0</v>
+      </c>
+      <c r="I56" s="39">
         <f t="shared" si="26"/>
-        <v>28</v>
-      </c>
-      <c r="J56" s="1">
-        <v>28</v>
+        <v>0</v>
+      </c>
+      <c r="J56" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="6">
         <v>999</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="36">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="6">
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E57" s="29">
+      <c r="E57" s="36">
         <f>AVERAGE(F$54:F57)</f>
-        <v>0.0315315315315315</v>
-      </c>
-      <c r="F57" s="29">
+        <v>0</v>
+      </c>
+      <c r="F57" s="36">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G57" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="39">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J57" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="6">
         <v>999</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="36">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="6">
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E58" s="29">
+      <c r="E58" s="36">
         <f>AVERAGE(F$54:F58)</f>
-        <v>0.0252252252252252</v>
-      </c>
-      <c r="F58" s="29">
+        <v>0</v>
+      </c>
+      <c r="F58" s="36">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I58" s="33">
+      <c r="I58" s="39">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J58" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="6">
         <v>999</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="36">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="6">
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E59" s="29">
+      <c r="E59" s="36">
         <f>AVERAGE(F$54:F59)</f>
-        <v>0.021021021021021</v>
-      </c>
-      <c r="F59" s="29">
+        <v>0</v>
+      </c>
+      <c r="F59" s="36">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="39">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J59" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="6">
         <v>999</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="36">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="6">
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E60" s="29">
+      <c r="E60" s="36">
         <f>AVERAGE(F$54:F60)</f>
-        <v>0.018018018018018</v>
-      </c>
-      <c r="F60" s="29">
+        <v>0</v>
+      </c>
+      <c r="F60" s="36">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G60" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I60" s="33">
+      <c r="I60" s="39">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J60" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4008,7 +4381,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A45:AH46 A47:I47 K47:AH48 A48:G48 I48 A36:AH39 K40:AH41 I32:I35 A32:G35 K31:AH35 A31:I31 A3:AG6 A7:AH30 A2:O2 A1:AG1 A44 A42:AH42 A43:I43 K43:AH44 C44:G44 I44" formulaRange="1"/>
+    <ignoredError sqref="A41:AR46 I39:I40 C39:G40 K38:AR40 A38:I38 A3:AR37 AL2:AR2 A2:AH2 A1:AR1 A47:I47 K48:AH48 A48:G50 I48:I50 B58:AR60 A57:AR57 K54:AR56 A54:I56 A51:AR53" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4016,340 +4389,420 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16384" width="10.7777777777778" style="1" customWidth="1"/>
+    <col min="1" max="16384" width="10.7777777777778" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="2" hidden="1" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="6">
         <v>202</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" hidden="1" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="6">
         <v>390</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4" hidden="1" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="6">
         <v>484</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="6" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="5" hidden="1" spans="1:5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="6">
         <v>240</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6" hidden="1" spans="1:5">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="6">
         <v>271</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" hidden="1" spans="1:5">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="6">
         <v>278</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" hidden="1" spans="1:5">
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="9" hidden="1" spans="1:5">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="6">
         <v>440</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10" hidden="1" spans="1:5">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="6">
         <v>378</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="6" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11" hidden="1" spans="1:5">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="6">
         <v>209</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="12" hidden="1" spans="1:5">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="6">
         <v>62</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" hidden="1" spans="1:5">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="6">
         <v>464</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="14" hidden="1" spans="1:5">
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" hidden="1" spans="1:5">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="6">
         <v>132</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="16" hidden="1" spans="1:5">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="6">
         <v>30</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="26"/>
-    </row>
-    <row r="17" hidden="1" spans="1:8">
-      <c r="A17" s="1" t="s">
+    </row>
+    <row r="17" hidden="1" spans="1:10">
+      <c r="A17" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="6">
         <v>395</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:8">
-      <c r="A18" s="1" t="s">
+    <row r="18" hidden="1" spans="1:10">
+      <c r="A18" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="6">
         <v>66</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:8">
-      <c r="C19" s="1" t="s">
+    <row r="19" hidden="1" spans="1:10">
+      <c r="C19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:8">
-      <c r="A20" s="1" t="s">
+    <row r="20" hidden="1" spans="1:10">
+      <c r="A20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="6">
         <f>SUM(C20:H20)</f>
         <v>357</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="6">
         <v>212</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="6">
         <v>52</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="6">
         <v>63</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="6">
         <v>16</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="21" hidden="1"/>
-    <row r="22" spans="1:8">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:10">
+      <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="1">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="1" t="s">
+      <c r="B22" s="6">
+        <v>523</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="1">
-        <v>143</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="1" t="s">
+      <c r="B23" s="6">
+        <v>434</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="6">
         <f>C24+D24</f>
-        <v>51</v>
-      </c>
-      <c r="C24" s="1">
-        <v>17</v>
-      </c>
-      <c r="D24" s="1">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="6">
+        <v>26</v>
+      </c>
+      <c r="D24" s="6">
+        <v>83</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="C25" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="1" t="s">
+      <c r="B26" s="6">
+        <f>SUM(C26:D26)</f>
+        <v>56</v>
+      </c>
+      <c r="C26" s="6">
         <v>38</v>
       </c>
-      <c r="B27" s="1">
-        <v>0</v>
+      <c r="D26" s="6">
+        <v>18</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6">
+        <v>13</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -4365,181 +4818,181 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="9.66666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.4444444444444" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5555555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.1111111111111" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.4444444444444" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.1111111111111" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="9.66666666666667" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25.4444444444444" style="6" customWidth="1"/>
+    <col min="3" max="3" width="23.1111111111111" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.5555555555556" style="6" customWidth="1"/>
+    <col min="5" max="5" width="23.1111111111111" style="6" customWidth="1"/>
+    <col min="6" max="6" width="26.5555555555556" style="6" customWidth="1"/>
+    <col min="7" max="7" width="25.4444444444444" style="6" customWidth="1"/>
+    <col min="8" max="8" width="23.1111111111111" style="6" customWidth="1"/>
+    <col min="9" max="16384" width="8.88888888888889" style="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.15" spans="1:4">
-      <c r="A1" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>96</v>
+      <c r="A1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:4">
-      <c r="A2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>97</v>
+      <c r="A2" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="3" ht="15.15" spans="1:4">
-      <c r="A3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>101</v>
+      <c r="A3" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="15.15" spans="1:4">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>104</v>
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>108</v>
+      <c r="A5" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:4">
-      <c r="A6" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>112</v>
+      <c r="A6" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:4">
-      <c r="A7" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
+      <c r="A7" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
     </row>
     <row r="8" ht="15.15" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>116</v>
+      <c r="A8" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="9" ht="15.15" spans="1:4">
-      <c r="A9" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>97</v>
+      <c r="A9" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>98</v>
+      <c r="A10" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:4">
-      <c r="A11" s="8"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="8"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="13"/>
     </row>
     <row r="12" ht="15.15" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>105</v>
+      <c r="A12" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:4">
-      <c r="A13" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>120</v>
+      <c r="A13" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4554,4 +5007,645 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="31.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="61.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="35.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="9.44444444444444" customWidth="1"/>
+    <col min="7" max="7" width="8.66666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.15" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" ht="15.15" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" ht="15.15" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" ht="15.15" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" ht="15.15" spans="1:7">
+      <c r="A5" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" ht="15.15" spans="1:7">
+      <c r="A6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" ht="15.15"/>
+    <row r="8" ht="15.15" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" ht="15.15" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="2">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" s="2">
+        <v>26.8</v>
+      </c>
+      <c r="F9" s="2">
+        <v>39.9</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" ht="15.15" spans="1:7">
+      <c r="A10" s="4"/>
+      <c r="B10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="2">
+        <v>25</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="2">
+        <v>31.6</v>
+      </c>
+      <c r="F10" s="2">
+        <v>40.1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" ht="15.15" spans="1:7">
+      <c r="A11" s="4"/>
+      <c r="B11" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="2">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="2">
+        <v>26.3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>39.2</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" ht="15.15" spans="1:7">
+      <c r="A12" s="5"/>
+      <c r="B12" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="2">
+        <v>75</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" s="2">
+        <v>26.3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>40.1</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" ht="15.15" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="2">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E13" s="2">
+        <v>8.2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>16.4</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.274</v>
+      </c>
+    </row>
+    <row r="14" ht="15.15" spans="1:7">
+      <c r="A14" s="4"/>
+      <c r="B14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" s="2">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>17.1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" ht="15.15" spans="1:7">
+      <c r="A15" s="4"/>
+      <c r="B15" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="2">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>19.3</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" ht="15.15" spans="1:7">
+      <c r="A16" s="5"/>
+      <c r="B16" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="2">
+        <v>75</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E16" s="2">
+        <v>8.2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>19.3</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" ht="15.15"/>
+    <row r="18" ht="15.15" spans="1:7">
+      <c r="A18" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" ht="15.15" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="2">
+        <v>25</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="2">
+        <v>20.55</v>
+      </c>
+      <c r="F19" s="2">
+        <v>47.12</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" ht="15.15" spans="1:7">
+      <c r="A20" s="4"/>
+      <c r="B20" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="2">
+        <v>25</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E20" s="2">
+        <v>29.18</v>
+      </c>
+      <c r="F20" s="2">
+        <v>48.1</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" ht="15.15" spans="1:7">
+      <c r="A21" s="4"/>
+      <c r="B21" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="2">
+        <v>25</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" s="2">
+        <v>33.77</v>
+      </c>
+      <c r="F21" s="2">
+        <v>56.1</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" ht="15.15" spans="1:7">
+      <c r="A22" s="5"/>
+      <c r="B22" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" s="2">
+        <v>75</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" s="2">
+        <v>20.55</v>
+      </c>
+      <c r="F22" s="2">
+        <v>56.1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" ht="15.15"/>
+    <row r="24" ht="15.15" spans="1:7">
+      <c r="A24" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" ht="15.15" spans="1:7">
+      <c r="A25" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="2">
+        <v>-0.4876</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1.63428</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.766</v>
+      </c>
+    </row>
+    <row r="26" ht="15.15" spans="1:7">
+      <c r="A26" s="4"/>
+      <c r="B26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="2">
+        <v>-5.3084</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1.63428</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" ht="15.15" spans="1:7">
+      <c r="A27" s="4"/>
+      <c r="B27" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0.4876</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.63428</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.766</v>
+      </c>
+    </row>
+    <row r="28" ht="15.15" spans="1:7">
+      <c r="A28" s="4"/>
+      <c r="B28" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D28" s="2">
+        <v>-4.8208</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1.63428</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" ht="15.15" spans="1:7">
+      <c r="A29" s="4"/>
+      <c r="B29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D29" s="2">
+        <v>5.3084</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1.63428</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" ht="15.15" spans="1:7">
+      <c r="A30" s="5"/>
+      <c r="B30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" s="2">
+        <v>4.8208</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1.63428</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="31" ht="15.15" spans="1:7">
+      <c r="A31" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" s="2">
+        <v>-0.452</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.81249</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="32" ht="15.15" spans="1:7">
+      <c r="A32" s="4"/>
+      <c r="B32" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2.26</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.81249</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="33" ht="15.15" spans="1:6">
+      <c r="A33" s="4"/>
+      <c r="B33" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.452</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.81249</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="34" ht="15.15" spans="1:6">
+      <c r="A34" s="4"/>
+      <c r="B34" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2.712</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.81249</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" ht="15.15" spans="1:6">
+      <c r="A35" s="4"/>
+      <c r="B35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" s="2">
+        <v>-2.26</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.81249</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" ht="15.15" spans="1:6">
+      <c r="A36" s="5"/>
+      <c r="B36" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" s="2">
+        <v>-2.712</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.81249</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A25:A30"/>
+    <mergeCell ref="A31:A36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -859,18 +859,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1389,7 +1383,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -1413,16 +1407,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="20">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="20">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="21">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="21">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="20">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="20">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="22">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="22">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="23">
@@ -1431,89 +1425,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="24">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1614,9 +1608,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1963,133 +1954,133 @@
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35">
+      <c r="B1" s="34">
         <v>46081</v>
       </c>
-      <c r="C1" s="35">
+      <c r="C1" s="34">
         <v>46082</v>
       </c>
-      <c r="D1" s="35">
+      <c r="D1" s="34">
         <v>46083</v>
       </c>
-      <c r="E1" s="35">
+      <c r="E1" s="34">
         <v>46084</v>
       </c>
-      <c r="F1" s="35">
+      <c r="F1" s="34">
         <v>46085</v>
       </c>
-      <c r="G1" s="35">
+      <c r="G1" s="34">
         <v>46086</v>
       </c>
-      <c r="H1" s="35">
+      <c r="H1" s="34">
         <v>46087</v>
       </c>
-      <c r="I1" s="35">
+      <c r="I1" s="34">
         <v>46088</v>
       </c>
-      <c r="J1" s="35">
+      <c r="J1" s="34">
         <v>46089</v>
       </c>
-      <c r="K1" s="35">
+      <c r="K1" s="34">
         <v>46090</v>
       </c>
-      <c r="L1" s="35">
+      <c r="L1" s="34">
         <v>46091</v>
       </c>
-      <c r="M1" s="35">
+      <c r="M1" s="34">
         <v>46092</v>
       </c>
-      <c r="N1" s="35">
+      <c r="N1" s="34">
         <v>46093</v>
       </c>
-      <c r="O1" s="35">
+      <c r="O1" s="34">
         <v>46094</v>
       </c>
-      <c r="P1" s="35">
+      <c r="P1" s="34">
         <v>46095</v>
       </c>
-      <c r="Q1" s="35">
+      <c r="Q1" s="34">
         <v>46096</v>
       </c>
-      <c r="R1" s="35">
+      <c r="R1" s="34">
         <v>46097</v>
       </c>
-      <c r="S1" s="35">
+      <c r="S1" s="34">
         <v>46098</v>
       </c>
-      <c r="T1" s="35">
+      <c r="T1" s="34">
         <v>46099</v>
       </c>
-      <c r="U1" s="35">
+      <c r="U1" s="34">
         <v>46100</v>
       </c>
-      <c r="V1" s="35">
+      <c r="V1" s="34">
         <v>46101</v>
       </c>
-      <c r="W1" s="35">
+      <c r="W1" s="34">
         <v>46102</v>
       </c>
-      <c r="X1" s="35">
+      <c r="X1" s="34">
         <v>46103</v>
       </c>
-      <c r="Y1" s="35">
+      <c r="Y1" s="34">
         <v>46104</v>
       </c>
-      <c r="Z1" s="35">
+      <c r="Z1" s="34">
         <v>46105</v>
       </c>
-      <c r="AA1" s="35">
+      <c r="AA1" s="34">
         <v>46106</v>
       </c>
-      <c r="AB1" s="35">
+      <c r="AB1" s="34">
         <v>46107</v>
       </c>
-      <c r="AC1" s="35">
+      <c r="AC1" s="34">
         <v>46108</v>
       </c>
-      <c r="AD1" s="35">
+      <c r="AD1" s="34">
         <v>46109</v>
       </c>
-      <c r="AE1" s="35">
+      <c r="AE1" s="34">
         <v>46110</v>
       </c>
-      <c r="AF1" s="35">
+      <c r="AF1" s="34">
         <v>46111</v>
       </c>
-      <c r="AG1" s="35">
+      <c r="AG1" s="34">
         <v>46112</v>
       </c>
-      <c r="AH1" s="35">
+      <c r="AH1" s="34">
         <v>46113</v>
       </c>
-      <c r="AI1" s="35">
+      <c r="AI1" s="34">
         <v>46114</v>
       </c>
-      <c r="AJ1" s="35">
+      <c r="AJ1" s="34">
         <v>46115</v>
       </c>
-      <c r="AK1" s="35">
+      <c r="AK1" s="34">
         <v>46116</v>
       </c>
-      <c r="AL1" s="35">
+      <c r="AL1" s="34">
         <v>46117</v>
       </c>
-      <c r="AM1" s="35">
+      <c r="AM1" s="34">
         <v>46118</v>
       </c>
-      <c r="AN1" s="35">
+      <c r="AN1" s="34">
         <v>46119</v>
       </c>
-      <c r="AO1" s="35">
+      <c r="AO1" s="34">
         <v>46120</v>
       </c>
-      <c r="AP1" s="35">
+      <c r="AP1" s="34">
         <v>46121</v>
       </c>
-      <c r="AQ1" s="35">
+      <c r="AQ1" s="34">
         <v>46122</v>
       </c>
-      <c r="AR1" s="35">
+      <c r="AR1" s="34">
         <v>46123</v>
       </c>
     </row>
@@ -2097,133 +2088,133 @@
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36">
+      <c r="B2" s="35">
         <v>0.15436753577515</v>
       </c>
-      <c r="C2" s="36">
+      <c r="C2" s="35">
         <v>0.15436753577515</v>
       </c>
-      <c r="D2" s="36">
+      <c r="D2" s="35">
         <v>0.15436753577515</v>
       </c>
-      <c r="E2" s="36">
+      <c r="E2" s="35">
         <v>0.15436753577515</v>
       </c>
-      <c r="F2" s="36">
+      <c r="F2" s="35">
         <v>0.15436753577515</v>
       </c>
-      <c r="G2" s="37">
+      <c r="G2" s="36">
         <v>0.15436753577515</v>
       </c>
-      <c r="H2" s="36">
+      <c r="H2" s="35">
         <v>0.073794785349101</v>
       </c>
-      <c r="I2" s="37">
+      <c r="I2" s="36">
         <v>0.155080443958291</v>
       </c>
-      <c r="J2" s="37">
+      <c r="J2" s="36">
         <v>0.155080443958291</v>
       </c>
-      <c r="K2" s="36">
+      <c r="K2" s="35">
         <v>0.155080443958291</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="35">
         <v>0.155080443958291</v>
       </c>
-      <c r="M2" s="36">
+      <c r="M2" s="35">
         <v>0.155080443958291</v>
       </c>
-      <c r="N2" s="36">
+      <c r="N2" s="35">
         <v>0.155080443958291</v>
       </c>
-      <c r="O2" s="36">
+      <c r="O2" s="35">
         <v>0.0695173362502559</v>
       </c>
-      <c r="P2" s="37">
+      <c r="P2" s="36">
         <v>0.15406162464986</v>
       </c>
-      <c r="Q2" s="36">
+      <c r="Q2" s="35">
         <v>0.15406162464986</v>
       </c>
-      <c r="R2" s="36">
+      <c r="R2" s="35">
         <v>0.15406162464986</v>
       </c>
-      <c r="S2" s="36">
+      <c r="S2" s="35">
         <v>0.15406162464986</v>
       </c>
-      <c r="T2" s="36">
+      <c r="T2" s="35">
         <v>0.15406162464986</v>
       </c>
-      <c r="U2" s="36">
+      <c r="U2" s="35">
         <v>0.15406162464986</v>
       </c>
-      <c r="V2" s="36">
+      <c r="V2" s="35">
         <v>0.0756302521008403</v>
       </c>
-      <c r="W2" s="36">
+      <c r="W2" s="35">
         <v>0.156031837360951</v>
       </c>
-      <c r="X2" s="36">
+      <c r="X2" s="35">
         <v>0.156031837360951</v>
       </c>
-      <c r="Y2" s="36">
+      <c r="Y2" s="35">
         <v>0.156031837360951</v>
       </c>
-      <c r="Z2" s="36">
+      <c r="Z2" s="35">
         <v>0.156031837360951</v>
       </c>
-      <c r="AA2" s="36">
+      <c r="AA2" s="35">
         <v>0.156031837360951</v>
       </c>
-      <c r="AB2" s="36">
+      <c r="AB2" s="35">
         <v>0.156031837360951</v>
       </c>
-      <c r="AC2" s="36">
+      <c r="AC2" s="35">
         <v>0.0638089758342923</v>
       </c>
-      <c r="AD2" s="36">
+      <c r="AD2" s="35">
         <v>0.154434951354911</v>
       </c>
-      <c r="AE2" s="36">
+      <c r="AE2" s="35">
         <v>0.154434951354911</v>
       </c>
-      <c r="AF2" s="36">
+      <c r="AF2" s="35">
         <v>0.154434951354911</v>
       </c>
-      <c r="AG2" s="36">
+      <c r="AG2" s="35">
         <v>0.154434951354911</v>
       </c>
-      <c r="AH2" s="36">
+      <c r="AH2" s="35">
         <v>0.154434951354911</v>
       </c>
-      <c r="AI2" s="36">
+      <c r="AI2" s="35">
         <v>0.154434951354911</v>
       </c>
-      <c r="AJ2" s="36">
+      <c r="AJ2" s="35">
         <v>0.0733902918705351</v>
       </c>
-      <c r="AK2" s="36">
+      <c r="AK2" s="35">
         <v>0.151612903225806</v>
       </c>
-      <c r="AL2" s="36">
+      <c r="AL2" s="35">
         <v>0</v>
       </c>
-      <c r="AM2" s="36">
+      <c r="AM2" s="35">
         <v>0</v>
       </c>
-      <c r="AN2" s="36">
+      <c r="AN2" s="35">
         <v>0</v>
       </c>
-      <c r="AO2" s="36">
+      <c r="AO2" s="35">
         <v>0</v>
       </c>
-      <c r="AP2" s="36">
+      <c r="AP2" s="35">
         <v>0</v>
       </c>
-      <c r="AQ2" s="36">
+      <c r="AQ2" s="35">
         <v>0</v>
       </c>
-      <c r="AR2" s="36">
+      <c r="AR2" s="35">
         <v>0</v>
       </c>
     </row>
@@ -2231,175 +2222,175 @@
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36">
+      <c r="B3" s="35">
         <f>SUM($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C3" s="36">
+      <c r="C3" s="35">
         <f>SUM($B2:C2)</f>
         <v>0.3087350715503</v>
       </c>
-      <c r="D3" s="36">
+      <c r="D3" s="35">
         <f>SUM($B2:D2)</f>
         <v>0.463102607325449</v>
       </c>
-      <c r="E3" s="36">
+      <c r="E3" s="35">
         <f>SUM($B2:E2)</f>
         <v>0.617470143100599</v>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="35">
         <f>SUM($B2:F2)</f>
         <v>0.771837678875749</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="35">
         <f>SUM($B2:G2)</f>
         <v>0.926205214650899</v>
       </c>
-      <c r="H3" s="36">
+      <c r="H3" s="35">
         <f>SUM($B2:H2)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="36">
+      <c r="I3" s="35">
         <f>SUM($B2:I2)</f>
         <v>1.15508044395829</v>
       </c>
-      <c r="J3" s="36">
+      <c r="J3" s="35">
         <f>SUM($B2:J2)</f>
         <v>1.31016088791658</v>
       </c>
-      <c r="K3" s="36">
+      <c r="K3" s="35">
         <f>SUM($B2:K2)</f>
         <v>1.46524133187487</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="35">
         <f>SUM($B2:L2)</f>
         <v>1.62032177583316</v>
       </c>
-      <c r="M3" s="36">
+      <c r="M3" s="35">
         <f>SUM($B2:M2)</f>
         <v>1.77540221979145</v>
       </c>
-      <c r="N3" s="36">
+      <c r="N3" s="35">
         <f>SUM($B2:N2)</f>
         <v>1.93048266374974</v>
       </c>
-      <c r="O3" s="36">
+      <c r="O3" s="35">
         <f>SUM($B2:O2)</f>
         <v>2</v>
       </c>
-      <c r="P3" s="36">
+      <c r="P3" s="35">
         <f>SUM($B2:P2)</f>
         <v>2.15406162464986</v>
       </c>
-      <c r="Q3" s="36">
+      <c r="Q3" s="35">
         <f>SUM($B2:Q2)</f>
         <v>2.30812324929972</v>
       </c>
-      <c r="R3" s="36">
+      <c r="R3" s="35">
         <f>SUM($B2:R2)</f>
         <v>2.46218487394958</v>
       </c>
-      <c r="S3" s="36">
+      <c r="S3" s="35">
         <f>SUM($B2:S2)</f>
         <v>2.61624649859944</v>
       </c>
-      <c r="T3" s="36">
+      <c r="T3" s="35">
         <f>SUM($B2:T2)</f>
         <v>2.7703081232493</v>
       </c>
-      <c r="U3" s="36">
+      <c r="U3" s="35">
         <f>SUM($B2:U2)</f>
         <v>2.92436974789916</v>
       </c>
-      <c r="V3" s="36">
+      <c r="V3" s="35">
         <f>SUM($B2:V2)</f>
         <v>3</v>
       </c>
-      <c r="W3" s="36">
+      <c r="W3" s="35">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208285</v>
       </c>
-      <c r="X3" s="36">
+      <c r="X3" s="35">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208285</v>
       </c>
-      <c r="Y3" s="36">
+      <c r="Y3" s="35">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208285</v>
       </c>
-      <c r="Z3" s="36">
+      <c r="Z3" s="35">
         <f>SUM($B2:Z2)</f>
         <v>3.6241273494438</v>
       </c>
-      <c r="AA3" s="36">
+      <c r="AA3" s="35">
         <f>SUM($B2:AA2)</f>
         <v>3.78015918680476</v>
       </c>
-      <c r="AB3" s="36">
+      <c r="AB3" s="35">
         <f>SUM($B2:AB2)</f>
         <v>3.93619102416571</v>
       </c>
-      <c r="AC3" s="36">
+      <c r="AC3" s="35">
         <f>SUM($B2:AC2)</f>
         <v>4</v>
       </c>
-      <c r="AD3" s="36">
+      <c r="AD3" s="35">
         <f>SUM($B2:AD2)</f>
         <v>4.15443495135491</v>
       </c>
-      <c r="AE3" s="36">
+      <c r="AE3" s="35">
         <f>SUM($B2:AE2)</f>
         <v>4.30886990270982</v>
       </c>
-      <c r="AF3" s="36">
+      <c r="AF3" s="35">
         <f>SUM($B2:AF2)</f>
         <v>4.46330485406473</v>
       </c>
-      <c r="AG3" s="36">
+      <c r="AG3" s="35">
         <f>SUM($B2:AG2)</f>
         <v>4.61773980541964</v>
       </c>
-      <c r="AH3" s="36">
+      <c r="AH3" s="35">
         <f>SUM($B2:AH2)</f>
         <v>4.77217475677455</v>
       </c>
-      <c r="AI3" s="36">
+      <c r="AI3" s="35">
         <f>SUM($B2:AI2)</f>
         <v>4.92660970812946</v>
       </c>
-      <c r="AJ3" s="36">
+      <c r="AJ3" s="35">
         <f>SUM($B2:AJ2)</f>
         <v>5</v>
       </c>
-      <c r="AK3" s="36">
+      <c r="AK3" s="35">
         <f>SUM($B2:AK2)</f>
         <v>5.1516129032258</v>
       </c>
-      <c r="AL3" s="36">
+      <c r="AL3" s="35">
         <f>SUM($B2:AL2)</f>
         <v>5.1516129032258</v>
       </c>
-      <c r="AM3" s="36">
+      <c r="AM3" s="35">
         <f>SUM($B2:AM2)</f>
         <v>5.1516129032258</v>
       </c>
-      <c r="AN3" s="36">
+      <c r="AN3" s="35">
         <f>SUM($B2:AN2)</f>
         <v>5.1516129032258</v>
       </c>
-      <c r="AO3" s="36">
+      <c r="AO3" s="35">
         <f>SUM($B2:AO2)</f>
         <v>5.1516129032258</v>
       </c>
-      <c r="AP3" s="36">
+      <c r="AP3" s="35">
         <f>SUM($B2:AP2)</f>
         <v>5.1516129032258</v>
       </c>
-      <c r="AQ3" s="36">
+      <c r="AQ3" s="35">
         <f>SUM($B2:AQ2)</f>
         <v>5.1516129032258</v>
       </c>
-      <c r="AR3" s="36">
+      <c r="AR3" s="35">
         <f>SUM($B2:AR2)</f>
         <v>5.1516129032258</v>
       </c>
@@ -2408,175 +2399,175 @@
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="35">
         <f>AVERAGE($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="35">
         <f>AVERAGE($B2:C2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="35">
         <f>AVERAGE($B2:D2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="35">
         <f>AVERAGE($B2:E2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="35">
         <f>AVERAGE($B2:F2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="35">
         <f>AVERAGE($B2:G2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="H4" s="36">
+      <c r="H4" s="35">
         <f>AVERAGE($B2:H2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="35">
         <f>AVERAGE($B2:I2)</f>
         <v>0.144385055494786</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="35">
         <f>AVERAGE($B2:J2)</f>
         <v>0.145573431990731</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="35">
         <f>AVERAGE($B2:K2)</f>
         <v>0.146524133187487</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="35">
         <f>AVERAGE($B2:L2)</f>
         <v>0.147301979621197</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="35">
         <f>AVERAGE($B2:M2)</f>
         <v>0.147950184982621</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="35">
         <f>AVERAGE($B2:N2)</f>
         <v>0.148498666442288</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="35">
         <f>AVERAGE($B2:O2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="35">
         <f>AVERAGE($B2:P2)</f>
         <v>0.143604108309991</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="35">
         <f>AVERAGE($B2:Q2)</f>
         <v>0.144257703081233</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="35">
         <f>AVERAGE($B2:R2)</f>
         <v>0.144834404349975</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="35">
         <f>AVERAGE($B2:S2)</f>
         <v>0.145347027699969</v>
       </c>
-      <c r="T4" s="36">
+      <c r="T4" s="35">
         <f>AVERAGE($B2:T2)</f>
         <v>0.145805690697332</v>
       </c>
-      <c r="U4" s="36">
+      <c r="U4" s="35">
         <f>AVERAGE($B2:U2)</f>
         <v>0.146218487394958</v>
       </c>
-      <c r="V4" s="36">
+      <c r="V4" s="35">
         <f>AVERAGE($B2:V2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="W4" s="36">
+      <c r="W4" s="35">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="X4" s="36">
+      <c r="X4" s="35">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="Y4" s="36">
+      <c r="Y4" s="35">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="Z4" s="36">
+      <c r="Z4" s="35">
         <f>AVERAGE($B2:Z2)</f>
         <v>0.144965093977752</v>
       </c>
-      <c r="AA4" s="36">
+      <c r="AA4" s="35">
         <f>AVERAGE($B2:AA2)</f>
         <v>0.145390737954029</v>
       </c>
-      <c r="AB4" s="36">
+      <c r="AB4" s="35">
         <f>AVERAGE($B2:AB2)</f>
         <v>0.145784852746878</v>
       </c>
-      <c r="AC4" s="36">
+      <c r="AC4" s="35">
         <f>AVERAGE($B2:AC2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="AD4" s="36">
+      <c r="AD4" s="35">
         <f>AVERAGE($B2:AD2)</f>
         <v>0.143256377632928</v>
       </c>
-      <c r="AE4" s="36">
+      <c r="AE4" s="35">
         <f>AVERAGE($B2:AE2)</f>
         <v>0.143628996756994</v>
       </c>
-      <c r="AF4" s="36">
+      <c r="AF4" s="35">
         <f>AVERAGE($B2:AF2)</f>
         <v>0.143977575937572</v>
       </c>
-      <c r="AG4" s="36">
+      <c r="AG4" s="35">
         <f>AVERAGE($B2:AG2)</f>
         <v>0.144304368919364</v>
       </c>
-      <c r="AH4" s="36">
+      <c r="AH4" s="35">
         <f>AVERAGE($B2:AH2)</f>
         <v>0.144611356265896</v>
       </c>
-      <c r="AI4" s="36">
+      <c r="AI4" s="35">
         <f>AVERAGE($B2:AI2)</f>
         <v>0.144900285533219</v>
       </c>
-      <c r="AJ4" s="36">
+      <c r="AJ4" s="35">
         <f>AVERAGE($B2:AJ2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="AK4" s="36">
+      <c r="AK4" s="35">
         <f>AVERAGE($B2:AK2)</f>
         <v>0.143100358422939</v>
       </c>
-      <c r="AL4" s="36">
+      <c r="AL4" s="35">
         <f>AVERAGE($B2:AL2)</f>
         <v>0.139232781168265</v>
       </c>
-      <c r="AM4" s="36">
+      <c r="AM4" s="35">
         <f>AVERAGE($B2:AM2)</f>
         <v>0.135568760611205</v>
       </c>
-      <c r="AN4" s="36">
+      <c r="AN4" s="35">
         <f>AVERAGE($B2:AN2)</f>
         <v>0.132092638544251</v>
       </c>
-      <c r="AO4" s="36">
+      <c r="AO4" s="35">
         <f>AVERAGE($B2:AO2)</f>
         <v>0.128790322580645</v>
       </c>
-      <c r="AP4" s="36">
+      <c r="AP4" s="35">
         <f>AVERAGE($B2:AP2)</f>
         <v>0.125649095200629</v>
       </c>
-      <c r="AQ4" s="36">
+      <c r="AQ4" s="35">
         <f>AVERAGE($B2:AQ2)</f>
         <v>0.122657450076805</v>
       </c>
-      <c r="AR4" s="36">
+      <c r="AR4" s="35">
         <f>AVERAGE($B2:AR2)</f>
         <v>0.119804951237809</v>
       </c>
@@ -2585,175 +2576,175 @@
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="35">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="35">
         <f t="shared" ref="C5:AR5" si="0">B5</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="J5" s="36">
+      <c r="J5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="K5" s="36">
+      <c r="K5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="M5" s="36">
+      <c r="M5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="N5" s="36">
+      <c r="N5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="O5" s="36">
+      <c r="O5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="P5" s="36">
+      <c r="P5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Q5" s="36">
+      <c r="Q5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="R5" s="36">
+      <c r="R5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="S5" s="36">
+      <c r="S5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="T5" s="36">
+      <c r="T5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="U5" s="36">
+      <c r="U5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="V5" s="36">
+      <c r="V5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="W5" s="36">
+      <c r="W5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="X5" s="36">
+      <c r="X5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Y5" s="36">
+      <c r="Y5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Z5" s="36">
+      <c r="Z5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AA5" s="36">
+      <c r="AA5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AB5" s="36">
+      <c r="AB5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AC5" s="36">
+      <c r="AC5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AD5" s="36">
+      <c r="AD5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AE5" s="36">
+      <c r="AE5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AF5" s="36">
+      <c r="AF5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AG5" s="36">
+      <c r="AG5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AH5" s="36">
+      <c r="AH5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AI5" s="36">
+      <c r="AI5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AJ5" s="36">
+      <c r="AJ5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AK5" s="36">
+      <c r="AK5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AL5" s="36">
+      <c r="AL5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AM5" s="36">
+      <c r="AM5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AN5" s="36">
+      <c r="AN5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AO5" s="36">
+      <c r="AO5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AP5" s="36">
+      <c r="AP5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AQ5" s="36">
+      <c r="AQ5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AR5" s="36">
+      <c r="AR5" s="35">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
@@ -2762,175 +2753,175 @@
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="35">
         <f t="shared" ref="B6:AR6" si="1">B5-B2</f>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="35">
         <f t="shared" si="1"/>
         <v>0.080051368497053</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="35">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="35">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="35">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="35">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="M6" s="36">
+      <c r="M6" s="35">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="35">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="O6" s="36">
+      <c r="O6" s="35">
         <f t="shared" si="1"/>
         <v>0.0843288175958981</v>
       </c>
-      <c r="P6" s="36">
+      <c r="P6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="Q6" s="36">
+      <c r="Q6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="R6" s="36">
+      <c r="R6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="S6" s="36">
+      <c r="S6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="T6" s="36">
+      <c r="T6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="U6" s="36">
+      <c r="U6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="V6" s="36">
+      <c r="V6" s="35">
         <f t="shared" si="1"/>
         <v>0.0782159017453137</v>
       </c>
-      <c r="W6" s="36">
+      <c r="W6" s="35">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="X6" s="36">
+      <c r="X6" s="35">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="Y6" s="36">
+      <c r="Y6" s="35">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="Z6" s="36">
+      <c r="Z6" s="35">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="AA6" s="36">
+      <c r="AA6" s="35">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="AB6" s="36">
+      <c r="AB6" s="35">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="AC6" s="36">
+      <c r="AC6" s="35">
         <f t="shared" si="1"/>
         <v>0.0900371780118617</v>
       </c>
-      <c r="AD6" s="36">
+      <c r="AD6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AE6" s="36">
+      <c r="AE6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AF6" s="36">
+      <c r="AF6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AG6" s="36">
+      <c r="AG6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AH6" s="36">
+      <c r="AH6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AI6" s="36">
+      <c r="AI6" s="35">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AJ6" s="36">
+      <c r="AJ6" s="35">
         <f t="shared" si="1"/>
         <v>0.0804558619756189</v>
       </c>
-      <c r="AK6" s="36">
+      <c r="AK6" s="35">
         <f t="shared" si="1"/>
         <v>0.00223325062034754</v>
       </c>
-      <c r="AL6" s="36">
+      <c r="AL6" s="35">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AM6" s="36">
+      <c r="AM6" s="35">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AN6" s="36">
+      <c r="AN6" s="35">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AO6" s="36">
+      <c r="AO6" s="35">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AP6" s="36">
+      <c r="AP6" s="35">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AQ6" s="36">
+      <c r="AQ6" s="35">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AR6" s="36">
+      <c r="AR6" s="35">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
@@ -2977,18 +2968,18 @@
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="35">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D10" s="6">
         <v>50</v>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="35">
         <f>AVERAGE(F$10:F10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="35">
         <f t="shared" ref="F10:F20" si="2">G10/B10</f>
         <v>0</v>
       </c>
@@ -3010,18 +3001,18 @@
       <c r="B11" s="6">
         <v>50</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="35">
         <f>C10</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D11" s="6">
         <v>25</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="35">
         <f>AVERAGE(F$10:F11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="35">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3081,7 +3072,7 @@
       <c r="B15" s="6">
         <v>257</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="35">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3089,11 +3080,11 @@
         <f t="shared" ref="D10:D20" si="4">ROUND(B15*C15,0)</f>
         <v>40</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="35">
         <f>AVERAGE(F$15:F15)</f>
         <v>0.066147859922179</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="35">
         <f t="shared" si="2"/>
         <v>0.066147859922179</v>
       </c>
@@ -3104,7 +3095,7 @@
       <c r="H15" s="6">
         <v>240</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15" s="37">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
@@ -3119,7 +3110,7 @@
       <c r="B16" s="6">
         <v>390</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="35">
         <f t="shared" ref="C16:C20" si="6">C15</f>
         <v>0.153846153846154</v>
       </c>
@@ -3127,11 +3118,11 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="35">
         <f>AVERAGE(F$15:F16)</f>
         <v>0.071535468422628</v>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="35">
         <f t="shared" si="2"/>
         <v>0.0769230769230769</v>
       </c>
@@ -3142,7 +3133,7 @@
       <c r="H16" s="6">
         <v>360</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16" s="37">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
@@ -3157,7 +3148,7 @@
       <c r="B17" s="6">
         <v>484</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="35">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -3165,11 +3156,11 @@
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="35">
         <f>AVERAGE(F$15:F17)</f>
         <v>0.0752385216481432</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="35">
         <f t="shared" si="2"/>
         <v>0.0826446280991736</v>
       </c>
@@ -3180,7 +3171,7 @@
       <c r="H17" s="6">
         <v>444</v>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="37">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
@@ -3195,7 +3186,7 @@
       <c r="B18" s="6">
         <v>240</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="35">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -3203,11 +3194,11 @@
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="35">
         <f>AVERAGE(F$15:F18)</f>
         <v>0.0751788912361074</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="35">
         <f t="shared" si="2"/>
         <v>0.075</v>
       </c>
@@ -3218,7 +3209,7 @@
       <c r="H18" s="6">
         <v>222</v>
       </c>
-      <c r="I18" s="38">
+      <c r="I18" s="37">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
@@ -3233,7 +3224,7 @@
       <c r="B19" s="6">
         <v>271</v>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="35">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -3241,11 +3232,11 @@
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="35">
         <f>AVERAGE(F$15:F19)</f>
         <v>0.0741652532102881</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="35">
         <f t="shared" si="2"/>
         <v>0.0701107011070111</v>
       </c>
@@ -3256,7 +3247,7 @@
       <c r="H19" s="6">
         <v>252</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19" s="37">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
@@ -3271,7 +3262,7 @@
       <c r="B20" s="6">
         <v>278</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="35">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -3279,11 +3270,11 @@
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="35">
         <f>AVERAGE(F$15:F20)</f>
         <v>0.073794785349101</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="35">
         <f t="shared" si="2"/>
         <v>0.0719424460431655</v>
       </c>
@@ -3294,7 +3285,7 @@
       <c r="H20" s="6">
         <v>258</v>
       </c>
-      <c r="I20" s="38">
+      <c r="I20" s="37">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
@@ -3303,17 +3294,17 @@
       </c>
     </row>
     <row r="21" hidden="1" spans="1:10">
-      <c r="C21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
+      <c r="C21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
     </row>
     <row r="22" hidden="1" spans="1:10">
       <c r="A22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
+      <c r="C22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
     </row>
     <row r="23" hidden="1" spans="1:10">
       <c r="A23" s="6" t="s">
@@ -3354,7 +3345,7 @@
       <c r="B24" s="6">
         <v>440</v>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="35">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3362,11 +3353,11 @@
         <f t="shared" ref="D24:D28" si="7">ROUND(B24*C24,0)</f>
         <v>68</v>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="35">
         <f>AVERAGE(F$24:F24)</f>
         <v>0.0727272727272727</v>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="35">
         <f t="shared" ref="F24:F28" si="8">G24/B24</f>
         <v>0.0727272727272727</v>
       </c>
@@ -3377,7 +3368,7 @@
       <c r="H24" s="6">
         <v>408</v>
       </c>
-      <c r="I24" s="38">
+      <c r="I24" s="37">
         <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
         <v>440</v>
       </c>
@@ -3392,7 +3383,7 @@
       <c r="B25" s="6">
         <v>378</v>
       </c>
-      <c r="C25" s="36">
+      <c r="C25" s="35">
         <f t="shared" ref="C25:C28" si="11">C24</f>
         <v>0.153846153846154</v>
       </c>
@@ -3400,11 +3391,11 @@
         <f t="shared" si="7"/>
         <v>58</v>
       </c>
-      <c r="E25" s="36">
+      <c r="E25" s="35">
         <f>AVERAGE(F$24:F25)</f>
         <v>0.076046176046176</v>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="35">
         <f t="shared" si="8"/>
         <v>0.0793650793650794</v>
       </c>
@@ -3415,7 +3406,7 @@
       <c r="H25" s="6">
         <v>348</v>
       </c>
-      <c r="I25" s="38">
+      <c r="I25" s="37">
         <f t="shared" si="10"/>
         <v>378</v>
       </c>
@@ -3430,7 +3421,7 @@
       <c r="B26" s="6">
         <v>209</v>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="35">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -3438,11 +3429,11 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="35">
         <f>AVERAGE(F$24:F26)</f>
         <v>0.0778106883370041</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="35">
         <f t="shared" si="8"/>
         <v>0.0813397129186603</v>
       </c>
@@ -3453,7 +3444,7 @@
       <c r="H26" s="6">
         <v>192</v>
       </c>
-      <c r="I26" s="38">
+      <c r="I26" s="37">
         <f t="shared" si="10"/>
         <v>209</v>
       </c>
@@ -3468,7 +3459,7 @@
       <c r="B27" s="6">
         <v>62</v>
       </c>
-      <c r="C27" s="36">
+      <c r="C27" s="35">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -3476,11 +3467,11 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="35">
         <f>AVERAGE(F$24:F27)</f>
         <v>0.0664225323817854</v>
       </c>
-      <c r="F27" s="36">
+      <c r="F27" s="35">
         <f t="shared" si="8"/>
         <v>0.032258064516129</v>
       </c>
@@ -3491,7 +3482,7 @@
       <c r="H27" s="6">
         <v>60</v>
       </c>
-      <c r="I27" s="38">
+      <c r="I27" s="37">
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
@@ -3506,7 +3497,7 @@
       <c r="B28" s="6">
         <v>464</v>
       </c>
-      <c r="C28" s="36">
+      <c r="C28" s="35">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -3514,11 +3505,11 @@
         <f t="shared" si="7"/>
         <v>71</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="35">
         <f>AVERAGE(F$24:F28)</f>
         <v>0.0695173362502559</v>
       </c>
-      <c r="F28" s="36">
+      <c r="F28" s="35">
         <f t="shared" si="8"/>
         <v>0.0818965517241379</v>
       </c>
@@ -3529,7 +3520,7 @@
       <c r="H28" s="6">
         <v>426</v>
       </c>
-      <c r="I28" s="38">
+      <c r="I28" s="37">
         <f t="shared" si="10"/>
         <v>464</v>
       </c>
@@ -3538,9 +3529,9 @@
       </c>
     </row>
     <row r="29" hidden="1" spans="1:10">
-      <c r="C29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
+      <c r="C29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
     </row>
     <row r="30" hidden="1" spans="1:10">
       <c r="A30" s="6" t="s">
@@ -3586,7 +3577,7 @@
       <c r="B32" s="6">
         <v>132</v>
       </c>
-      <c r="C32" s="36">
+      <c r="C32" s="35">
         <f t="shared" ref="C32:C35" si="12">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3594,11 +3585,11 @@
         <f t="shared" ref="D32:D35" si="13">ROUND(B32*C32,0)</f>
         <v>20</v>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="35">
         <f>AVERAGE(F$32:F32)</f>
         <v>0.0909090909090909</v>
       </c>
-      <c r="F32" s="36">
+      <c r="F32" s="35">
         <f t="shared" ref="F32:F35" si="14">G32/B32</f>
         <v>0.0909090909090909</v>
       </c>
@@ -3609,7 +3600,7 @@
       <c r="H32" s="6">
         <v>120</v>
       </c>
-      <c r="I32" s="38">
+      <c r="I32" s="37">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
         <v>132</v>
       </c>
@@ -3624,7 +3615,7 @@
       <c r="B33" s="6">
         <v>30</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="35">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -3632,11 +3623,11 @@
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="35">
         <f>AVERAGE(F$32:F33)</f>
         <v>0.0454545454545455</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="35">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -3647,7 +3638,7 @@
       <c r="H33" s="6">
         <v>30</v>
       </c>
-      <c r="I33" s="38">
+      <c r="I33" s="37">
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
@@ -3662,7 +3653,7 @@
       <c r="B34" s="6">
         <v>395</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="35">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -3670,11 +3661,11 @@
         <f t="shared" si="13"/>
         <v>61</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="35">
         <f>AVERAGE(F$32:F34)</f>
         <v>0.0547756041426928</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="35">
         <f t="shared" si="14"/>
         <v>0.0734177215189873</v>
       </c>
@@ -3685,7 +3676,7 @@
       <c r="H34" s="6">
         <v>366</v>
       </c>
-      <c r="I34" s="38">
+      <c r="I34" s="37">
         <f t="shared" si="16"/>
         <v>395</v>
       </c>
@@ -3700,7 +3691,7 @@
       <c r="B35" s="6">
         <v>66</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="35">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -3708,11 +3699,11 @@
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="35">
         <f>AVERAGE(F$32:F35)</f>
         <v>0.0638089758342923</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="35">
         <f t="shared" si="14"/>
         <v>0.0909090909090909</v>
       </c>
@@ -3723,7 +3714,7 @@
       <c r="H35" s="6">
         <v>60</v>
       </c>
-      <c r="I35" s="38">
+      <c r="I35" s="37">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
@@ -3735,9 +3726,9 @@
       <c r="A37" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
+      <c r="C37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="33" t="s">
@@ -3779,7 +3770,7 @@
         <f>100+148</f>
         <v>248</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="35">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3787,27 +3778,27 @@
         <f>ROUND(B39*C39,0)</f>
         <v>38</v>
       </c>
-      <c r="E39" s="36">
+      <c r="E39" s="35">
         <f>AVERAGE(F$39:F39)</f>
-        <v>0.0725806451612903</v>
-      </c>
-      <c r="F39" s="36">
+        <v>0.0887096774193548</v>
+      </c>
+      <c r="F39" s="35">
         <f>G39/B39</f>
-        <v>0.0725806451612903</v>
+        <v>0.0887096774193548</v>
       </c>
       <c r="G39" s="6">
         <f>I39-H39</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H39" s="6">
         <v>38</v>
       </c>
-      <c r="I39" s="39">
+      <c r="I39" s="38">
         <f>MIN($J$38*D39,J39)</f>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J39" s="6">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3817,7 +3808,7 @@
       <c r="B40" s="6">
         <v>40</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="35">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3825,11 +3816,11 @@
         <f>ROUND(B40*C40,0)</f>
         <v>6</v>
       </c>
-      <c r="E40" s="36">
+      <c r="E40" s="35">
         <f>AVERAGE(F$39:F40)</f>
-        <v>0.111290322580645</v>
-      </c>
-      <c r="F40" s="36">
+        <v>0.119354838709677</v>
+      </c>
+      <c r="F40" s="35">
         <f>G40/B40</f>
         <v>0.15</v>
       </c>
@@ -3840,7 +3831,7 @@
       <c r="H40" s="6">
         <v>6</v>
       </c>
-      <c r="I40" s="38">
+      <c r="I40" s="37">
         <f>MIN($J$38*D40,J40)</f>
         <v>12</v>
       </c>
@@ -3853,9 +3844,9 @@
       <c r="A42" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
+      <c r="C42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
     </row>
     <row r="43" hidden="1" spans="1:10">
       <c r="A43" s="6" t="s">
@@ -3897,7 +3888,7 @@
         <f>212+52+63+30</f>
         <v>357</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="35">
         <f t="shared" ref="C44:C49" si="17">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3905,11 +3896,11 @@
         <f>ROUND(B44*C44,0)</f>
         <v>55</v>
       </c>
-      <c r="E44" s="36">
+      <c r="E44" s="35">
         <f>AVERAGE(F$44:F44)</f>
         <v>0.0756302521008403</v>
       </c>
-      <c r="F44" s="36">
+      <c r="F44" s="35">
         <f>G44/B44</f>
         <v>0.0756302521008403</v>
       </c>
@@ -3920,7 +3911,7 @@
       <c r="H44" s="6">
         <v>330</v>
       </c>
-      <c r="I44" s="38">
+      <c r="I44" s="37">
         <f>MIN($J$43*D44,J44)</f>
         <v>357</v>
       </c>
@@ -3934,9 +3925,9 @@
       <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
+      <c r="C46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
     </row>
     <row r="47" hidden="1" spans="1:10">
       <c r="A47" s="6" t="s">
@@ -3977,7 +3968,7 @@
       <c r="B48" s="6">
         <v>523</v>
       </c>
-      <c r="C48" s="36">
+      <c r="C48" s="35">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
@@ -3985,11 +3976,11 @@
         <f t="shared" ref="D48:D54" si="18">ROUND(B48*C48,0)</f>
         <v>80</v>
       </c>
-      <c r="E48" s="36">
+      <c r="E48" s="35">
         <f>AVERAGE(F$48:F48)</f>
         <v>0.0822179732313576</v>
       </c>
-      <c r="F48" s="36">
+      <c r="F48" s="35">
         <f t="shared" ref="F48:F54" si="19">G48/B48</f>
         <v>0.0822179732313576</v>
       </c>
@@ -4000,7 +3991,7 @@
       <c r="H48" s="6">
         <v>480</v>
       </c>
-      <c r="I48" s="38">
+      <c r="I48" s="37">
         <f t="shared" ref="I48:I54" si="21">MIN($J$47*D48,J48)</f>
         <v>523</v>
       </c>
@@ -4015,7 +4006,7 @@
       <c r="B49" s="6">
         <v>434</v>
       </c>
-      <c r="C49" s="36">
+      <c r="C49" s="35">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
@@ -4023,11 +4014,11 @@
         <f t="shared" si="18"/>
         <v>67</v>
       </c>
-      <c r="E49" s="36">
+      <c r="E49" s="35">
         <f>AVERAGE(F$48:F49)</f>
         <v>0.0779753460626834</v>
       </c>
-      <c r="F49" s="36">
+      <c r="F49" s="35">
         <f t="shared" si="19"/>
         <v>0.0737327188940092</v>
       </c>
@@ -4038,7 +4029,7 @@
       <c r="H49" s="6">
         <v>402</v>
       </c>
-      <c r="I49" s="38">
+      <c r="I49" s="37">
         <f t="shared" si="21"/>
         <v>434</v>
       </c>
@@ -4054,7 +4045,7 @@
         <f>26+83</f>
         <v>109</v>
       </c>
-      <c r="C50" s="36">
+      <c r="C50" s="35">
         <f t="shared" ref="C50:C60" si="22">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -4062,11 +4053,11 @@
         <f t="shared" si="18"/>
         <v>17</v>
       </c>
-      <c r="E50" s="36">
+      <c r="E50" s="35">
         <f>AVERAGE(F$48:F50)</f>
         <v>0.0733902918705351</v>
       </c>
-      <c r="F50" s="36">
+      <c r="F50" s="35">
         <f t="shared" si="19"/>
         <v>0.0642201834862385</v>
       </c>
@@ -4077,7 +4068,7 @@
       <c r="H50" s="6">
         <v>102</v>
       </c>
-      <c r="I50" s="38">
+      <c r="I50" s="37">
         <f t="shared" si="21"/>
         <v>109</v>
       </c>
@@ -4086,18 +4077,18 @@
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="C51" s="36"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
-      <c r="I51" s="39"/>
+      <c r="C51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="I51" s="38"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="36"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
+      <c r="C52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="6" t="s">
@@ -4132,13 +4123,13 @@
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="40" t="s">
+      <c r="A54" s="39" t="s">
         <v>45</v>
       </c>
       <c r="B54" s="6">
         <v>999</v>
       </c>
-      <c r="C54" s="36">
+      <c r="C54" s="35">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
@@ -4146,11 +4137,11 @@
         <f t="shared" ref="D54:D60" si="23">ROUND(B54*C54,0)</f>
         <v>154</v>
       </c>
-      <c r="E54" s="36">
+      <c r="E54" s="35">
         <f>AVERAGE(F$54:F54)</f>
         <v>0</v>
       </c>
-      <c r="F54" s="36">
+      <c r="F54" s="35">
         <f t="shared" ref="F54:F60" si="24">G54/B54</f>
         <v>0</v>
       </c>
@@ -4158,7 +4149,7 @@
         <f t="shared" ref="G54:G60" si="25">I54-H54</f>
         <v>0</v>
       </c>
-      <c r="I54" s="39">
+      <c r="I54" s="38">
         <f t="shared" ref="I54:I60" si="26">MIN($J$53*D54,J54)</f>
         <v>0</v>
       </c>
@@ -4167,13 +4158,13 @@
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="40" t="s">
+      <c r="A55" s="39" t="s">
         <v>46</v>
       </c>
       <c r="B55" s="6">
         <v>999</v>
       </c>
-      <c r="C55" s="36">
+      <c r="C55" s="35">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
@@ -4181,11 +4172,11 @@
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E55" s="36">
+      <c r="E55" s="35">
         <f>AVERAGE(F$54:F55)</f>
         <v>0</v>
       </c>
-      <c r="F55" s="36">
+      <c r="F55" s="35">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -4193,7 +4184,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I55" s="39">
+      <c r="I55" s="38">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
@@ -4202,13 +4193,13 @@
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="40" t="s">
+      <c r="A56" s="39" t="s">
         <v>47</v>
       </c>
       <c r="B56" s="6">
         <v>999</v>
       </c>
-      <c r="C56" s="36">
+      <c r="C56" s="35">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
@@ -4216,11 +4207,11 @@
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E56" s="36">
+      <c r="E56" s="35">
         <f>AVERAGE(F$54:F56)</f>
         <v>0</v>
       </c>
-      <c r="F56" s="36">
+      <c r="F56" s="35">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -4228,7 +4219,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I56" s="39">
+      <c r="I56" s="38">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
@@ -4237,13 +4228,13 @@
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="40" t="s">
+      <c r="A57" s="39" t="s">
         <v>48</v>
       </c>
       <c r="B57" s="6">
         <v>999</v>
       </c>
-      <c r="C57" s="36">
+      <c r="C57" s="35">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
@@ -4251,11 +4242,11 @@
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E57" s="36">
+      <c r="E57" s="35">
         <f>AVERAGE(F$54:F57)</f>
         <v>0</v>
       </c>
-      <c r="F57" s="36">
+      <c r="F57" s="35">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -4263,7 +4254,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I57" s="39">
+      <c r="I57" s="38">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
@@ -4272,13 +4263,13 @@
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="41" t="s">
+      <c r="A58" s="40" t="s">
         <v>49</v>
       </c>
       <c r="B58" s="6">
         <v>999</v>
       </c>
-      <c r="C58" s="36">
+      <c r="C58" s="35">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
@@ -4286,11 +4277,11 @@
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E58" s="36">
+      <c r="E58" s="35">
         <f>AVERAGE(F$54:F58)</f>
         <v>0</v>
       </c>
-      <c r="F58" s="36">
+      <c r="F58" s="35">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -4298,7 +4289,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I58" s="39">
+      <c r="I58" s="38">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
@@ -4307,13 +4298,13 @@
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="41" t="s">
+      <c r="A59" s="40" t="s">
         <v>50</v>
       </c>
       <c r="B59" s="6">
         <v>999</v>
       </c>
-      <c r="C59" s="36">
+      <c r="C59" s="35">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
@@ -4321,11 +4312,11 @@
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E59" s="36">
+      <c r="E59" s="35">
         <f>AVERAGE(F$54:F59)</f>
         <v>0</v>
       </c>
-      <c r="F59" s="36">
+      <c r="F59" s="35">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -4333,7 +4324,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I59" s="39">
+      <c r="I59" s="38">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
@@ -4342,13 +4333,13 @@
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="41" t="s">
+      <c r="A60" s="40" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="6">
         <v>999</v>
       </c>
-      <c r="C60" s="36">
+      <c r="C60" s="35">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
@@ -4356,11 +4347,11 @@
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E60" s="36">
+      <c r="E60" s="35">
         <f>AVERAGE(F$54:F60)</f>
         <v>0</v>
       </c>
-      <c r="F60" s="36">
+      <c r="F60" s="35">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -4368,7 +4359,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I60" s="39">
+      <c r="I60" s="38">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
@@ -4381,7 +4372,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A41:AR46 I39:I40 C39:G40 K38:AR40 A38:I38 A3:AR37 AL2:AR2 A2:AH2 A1:AR1 A47:I47 K48:AH48 A48:G50 I48:I50 B58:AR60 A57:AR57 K54:AR56 A54:I56 A51:AR53" formulaRange="1"/>
+    <ignoredError sqref="A51:AR53 A54:I56 K54:AR56 A57:AR57 B58:AR60 I48:I50 A48:G50 K48:AH48 A47:I47 A1:AR1 A2:AH2 AL2:AR2 A3:AR37 A38:I38 K38:AR40 C39:G40 I39:I40 A41:AR46" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4770,10 +4761,10 @@
       </c>
       <c r="B26" s="6">
         <f>SUM(C26:D26)</f>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C26" s="6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D26" s="6">
         <v>18</v>
@@ -4801,7 +4792,7 @@
       <c r="G27" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="H27" s="34" t="s">
+      <c r="H27" s="32" t="s">
         <v>116</v>
       </c>
     </row>

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="218">
   <si>
     <t>日期</t>
   </si>
@@ -317,6 +317,9 @@
     <t>陈双敏</t>
   </si>
   <si>
+    <t>程远志</t>
+  </si>
+  <si>
     <t>信号</t>
   </si>
   <si>
@@ -335,6 +338,12 @@
     <t>融合字词增强语义多注意力的医疗自动问答</t>
   </si>
   <si>
+    <t>A_Fast_Approach_to_Compute_Smooth_Geodesic_Distanc</t>
+  </si>
+  <si>
+    <t>Axis-Guided_Vessel_Segmentation_Using_a_Self-Const</t>
+  </si>
+  <si>
     <t>论文2</t>
   </si>
   <si>
@@ -347,6 +356,9 @@
     <t>基于强化学习的多策略HHO求解分布式混合流水车间调度</t>
   </si>
   <si>
+    <t>DeFillet_paper552</t>
+  </si>
+  <si>
     <t>网络</t>
   </si>
   <si>
@@ -365,6 +377,9 @@
     <t>基于改进人工蜂群算法的混合约束流水车间调度</t>
   </si>
   <si>
+    <t>ImS_implicit_shell_for_the_sandwich-walled_space_s</t>
+  </si>
+  <si>
     <t>论文4</t>
   </si>
   <si>
@@ -374,6 +389,12 @@
     <t>Optimizing_feature_map_matching_for_marine_benthic</t>
   </si>
   <si>
+    <t>分时期教学优化算法求解双目标分布式异构混合流水车间调度问题</t>
+  </si>
+  <si>
+    <t>RevolRecon_Neural_Representation_for_Reconstructin</t>
+  </si>
+  <si>
     <t>论文5</t>
   </si>
   <si>
@@ -381,6 +402,12 @@
   </si>
   <si>
     <t>Semi-supervised_medical_image_segmentation_with_di</t>
+  </si>
+  <si>
+    <t>多卷积模型结合注意力机制的水下图像增强方法及系统</t>
+  </si>
+  <si>
+    <t>Swept_Volume_Computation_with_Enhanced_Geometric_D</t>
   </si>
   <si>
     <t>正常电脑</t>
@@ -2197,10 +2224,10 @@
         <v>0.151612903225806</v>
       </c>
       <c r="AL2" s="35">
-        <v>0</v>
+        <v>0.151612903225806</v>
       </c>
       <c r="AM2" s="35">
-        <v>0</v>
+        <v>0.151612903225806</v>
       </c>
       <c r="AN2" s="35">
         <v>0</v>
@@ -2368,31 +2395,31 @@
       </c>
       <c r="AL3" s="35">
         <f>SUM($B2:AL2)</f>
-        <v>5.1516129032258</v>
+        <v>5.30322580645161</v>
       </c>
       <c r="AM3" s="35">
         <f>SUM($B2:AM2)</f>
-        <v>5.1516129032258</v>
+        <v>5.45483870967742</v>
       </c>
       <c r="AN3" s="35">
         <f>SUM($B2:AN2)</f>
-        <v>5.1516129032258</v>
+        <v>5.45483870967742</v>
       </c>
       <c r="AO3" s="35">
         <f>SUM($B2:AO2)</f>
-        <v>5.1516129032258</v>
+        <v>5.45483870967742</v>
       </c>
       <c r="AP3" s="35">
         <f>SUM($B2:AP2)</f>
-        <v>5.1516129032258</v>
+        <v>5.45483870967742</v>
       </c>
       <c r="AQ3" s="35">
         <f>SUM($B2:AQ2)</f>
-        <v>5.1516129032258</v>
+        <v>5.45483870967742</v>
       </c>
       <c r="AR3" s="35">
         <f>SUM($B2:AR2)</f>
-        <v>5.1516129032258</v>
+        <v>5.45483870967742</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -2545,31 +2572,31 @@
       </c>
       <c r="AL4" s="35">
         <f>AVERAGE($B2:AL2)</f>
-        <v>0.139232781168265</v>
+        <v>0.143330427201395</v>
       </c>
       <c r="AM4" s="35">
         <f>AVERAGE($B2:AM2)</f>
-        <v>0.135568760611205</v>
+        <v>0.143548387096774</v>
       </c>
       <c r="AN4" s="35">
         <f>AVERAGE($B2:AN2)</f>
-        <v>0.132092638544251</v>
+        <v>0.139867659222498</v>
       </c>
       <c r="AO4" s="35">
         <f>AVERAGE($B2:AO2)</f>
-        <v>0.128790322580645</v>
+        <v>0.136370967741935</v>
       </c>
       <c r="AP4" s="35">
         <f>AVERAGE($B2:AP2)</f>
-        <v>0.125649095200629</v>
+        <v>0.133044846577498</v>
       </c>
       <c r="AQ4" s="35">
         <f>AVERAGE($B2:AQ2)</f>
-        <v>0.122657450076805</v>
+        <v>0.129877112135177</v>
       </c>
       <c r="AR4" s="35">
         <f>AVERAGE($B2:AR2)</f>
-        <v>0.119804951237809</v>
+        <v>0.126856714178545</v>
       </c>
     </row>
     <row r="5" spans="1:44">
@@ -2895,15 +2922,15 @@
       </c>
       <c r="AK6" s="35">
         <f t="shared" si="1"/>
-        <v>0.00223325062034754</v>
+        <v>0.00223325062034799</v>
       </c>
       <c r="AL6" s="35">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>0.00223325062034799</v>
       </c>
       <c r="AM6" s="35">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>0.00223325062034754</v>
       </c>
       <c r="AN6" s="35">
         <f t="shared" si="1"/>
@@ -3759,7 +3786,7 @@
         <v>15</v>
       </c>
       <c r="J38" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -3780,25 +3807,25 @@
       </c>
       <c r="E39" s="35">
         <f>AVERAGE(F$39:F39)</f>
-        <v>0.0887096774193548</v>
+        <v>0.0120967741935484</v>
       </c>
       <c r="F39" s="35">
         <f>G39/B39</f>
-        <v>0.0887096774193548</v>
+        <v>0.0120967741935484</v>
       </c>
       <c r="G39" s="6">
         <f>I39-H39</f>
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="H39" s="6">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="I39" s="38">
         <f>MIN($J$38*D39,J39)</f>
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="J39" s="6">
-        <v>60</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3818,25 +3845,25 @@
       </c>
       <c r="E40" s="35">
         <f>AVERAGE(F$39:F40)</f>
-        <v>0.119354838709677</v>
+        <v>0.0185483870967742</v>
       </c>
       <c r="F40" s="35">
         <f>G40/B40</f>
-        <v>0.15</v>
+        <v>0.025</v>
       </c>
       <c r="G40" s="6">
         <f>I40-H40</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6">
-        <v>6</v>
-      </c>
-      <c r="I40" s="37">
+        <v>18</v>
+      </c>
+      <c r="I40" s="38">
         <f>MIN($J$38*D40,J40)</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J40" s="6">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" hidden="1"/>
@@ -4372,7 +4399,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A51:AR53 A54:I56 K54:AR56 A57:AR57 B58:AR60 I48:I50 A48:G50 K48:AH48 A47:I47 A1:AR1 A2:AH2 AL2:AR2 A3:AR37 A38:I38 K38:AR40 C39:G40 I39:I40 A41:AR46" formulaRange="1"/>
+    <ignoredError sqref="A41:AR46 I39:I40 C39:G40 K38:AR40 A38:I38 A3:AR37 AN2:AR2 A2:AH2 A1:AR1 A47:I47 K48:AH48 A48:G50 I48:I50 B58:AR60 A57:AR57 K54:AR56 A54:I56 A51:AR53" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4380,7 +4407,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="10.7777777777778" style="6" customWidth="1"/>
@@ -4595,7 +4622,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:10">
+    <row r="17" hidden="1" spans="1:11">
       <c r="A17" s="6" t="s">
         <v>34</v>
       </c>
@@ -4606,7 +4633,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:10">
+    <row r="18" hidden="1" spans="1:11">
       <c r="A18" s="6" t="s">
         <v>85</v>
       </c>
@@ -4614,7 +4641,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:10">
+    <row r="19" hidden="1" spans="1:11">
       <c r="C19" s="6" t="s">
         <v>86</v>
       </c>
@@ -4634,7 +4661,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:10">
+    <row r="20" hidden="1" spans="1:11">
       <c r="A20" s="6" t="s">
         <v>40</v>
       </c>
@@ -4662,7 +4689,7 @@
       </c>
     </row>
     <row r="21" hidden="1"/>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:11">
       <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
@@ -4681,8 +4708,11 @@
       <c r="J22" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="6" t="s">
         <v>42</v>
       </c>
@@ -4690,25 +4720,31 @@
         <v>434</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G23" s="32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>101</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="6" t="s">
         <v>43</v>
       </c>
@@ -4723,77 +4759,95 @@
         <v>83</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G24" s="32" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I24" s="32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>107</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="C25" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G25" s="32" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I25" s="32" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>114</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="33" t="s">
         <v>37</v>
       </c>
       <c r="B26" s="6">
         <f>SUM(C26:D26)</f>
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="C26" s="6">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D26" s="6">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G26" s="32" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H26" s="32" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>118</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="33" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="6">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G27" s="32" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -4822,89 +4876,89 @@
   <sheetData>
     <row r="1" ht="15.15" spans="1:4">
       <c r="A1" s="7" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:4">
       <c r="A2" s="11" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="15.15" spans="1:4">
       <c r="A3" s="10" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" ht="15.15" spans="1:4">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:4">
       <c r="A6" s="13" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:4">
       <c r="A7" s="21" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -4912,44 +4966,44 @@
     </row>
     <row r="8" ht="15.15" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" ht="15.15" spans="1:4">
       <c r="A9" s="25" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="10" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:4">
@@ -4960,30 +5014,30 @@
     </row>
     <row r="12" ht="15.15" spans="1:4">
       <c r="A12" s="7" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:4">
       <c r="A13" s="13" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -5017,106 +5071,106 @@
   <sheetData>
     <row r="1" ht="15.15" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" ht="15.15" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" ht="15.15" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" ht="15.15"/>
     <row r="8" ht="15.15" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" ht="15.15" spans="1:7">
       <c r="A9" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C9" s="2">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E9" s="2">
         <v>26.8</v>
@@ -5125,19 +5179,19 @@
         <v>39.9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" ht="15.15" spans="1:7">
       <c r="A10" s="4"/>
       <c r="B10" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C10" s="2">
         <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E10" s="2">
         <v>31.6</v>
@@ -5146,19 +5200,19 @@
         <v>40.1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:7">
       <c r="A11" s="4"/>
       <c r="B11" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C11" s="2">
         <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E11" s="2">
         <v>26.3</v>
@@ -5167,19 +5221,19 @@
         <v>39.2</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" ht="15.15" spans="1:7">
       <c r="A12" s="5"/>
       <c r="B12" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C12" s="2">
         <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E12" s="2">
         <v>26.3</v>
@@ -5188,21 +5242,21 @@
         <v>40.1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:7">
       <c r="A13" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C13" s="2">
         <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="E13" s="2">
         <v>8.2</v>
@@ -5217,13 +5271,13 @@
     <row r="14" ht="15.15" spans="1:7">
       <c r="A14" s="4"/>
       <c r="B14" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C14" s="2">
         <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="E14" s="2">
         <v>10.3</v>
@@ -5232,19 +5286,19 @@
         <v>17.1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" ht="15.15" spans="1:7">
       <c r="A15" s="4"/>
       <c r="B15" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2">
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="E15" s="2">
         <v>11.2</v>
@@ -5253,19 +5307,19 @@
         <v>19.3</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" ht="15.15" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2">
         <v>75</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E16" s="2">
         <v>8.2</v>
@@ -5274,45 +5328,45 @@
         <v>19.3</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" ht="15.15"/>
     <row r="18" ht="15.15" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" ht="15.15" spans="1:7">
       <c r="A19" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2">
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="E19" s="2">
         <v>20.55</v>
@@ -5321,19 +5375,19 @@
         <v>47.12</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" ht="15.15" spans="1:7">
       <c r="A20" s="4"/>
       <c r="B20" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2">
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="E20" s="2">
         <v>29.18</v>
@@ -5342,19 +5396,19 @@
         <v>48.1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" ht="15.15" spans="1:7">
       <c r="A21" s="4"/>
       <c r="B21" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C21" s="2">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E21" s="2">
         <v>33.77</v>
@@ -5363,19 +5417,19 @@
         <v>56.1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" ht="15.15" spans="1:7">
       <c r="A22" s="5"/>
       <c r="B22" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C22" s="2">
         <v>75</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E22" s="2">
         <v>20.55</v>
@@ -5384,39 +5438,39 @@
         <v>56.1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" ht="15.15"/>
     <row r="24" ht="15.15" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" ht="15.15" spans="1:7">
       <c r="A25" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D25" s="2">
         <v>-0.4876</v>
@@ -5431,10 +5485,10 @@
     <row r="26" ht="15.15" spans="1:7">
       <c r="A26" s="4"/>
       <c r="B26" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D26" s="2">
         <v>-5.3084</v>
@@ -5443,16 +5497,16 @@
         <v>1.63428</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" ht="15.15" spans="1:7">
       <c r="A27" s="4"/>
       <c r="B27" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D27" s="2">
         <v>0.4876</v>
@@ -5467,10 +5521,10 @@
     <row r="28" ht="15.15" spans="1:7">
       <c r="A28" s="4"/>
       <c r="B28" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D28" s="2">
         <v>-4.8208</v>
@@ -5479,16 +5533,16 @@
         <v>1.63428</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" ht="15.15" spans="1:7">
       <c r="A29" s="4"/>
       <c r="B29" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D29" s="2">
         <v>5.3084</v>
@@ -5497,16 +5551,16 @@
         <v>1.63428</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" ht="15.15" spans="1:7">
       <c r="A30" s="5"/>
       <c r="B30" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D30" s="2">
         <v>4.8208</v>
@@ -5515,18 +5569,18 @@
         <v>1.63428</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" ht="15.15" spans="1:7">
       <c r="A31" s="3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D31" s="2">
         <v>-0.452</v>
@@ -5541,10 +5595,10 @@
     <row r="32" ht="15.15" spans="1:7">
       <c r="A32" s="4"/>
       <c r="B32" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D32" s="2">
         <v>2.26</v>
@@ -5553,16 +5607,16 @@
         <v>0.81249</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" ht="15.15" spans="1:6">
       <c r="A33" s="4"/>
       <c r="B33" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D33" s="2">
         <v>0.452</v>
@@ -5577,10 +5631,10 @@
     <row r="34" ht="15.15" spans="1:6">
       <c r="A34" s="4"/>
       <c r="B34" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D34" s="2">
         <v>2.712</v>
@@ -5589,16 +5643,16 @@
         <v>0.81249</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" ht="15.15" spans="1:6">
       <c r="A35" s="4"/>
       <c r="B35" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D35" s="2">
         <v>-2.26</v>
@@ -5607,16 +5661,16 @@
         <v>0.81249</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" ht="15.15" spans="1:6">
       <c r="A36" s="5"/>
       <c r="B36" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D36" s="2">
         <v>-2.712</v>
@@ -5625,7 +5679,7 @@
         <v>0.81249</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="239">
   <si>
     <t>日期</t>
   </si>
@@ -167,7 +167,7 @@
     <t>青岛科技</t>
   </si>
   <si>
-    <t>矩阵理论</t>
+    <t>概统应用</t>
   </si>
   <si>
     <t>人工智能</t>
@@ -320,6 +320,15 @@
     <t>程远志</t>
   </si>
   <si>
+    <t>段利亚</t>
+  </si>
+  <si>
+    <t>宋廷强</t>
+  </si>
+  <si>
+    <t>王鑫</t>
+  </si>
+  <si>
     <t>信号</t>
   </si>
   <si>
@@ -344,6 +353,15 @@
     <t>Axis-Guided_Vessel_Segmentation_Using_a_Self-Const</t>
   </si>
   <si>
+    <t>多卷积模型结合注意力机制的水下图像增强方法及系统</t>
+  </si>
+  <si>
+    <t>Development_and_external_validation_of_a_non-invas</t>
+  </si>
+  <si>
+    <t>人工智能技术在现代普外科中的应用进展</t>
+  </si>
+  <si>
     <t>论文2</t>
   </si>
   <si>
@@ -359,6 +377,18 @@
     <t>DeFillet_paper552</t>
   </si>
   <si>
+    <t>Foreground_Background_Difference_Knowledge-Based_S</t>
+  </si>
+  <si>
+    <t>基于希尔伯特变换和改进卷积神经网络的通用水声信号解调方法</t>
+  </si>
+  <si>
+    <t>Integrating_Contrastive_Learning_and_Cycle_Generat</t>
+  </si>
+  <si>
+    <t>细粒度学习能力增强的可解释知识追踪</t>
+  </si>
+  <si>
     <t>网络</t>
   </si>
   <si>
@@ -380,6 +410,18 @@
     <t>ImS_implicit_shell_for_the_sandwich-walled_space_s</t>
   </si>
   <si>
+    <t>Patient-specific_probabilistic_atlas_combining_mod</t>
+  </si>
+  <si>
+    <t>基于旋转体曲面重构的绝缘子缺陷检测方法</t>
+  </si>
+  <si>
+    <t>MAMIFusion_a_multimodal_data_fusion_framework_base</t>
+  </si>
+  <si>
+    <t>一种多孔介质微孔结构提取方法及应用</t>
+  </si>
+  <si>
     <t>论文4</t>
   </si>
   <si>
@@ -395,6 +437,18 @@
     <t>RevolRecon_Neural_Representation_for_Reconstructin</t>
   </si>
   <si>
+    <t>Vector_Field_Convolution-Based_B-Spline_Deformatio</t>
+  </si>
+  <si>
+    <t>一种基于浅层神经网络的水下图像增强方法</t>
+  </si>
+  <si>
+    <t>Spatial-Spectral_Contrastive_Graph_Neural_Network_</t>
+  </si>
+  <si>
+    <t>一种基于机器学习的图像中心线结构提取方法</t>
+  </si>
+  <si>
     <t>论文5</t>
   </si>
   <si>
@@ -404,10 +458,19 @@
     <t>Semi-supervised_medical_image_segmentation_with_di</t>
   </si>
   <si>
-    <t>多卷积模型结合注意力机制的水下图像增强方法及系统</t>
-  </si>
-  <si>
     <t>Swept_Volume_Computation_with_Enhanced_Geometric_D</t>
+  </si>
+  <si>
+    <t>WangProbAtlasIJCARS2015</t>
+  </si>
+  <si>
+    <t>一种双引导的水下图像多尺度增强方法</t>
+  </si>
+  <si>
+    <t>YOLOv11-Hunter_Detection_of_Threats_by_Unmanned_Ae</t>
+  </si>
+  <si>
+    <t>一种基于深度学习的海底钻井电成像图像修复方法</t>
   </si>
   <si>
     <t>正常电脑</t>
@@ -2230,13 +2293,13 @@
         <v>0.151612903225806</v>
       </c>
       <c r="AN2" s="35">
-        <v>0</v>
+        <v>0.151612903225806</v>
       </c>
       <c r="AO2" s="35">
-        <v>0</v>
+        <v>0.151612903225806</v>
       </c>
       <c r="AP2" s="35">
-        <v>0</v>
+        <v>0.151612903225806</v>
       </c>
       <c r="AQ2" s="35">
         <v>0</v>
@@ -2403,23 +2466,23 @@
       </c>
       <c r="AN3" s="35">
         <f>SUM($B2:AN2)</f>
-        <v>5.45483870967742</v>
+        <v>5.60645161290322</v>
       </c>
       <c r="AO3" s="35">
         <f>SUM($B2:AO2)</f>
-        <v>5.45483870967742</v>
+        <v>5.75806451612903</v>
       </c>
       <c r="AP3" s="35">
         <f>SUM($B2:AP2)</f>
-        <v>5.45483870967742</v>
+        <v>5.90967741935483</v>
       </c>
       <c r="AQ3" s="35">
         <f>SUM($B2:AQ2)</f>
-        <v>5.45483870967742</v>
+        <v>5.90967741935483</v>
       </c>
       <c r="AR3" s="35">
         <f>SUM($B2:AR2)</f>
-        <v>5.45483870967742</v>
+        <v>5.90967741935483</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -2580,23 +2643,23 @@
       </c>
       <c r="AN4" s="35">
         <f>AVERAGE($B2:AN2)</f>
-        <v>0.139867659222498</v>
+        <v>0.143755169561621</v>
       </c>
       <c r="AO4" s="35">
         <f>AVERAGE($B2:AO2)</f>
-        <v>0.136370967741935</v>
+        <v>0.143951612903226</v>
       </c>
       <c r="AP4" s="35">
         <f>AVERAGE($B2:AP2)</f>
-        <v>0.133044846577498</v>
+        <v>0.144138473642801</v>
       </c>
       <c r="AQ4" s="35">
         <f>AVERAGE($B2:AQ2)</f>
-        <v>0.129877112135177</v>
+        <v>0.140706605222734</v>
       </c>
       <c r="AR4" s="35">
         <f>AVERAGE($B2:AR2)</f>
-        <v>0.126856714178545</v>
+        <v>0.137434358589647</v>
       </c>
     </row>
     <row r="5" spans="1:44">
@@ -2930,19 +2993,19 @@
       </c>
       <c r="AM6" s="35">
         <f t="shared" si="1"/>
-        <v>0.00223325062034754</v>
+        <v>0.00223325062034799</v>
       </c>
       <c r="AN6" s="35">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>0.00223325062034799</v>
       </c>
       <c r="AO6" s="35">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>0.00223325062034799</v>
       </c>
       <c r="AP6" s="35">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
+        <v>0.00223325062034754</v>
       </c>
       <c r="AQ6" s="35">
         <f t="shared" si="1"/>
@@ -3786,7 +3849,7 @@
         <v>15</v>
       </c>
       <c r="J38" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -3818,14 +3881,14 @@
         <v>3</v>
       </c>
       <c r="H39" s="6">
-        <v>114</v>
+        <v>228</v>
       </c>
       <c r="I39" s="38">
         <f>MIN($J$38*D39,J39)</f>
-        <v>117</v>
+        <v>231</v>
       </c>
       <c r="J39" s="6">
-        <v>117</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -3845,25 +3908,25 @@
       </c>
       <c r="E40" s="35">
         <f>AVERAGE(F$39:F40)</f>
-        <v>0.0185483870967742</v>
+        <v>0.0560483870967742</v>
       </c>
       <c r="F40" s="35">
         <f>G40/B40</f>
-        <v>0.025</v>
+        <v>0.1</v>
       </c>
       <c r="G40" s="6">
         <f>I40-H40</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H40" s="6">
-        <v>18</v>
-      </c>
-      <c r="I40" s="38">
+        <v>36</v>
+      </c>
+      <c r="I40" s="37">
         <f>MIN($J$38*D40,J40)</f>
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J40" s="6">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" hidden="1"/>
@@ -4399,7 +4462,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A41:AR46 I39:I40 C39:G40 K38:AR40 A38:I38 A3:AR37 AN2:AR2 A2:AH2 A1:AR1 A47:I47 K48:AH48 A48:G50 I48:I50 B58:AR60 A57:AR57 K54:AR56 A54:I56 A51:AR53" formulaRange="1"/>
+    <ignoredError sqref="A41:AR46 I39:I40 C39:G40 K38:AR40 A38:I38 A3:AR37 AQ2:AR2 A2:AH2 A1:AR1 A47:I47 K48:AH48 A48:G50 I48:I50 B58:AR60 A57:AR57 K54:AR56 A55:I56 B54:I54 A51:AR53" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4407,7 +4470,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="10.7777777777778" style="6" customWidth="1"/>
@@ -4622,7 +4685,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:11">
+    <row r="17" hidden="1" spans="1:14">
       <c r="A17" s="6" t="s">
         <v>34</v>
       </c>
@@ -4633,7 +4696,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:11">
+    <row r="18" hidden="1" spans="1:14">
       <c r="A18" s="6" t="s">
         <v>85</v>
       </c>
@@ -4641,7 +4704,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:11">
+    <row r="19" hidden="1" spans="1:14">
       <c r="C19" s="6" t="s">
         <v>86</v>
       </c>
@@ -4661,7 +4724,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:11">
+    <row r="20" hidden="1" spans="1:14">
       <c r="A20" s="6" t="s">
         <v>40</v>
       </c>
@@ -4689,7 +4752,7 @@
       </c>
     </row>
     <row r="21" hidden="1"/>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:14">
       <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
@@ -4711,8 +4774,17 @@
       <c r="K22" s="6" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="6" t="s">
         <v>42</v>
       </c>
@@ -4720,31 +4792,40 @@
         <v>434</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G23" s="32" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J23" s="32" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K23" s="32" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>106</v>
+      </c>
+      <c r="L23" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="M23" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="N23" s="32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="6" t="s">
         <v>43</v>
       </c>
@@ -4759,95 +4840,143 @@
         <v>83</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G24" s="32" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I24" s="32" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J24" s="32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>114</v>
+      </c>
+      <c r="K24" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="L24" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="M24" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="N24" s="32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="C25" s="6" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G25" s="32" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="I25" s="32" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="J25" s="32" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>125</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="L25" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="M25" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="N25" s="32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="33" t="s">
         <v>37</v>
       </c>
       <c r="B26" s="6">
         <f>SUM(C26:D26)</f>
-        <v>117</v>
+        <v>231</v>
       </c>
       <c r="C26" s="6">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="D26" s="6">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="G26" s="32" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H26" s="32" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="I26" s="32" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="J26" s="32" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>134</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="L26" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="M26" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="N26" s="32" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="33" t="s">
         <v>38</v>
       </c>
       <c r="B27" s="6">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="G27" s="32" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="I27" s="32" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="J27" s="32" t="s">
-        <v>125</v>
+        <v>142</v>
+      </c>
+      <c r="K27" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="L27" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="M27" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="N27" s="32" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -4876,89 +5005,89 @@
   <sheetData>
     <row r="1" ht="15.15" spans="1:4">
       <c r="A1" s="7" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:4">
       <c r="A2" s="11" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" ht="15.15" spans="1:4">
       <c r="A3" s="10" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="15.15" spans="1:4">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:4">
       <c r="A6" s="13" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" ht="15.15" spans="1:4">
       <c r="A7" s="21" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -4966,44 +5095,44 @@
     </row>
     <row r="8" ht="15.15" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" ht="15.15" spans="1:4">
       <c r="A9" s="25" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="10" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:4">
@@ -5014,30 +5143,30 @@
     </row>
     <row r="12" ht="15.15" spans="1:4">
       <c r="A12" s="7" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:4">
       <c r="A13" s="13" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -5071,106 +5200,106 @@
   <sheetData>
     <row r="1" ht="15.15" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" ht="15.15" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" ht="15.15" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" ht="15.15" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" ht="15.15" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" ht="15.15" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" ht="15.15"/>
     <row r="8" ht="15.15" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" ht="15.15" spans="1:7">
       <c r="A9" s="3" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C9" s="2">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="E9" s="2">
         <v>26.8</v>
@@ -5179,19 +5308,19 @@
         <v>39.9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" ht="15.15" spans="1:7">
       <c r="A10" s="4"/>
       <c r="B10" s="2" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="C10" s="2">
         <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="E10" s="2">
         <v>31.6</v>
@@ -5200,19 +5329,19 @@
         <v>40.1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" ht="15.15" spans="1:7">
       <c r="A11" s="4"/>
       <c r="B11" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C11" s="2">
         <v>25</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="E11" s="2">
         <v>26.3</v>
@@ -5221,19 +5350,19 @@
         <v>39.2</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" ht="15.15" spans="1:7">
       <c r="A12" s="5"/>
       <c r="B12" s="2" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="C12" s="2">
         <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="E12" s="2">
         <v>26.3</v>
@@ -5242,21 +5371,21 @@
         <v>40.1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" ht="15.15" spans="1:7">
       <c r="A13" s="3" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C13" s="2">
         <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="E13" s="2">
         <v>8.2</v>
@@ -5271,13 +5400,13 @@
     <row r="14" ht="15.15" spans="1:7">
       <c r="A14" s="4"/>
       <c r="B14" s="2" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="C14" s="2">
         <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="E14" s="2">
         <v>10.3</v>
@@ -5286,19 +5415,19 @@
         <v>17.1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" ht="15.15" spans="1:7">
       <c r="A15" s="4"/>
       <c r="B15" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C15" s="2">
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="E15" s="2">
         <v>11.2</v>
@@ -5307,19 +5436,19 @@
         <v>19.3</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" ht="15.15" spans="1:7">
       <c r="A16" s="5"/>
       <c r="B16" s="2" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="C16" s="2">
         <v>75</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="E16" s="2">
         <v>8.2</v>
@@ -5328,45 +5457,45 @@
         <v>19.3</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" ht="15.15"/>
     <row r="18" ht="15.15" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" ht="15.15" spans="1:7">
       <c r="A19" s="3" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2">
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="E19" s="2">
         <v>20.55</v>
@@ -5375,19 +5504,19 @@
         <v>47.12</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" ht="15.15" spans="1:7">
       <c r="A20" s="4"/>
       <c r="B20" s="2" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2">
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="E20" s="2">
         <v>29.18</v>
@@ -5396,19 +5525,19 @@
         <v>48.1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" ht="15.15" spans="1:7">
       <c r="A21" s="4"/>
       <c r="B21" s="2" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C21" s="2">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="E21" s="2">
         <v>33.77</v>
@@ -5417,19 +5546,19 @@
         <v>56.1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" ht="15.15" spans="1:7">
       <c r="A22" s="5"/>
       <c r="B22" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2">
         <v>75</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="E22" s="2">
         <v>20.55</v>
@@ -5438,39 +5567,39 @@
         <v>56.1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" ht="15.15"/>
     <row r="24" ht="15.15" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" ht="15.15" spans="1:7">
       <c r="A25" s="3" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="D25" s="2">
         <v>-0.4876</v>
@@ -5485,10 +5614,10 @@
     <row r="26" ht="15.15" spans="1:7">
       <c r="A26" s="4"/>
       <c r="B26" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="D26" s="2">
         <v>-5.3084</v>
@@ -5497,16 +5626,16 @@
         <v>1.63428</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" ht="15.15" spans="1:7">
       <c r="A27" s="4"/>
       <c r="B27" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="D27" s="2">
         <v>0.4876</v>
@@ -5521,10 +5650,10 @@
     <row r="28" ht="15.15" spans="1:7">
       <c r="A28" s="4"/>
       <c r="B28" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="D28" s="2">
         <v>-4.8208</v>
@@ -5533,16 +5662,16 @@
         <v>1.63428</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29" ht="15.15" spans="1:7">
       <c r="A29" s="4"/>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="D29" s="2">
         <v>5.3084</v>
@@ -5551,16 +5680,16 @@
         <v>1.63428</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" ht="15.15" spans="1:7">
       <c r="A30" s="5"/>
       <c r="B30" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="D30" s="2">
         <v>4.8208</v>
@@ -5569,18 +5698,18 @@
         <v>1.63428</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" ht="15.15" spans="1:7">
       <c r="A31" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="D31" s="2">
         <v>-0.452</v>
@@ -5595,10 +5724,10 @@
     <row r="32" ht="15.15" spans="1:7">
       <c r="A32" s="4"/>
       <c r="B32" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="D32" s="2">
         <v>2.26</v>
@@ -5607,16 +5736,16 @@
         <v>0.81249</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" ht="15.15" spans="1:6">
       <c r="A33" s="4"/>
       <c r="B33" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="D33" s="2">
         <v>0.452</v>
@@ -5631,10 +5760,10 @@
     <row r="34" ht="15.15" spans="1:6">
       <c r="A34" s="4"/>
       <c r="B34" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="D34" s="2">
         <v>2.712</v>
@@ -5643,16 +5772,16 @@
         <v>0.81249</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" ht="15.15" spans="1:6">
       <c r="A35" s="4"/>
       <c r="B35" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="D35" s="2">
         <v>-2.26</v>
@@ -5661,16 +5790,16 @@
         <v>0.81249</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" ht="15.15" spans="1:6">
       <c r="A36" s="5"/>
       <c r="B36" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="D36" s="2">
         <v>-2.712</v>
@@ -5679,7 +5808,7 @@
         <v>0.81249</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="239">
   <si>
     <t>日期</t>
   </si>
@@ -784,6 +784,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -792,14 +800,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1700,25 +1700,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2032,997 +2032,1195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AR60"/>
+  <dimension ref="A1:BA60"/>
   <sheetFormatPr defaultColWidth="15.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="10" width="15.7777777777778" style="6" customWidth="1"/>
-    <col min="11" max="36" width="15.7777777777778" style="6" hidden="1" customWidth="1"/>
-    <col min="37" max="16384" width="15.7777777777778" style="6" customWidth="1"/>
+    <col min="11" max="42" width="15.7777777777778" style="6" hidden="1" customWidth="1"/>
+    <col min="43" max="16384" width="15.7777777777778" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44">
+    <row r="1" spans="1:53">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34">
+      <c r="B1" s="36">
         <v>46081</v>
       </c>
-      <c r="C1" s="34">
+      <c r="C1" s="36">
         <v>46082</v>
       </c>
-      <c r="D1" s="34">
+      <c r="D1" s="36">
         <v>46083</v>
       </c>
-      <c r="E1" s="34">
+      <c r="E1" s="36">
         <v>46084</v>
       </c>
-      <c r="F1" s="34">
+      <c r="F1" s="36">
         <v>46085</v>
       </c>
-      <c r="G1" s="34">
+      <c r="G1" s="36">
         <v>46086</v>
       </c>
-      <c r="H1" s="34">
+      <c r="H1" s="36">
         <v>46087</v>
       </c>
-      <c r="I1" s="34">
+      <c r="I1" s="36">
         <v>46088</v>
       </c>
-      <c r="J1" s="34">
+      <c r="J1" s="36">
         <v>46089</v>
       </c>
-      <c r="K1" s="34">
+      <c r="K1" s="36">
         <v>46090</v>
       </c>
-      <c r="L1" s="34">
+      <c r="L1" s="36">
         <v>46091</v>
       </c>
-      <c r="M1" s="34">
+      <c r="M1" s="36">
         <v>46092</v>
       </c>
-      <c r="N1" s="34">
+      <c r="N1" s="36">
         <v>46093</v>
       </c>
-      <c r="O1" s="34">
+      <c r="O1" s="36">
         <v>46094</v>
       </c>
-      <c r="P1" s="34">
+      <c r="P1" s="36">
         <v>46095</v>
       </c>
-      <c r="Q1" s="34">
+      <c r="Q1" s="36">
         <v>46096</v>
       </c>
-      <c r="R1" s="34">
+      <c r="R1" s="36">
         <v>46097</v>
       </c>
-      <c r="S1" s="34">
+      <c r="S1" s="36">
         <v>46098</v>
       </c>
-      <c r="T1" s="34">
+      <c r="T1" s="36">
         <v>46099</v>
       </c>
-      <c r="U1" s="34">
+      <c r="U1" s="36">
         <v>46100</v>
       </c>
-      <c r="V1" s="34">
+      <c r="V1" s="36">
         <v>46101</v>
       </c>
-      <c r="W1" s="34">
+      <c r="W1" s="36">
         <v>46102</v>
       </c>
-      <c r="X1" s="34">
+      <c r="X1" s="36">
         <v>46103</v>
       </c>
-      <c r="Y1" s="34">
+      <c r="Y1" s="36">
         <v>46104</v>
       </c>
-      <c r="Z1" s="34">
+      <c r="Z1" s="36">
         <v>46105</v>
       </c>
-      <c r="AA1" s="34">
+      <c r="AA1" s="36">
         <v>46106</v>
       </c>
-      <c r="AB1" s="34">
+      <c r="AB1" s="36">
         <v>46107</v>
       </c>
-      <c r="AC1" s="34">
+      <c r="AC1" s="36">
         <v>46108</v>
       </c>
-      <c r="AD1" s="34">
+      <c r="AD1" s="36">
         <v>46109</v>
       </c>
-      <c r="AE1" s="34">
+      <c r="AE1" s="36">
         <v>46110</v>
       </c>
-      <c r="AF1" s="34">
+      <c r="AF1" s="36">
         <v>46111</v>
       </c>
-      <c r="AG1" s="34">
+      <c r="AG1" s="36">
         <v>46112</v>
       </c>
-      <c r="AH1" s="34">
+      <c r="AH1" s="36">
         <v>46113</v>
       </c>
-      <c r="AI1" s="34">
+      <c r="AI1" s="36">
         <v>46114</v>
       </c>
-      <c r="AJ1" s="34">
+      <c r="AJ1" s="36">
         <v>46115</v>
       </c>
-      <c r="AK1" s="34">
+      <c r="AK1" s="36">
         <v>46116</v>
       </c>
-      <c r="AL1" s="34">
+      <c r="AL1" s="36">
         <v>46117</v>
       </c>
-      <c r="AM1" s="34">
+      <c r="AM1" s="36">
         <v>46118</v>
       </c>
-      <c r="AN1" s="34">
+      <c r="AN1" s="36">
         <v>46119</v>
       </c>
-      <c r="AO1" s="34">
+      <c r="AO1" s="36">
         <v>46120</v>
       </c>
-      <c r="AP1" s="34">
+      <c r="AP1" s="36">
         <v>46121</v>
       </c>
-      <c r="AQ1" s="34">
+      <c r="AQ1" s="36">
         <v>46122</v>
       </c>
-      <c r="AR1" s="34">
+      <c r="AR1" s="36">
         <v>46123</v>
       </c>
-    </row>
-    <row r="2" spans="1:44">
+      <c r="AS1" s="36">
+        <v>46124</v>
+      </c>
+      <c r="AT1" s="36">
+        <v>46125</v>
+      </c>
+      <c r="AU1" s="36">
+        <v>46126</v>
+      </c>
+      <c r="AV1" s="36">
+        <v>46127</v>
+      </c>
+      <c r="AW1" s="36">
+        <v>46128</v>
+      </c>
+      <c r="AX1" s="36">
+        <v>46129</v>
+      </c>
+      <c r="AY1" s="36">
+        <v>46130</v>
+      </c>
+      <c r="AZ1" s="36">
+        <v>46131</v>
+      </c>
+      <c r="BA1" s="36">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="37">
         <v>0.15436753577515</v>
       </c>
-      <c r="C2" s="35">
+      <c r="C2" s="37">
         <v>0.15436753577515</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="37">
         <v>0.15436753577515</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="37">
         <v>0.15436753577515</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="37">
         <v>0.15436753577515</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="38">
         <v>0.15436753577515</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="37">
         <v>0.073794785349101</v>
       </c>
-      <c r="I2" s="36">
+      <c r="I2" s="38">
         <v>0.155080443958291</v>
       </c>
-      <c r="J2" s="36">
+      <c r="J2" s="38">
         <v>0.155080443958291</v>
       </c>
-      <c r="K2" s="35">
+      <c r="K2" s="37">
         <v>0.155080443958291</v>
       </c>
-      <c r="L2" s="35">
+      <c r="L2" s="37">
         <v>0.155080443958291</v>
       </c>
-      <c r="M2" s="35">
+      <c r="M2" s="37">
         <v>0.155080443958291</v>
       </c>
-      <c r="N2" s="35">
+      <c r="N2" s="37">
         <v>0.155080443958291</v>
       </c>
-      <c r="O2" s="35">
+      <c r="O2" s="37">
         <v>0.0695173362502559</v>
       </c>
-      <c r="P2" s="36">
+      <c r="P2" s="38">
         <v>0.15406162464986</v>
       </c>
-      <c r="Q2" s="35">
+      <c r="Q2" s="37">
         <v>0.15406162464986</v>
       </c>
-      <c r="R2" s="35">
+      <c r="R2" s="37">
         <v>0.15406162464986</v>
       </c>
-      <c r="S2" s="35">
+      <c r="S2" s="37">
         <v>0.15406162464986</v>
       </c>
-      <c r="T2" s="35">
+      <c r="T2" s="37">
         <v>0.15406162464986</v>
       </c>
-      <c r="U2" s="35">
+      <c r="U2" s="37">
         <v>0.15406162464986</v>
       </c>
-      <c r="V2" s="35">
+      <c r="V2" s="37">
         <v>0.0756302521008403</v>
       </c>
-      <c r="W2" s="35">
+      <c r="W2" s="37">
         <v>0.156031837360951</v>
       </c>
-      <c r="X2" s="35">
+      <c r="X2" s="37">
         <v>0.156031837360951</v>
       </c>
-      <c r="Y2" s="35">
+      <c r="Y2" s="37">
         <v>0.156031837360951</v>
       </c>
-      <c r="Z2" s="35">
+      <c r="Z2" s="37">
         <v>0.156031837360951</v>
       </c>
-      <c r="AA2" s="35">
+      <c r="AA2" s="37">
         <v>0.156031837360951</v>
       </c>
-      <c r="AB2" s="35">
+      <c r="AB2" s="37">
         <v>0.156031837360951</v>
       </c>
-      <c r="AC2" s="35">
+      <c r="AC2" s="37">
         <v>0.0638089758342923</v>
       </c>
-      <c r="AD2" s="35">
+      <c r="AD2" s="37">
         <v>0.154434951354911</v>
       </c>
-      <c r="AE2" s="35">
+      <c r="AE2" s="37">
         <v>0.154434951354911</v>
       </c>
-      <c r="AF2" s="35">
+      <c r="AF2" s="37">
         <v>0.154434951354911</v>
       </c>
-      <c r="AG2" s="35">
+      <c r="AG2" s="37">
         <v>0.154434951354911</v>
       </c>
-      <c r="AH2" s="35">
+      <c r="AH2" s="37">
         <v>0.154434951354911</v>
       </c>
-      <c r="AI2" s="35">
+      <c r="AI2" s="37">
         <v>0.154434951354911</v>
       </c>
-      <c r="AJ2" s="35">
+      <c r="AJ2" s="37">
         <v>0.0733902918705351</v>
       </c>
-      <c r="AK2" s="35">
+      <c r="AK2" s="37">
         <v>0.151612903225806</v>
       </c>
-      <c r="AL2" s="35">
+      <c r="AL2" s="37">
         <v>0.151612903225806</v>
       </c>
-      <c r="AM2" s="35">
+      <c r="AM2" s="37">
         <v>0.151612903225806</v>
       </c>
-      <c r="AN2" s="35">
+      <c r="AN2" s="37">
         <v>0.151612903225806</v>
       </c>
-      <c r="AO2" s="35">
+      <c r="AO2" s="37">
         <v>0.151612903225806</v>
       </c>
-      <c r="AP2" s="35">
+      <c r="AP2" s="37">
         <v>0.151612903225806</v>
       </c>
-      <c r="AQ2" s="35">
+      <c r="AQ2" s="37">
+        <v>0.0903225806451613</v>
+      </c>
+      <c r="AR2" s="37">
         <v>0</v>
       </c>
-      <c r="AR2" s="35">
+      <c r="AS2" s="37">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:44">
+      <c r="AT2" s="37">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="37">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="37">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="37">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="37">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="37">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="37">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35">
+      <c r="B3" s="37">
         <f>SUM($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="37">
         <f>SUM($B2:C2)</f>
         <v>0.3087350715503</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="37">
         <f>SUM($B2:D2)</f>
         <v>0.463102607325449</v>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="37">
         <f>SUM($B2:E2)</f>
         <v>0.617470143100599</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="37">
         <f>SUM($B2:F2)</f>
         <v>0.771837678875749</v>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="37">
         <f>SUM($B2:G2)</f>
         <v>0.926205214650899</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="37">
         <f>SUM($B2:H2)</f>
         <v>1</v>
       </c>
-      <c r="I3" s="35">
+      <c r="I3" s="37">
         <f>SUM($B2:I2)</f>
         <v>1.15508044395829</v>
       </c>
-      <c r="J3" s="35">
+      <c r="J3" s="37">
         <f>SUM($B2:J2)</f>
         <v>1.31016088791658</v>
       </c>
-      <c r="K3" s="35">
+      <c r="K3" s="37">
         <f>SUM($B2:K2)</f>
         <v>1.46524133187487</v>
       </c>
-      <c r="L3" s="35">
+      <c r="L3" s="37">
         <f>SUM($B2:L2)</f>
         <v>1.62032177583316</v>
       </c>
-      <c r="M3" s="35">
+      <c r="M3" s="37">
         <f>SUM($B2:M2)</f>
         <v>1.77540221979145</v>
       </c>
-      <c r="N3" s="35">
+      <c r="N3" s="37">
         <f>SUM($B2:N2)</f>
         <v>1.93048266374974</v>
       </c>
-      <c r="O3" s="35">
+      <c r="O3" s="37">
         <f>SUM($B2:O2)</f>
         <v>2</v>
       </c>
-      <c r="P3" s="35">
+      <c r="P3" s="37">
         <f>SUM($B2:P2)</f>
         <v>2.15406162464986</v>
       </c>
-      <c r="Q3" s="35">
+      <c r="Q3" s="37">
         <f>SUM($B2:Q2)</f>
         <v>2.30812324929972</v>
       </c>
-      <c r="R3" s="35">
+      <c r="R3" s="37">
         <f>SUM($B2:R2)</f>
         <v>2.46218487394958</v>
       </c>
-      <c r="S3" s="35">
+      <c r="S3" s="37">
         <f>SUM($B2:S2)</f>
         <v>2.61624649859944</v>
       </c>
-      <c r="T3" s="35">
+      <c r="T3" s="37">
         <f>SUM($B2:T2)</f>
         <v>2.7703081232493</v>
       </c>
-      <c r="U3" s="35">
+      <c r="U3" s="37">
         <f>SUM($B2:U2)</f>
         <v>2.92436974789916</v>
       </c>
-      <c r="V3" s="35">
+      <c r="V3" s="37">
         <f>SUM($B2:V2)</f>
         <v>3</v>
       </c>
-      <c r="W3" s="35">
+      <c r="W3" s="37">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208285</v>
       </c>
-      <c r="X3" s="35">
+      <c r="X3" s="37">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208285</v>
       </c>
-      <c r="Y3" s="35">
+      <c r="Y3" s="37">
         <f>SUM($B2:Y2)</f>
         <v>3.46809551208285</v>
       </c>
-      <c r="Z3" s="35">
+      <c r="Z3" s="37">
         <f>SUM($B2:Z2)</f>
         <v>3.6241273494438</v>
       </c>
-      <c r="AA3" s="35">
+      <c r="AA3" s="37">
         <f>SUM($B2:AA2)</f>
         <v>3.78015918680476</v>
       </c>
-      <c r="AB3" s="35">
+      <c r="AB3" s="37">
         <f>SUM($B2:AB2)</f>
         <v>3.93619102416571</v>
       </c>
-      <c r="AC3" s="35">
+      <c r="AC3" s="37">
         <f>SUM($B2:AC2)</f>
         <v>4</v>
       </c>
-      <c r="AD3" s="35">
+      <c r="AD3" s="37">
         <f>SUM($B2:AD2)</f>
         <v>4.15443495135491</v>
       </c>
-      <c r="AE3" s="35">
+      <c r="AE3" s="37">
         <f>SUM($B2:AE2)</f>
         <v>4.30886990270982</v>
       </c>
-      <c r="AF3" s="35">
+      <c r="AF3" s="37">
         <f>SUM($B2:AF2)</f>
         <v>4.46330485406473</v>
       </c>
-      <c r="AG3" s="35">
+      <c r="AG3" s="37">
         <f>SUM($B2:AG2)</f>
         <v>4.61773980541964</v>
       </c>
-      <c r="AH3" s="35">
+      <c r="AH3" s="37">
         <f>SUM($B2:AH2)</f>
         <v>4.77217475677455</v>
       </c>
-      <c r="AI3" s="35">
+      <c r="AI3" s="37">
         <f>SUM($B2:AI2)</f>
         <v>4.92660970812946</v>
       </c>
-      <c r="AJ3" s="35">
+      <c r="AJ3" s="37">
         <f>SUM($B2:AJ2)</f>
         <v>5</v>
       </c>
-      <c r="AK3" s="35">
+      <c r="AK3" s="37">
         <f>SUM($B2:AK2)</f>
         <v>5.1516129032258</v>
       </c>
-      <c r="AL3" s="35">
+      <c r="AL3" s="37">
         <f>SUM($B2:AL2)</f>
         <v>5.30322580645161</v>
       </c>
-      <c r="AM3" s="35">
+      <c r="AM3" s="37">
         <f>SUM($B2:AM2)</f>
         <v>5.45483870967742</v>
       </c>
-      <c r="AN3" s="35">
+      <c r="AN3" s="37">
         <f>SUM($B2:AN2)</f>
         <v>5.60645161290322</v>
       </c>
-      <c r="AO3" s="35">
+      <c r="AO3" s="37">
         <f>SUM($B2:AO2)</f>
         <v>5.75806451612903</v>
       </c>
-      <c r="AP3" s="35">
+      <c r="AP3" s="37">
         <f>SUM($B2:AP2)</f>
         <v>5.90967741935483</v>
       </c>
-      <c r="AQ3" s="35">
+      <c r="AQ3" s="37">
         <f>SUM($B2:AQ2)</f>
-        <v>5.90967741935483</v>
-      </c>
-      <c r="AR3" s="35">
+        <v>6</v>
+      </c>
+      <c r="AR3" s="37">
         <f>SUM($B2:AR2)</f>
-        <v>5.90967741935483</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44">
+        <v>6</v>
+      </c>
+      <c r="AS3" s="37">
+        <f>SUM($B2:AS2)</f>
+        <v>6</v>
+      </c>
+      <c r="AT3" s="37">
+        <f>SUM($B2:AT2)</f>
+        <v>6</v>
+      </c>
+      <c r="AU3" s="37">
+        <f>SUM($B2:AU2)</f>
+        <v>6</v>
+      </c>
+      <c r="AV3" s="37">
+        <f>SUM($B2:AV2)</f>
+        <v>6</v>
+      </c>
+      <c r="AW3" s="37">
+        <f>SUM($B2:AW2)</f>
+        <v>6</v>
+      </c>
+      <c r="AX3" s="37">
+        <f>SUM($B2:AX2)</f>
+        <v>6</v>
+      </c>
+      <c r="AY3" s="37">
+        <f>SUM($B2:AY2)</f>
+        <v>6</v>
+      </c>
+      <c r="AZ3" s="37">
+        <f>SUM($B2:AZ2)</f>
+        <v>6</v>
+      </c>
+      <c r="BA3" s="37">
+        <f>SUM($B2:BA2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="37">
         <f>AVERAGE($B2:B2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="37">
         <f>AVERAGE($B2:C2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="37">
         <f>AVERAGE($B2:D2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="37">
         <f>AVERAGE($B2:E2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="37">
         <f>AVERAGE($B2:F2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="37">
         <f>AVERAGE($B2:G2)</f>
         <v>0.15436753577515</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="37">
         <f>AVERAGE($B2:H2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="37">
         <f>AVERAGE($B2:I2)</f>
         <v>0.144385055494786</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="37">
         <f>AVERAGE($B2:J2)</f>
         <v>0.145573431990731</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="37">
         <f>AVERAGE($B2:K2)</f>
         <v>0.146524133187487</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="37">
         <f>AVERAGE($B2:L2)</f>
         <v>0.147301979621197</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="37">
         <f>AVERAGE($B2:M2)</f>
         <v>0.147950184982621</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="37">
         <f>AVERAGE($B2:N2)</f>
         <v>0.148498666442288</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="37">
         <f>AVERAGE($B2:O2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="37">
         <f>AVERAGE($B2:P2)</f>
         <v>0.143604108309991</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="37">
         <f>AVERAGE($B2:Q2)</f>
         <v>0.144257703081233</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="37">
         <f>AVERAGE($B2:R2)</f>
         <v>0.144834404349975</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="37">
         <f>AVERAGE($B2:S2)</f>
         <v>0.145347027699969</v>
       </c>
-      <c r="T4" s="35">
+      <c r="T4" s="37">
         <f>AVERAGE($B2:T2)</f>
         <v>0.145805690697332</v>
       </c>
-      <c r="U4" s="35">
+      <c r="U4" s="37">
         <f>AVERAGE($B2:U2)</f>
         <v>0.146218487394958</v>
       </c>
-      <c r="V4" s="35">
+      <c r="V4" s="37">
         <f>AVERAGE($B2:V2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="W4" s="35">
+      <c r="W4" s="37">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="X4" s="35">
+      <c r="X4" s="37">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="Y4" s="35">
+      <c r="Y4" s="37">
         <f>AVERAGE($B2:Y2)</f>
         <v>0.144503979670119</v>
       </c>
-      <c r="Z4" s="35">
+      <c r="Z4" s="37">
         <f>AVERAGE($B2:Z2)</f>
         <v>0.144965093977752</v>
       </c>
-      <c r="AA4" s="35">
+      <c r="AA4" s="37">
         <f>AVERAGE($B2:AA2)</f>
         <v>0.145390737954029</v>
       </c>
-      <c r="AB4" s="35">
+      <c r="AB4" s="37">
         <f>AVERAGE($B2:AB2)</f>
         <v>0.145784852746878</v>
       </c>
-      <c r="AC4" s="35">
+      <c r="AC4" s="37">
         <f>AVERAGE($B2:AC2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="AD4" s="35">
+      <c r="AD4" s="37">
         <f>AVERAGE($B2:AD2)</f>
         <v>0.143256377632928</v>
       </c>
-      <c r="AE4" s="35">
+      <c r="AE4" s="37">
         <f>AVERAGE($B2:AE2)</f>
         <v>0.143628996756994</v>
       </c>
-      <c r="AF4" s="35">
+      <c r="AF4" s="37">
         <f>AVERAGE($B2:AF2)</f>
         <v>0.143977575937572</v>
       </c>
-      <c r="AG4" s="35">
+      <c r="AG4" s="37">
         <f>AVERAGE($B2:AG2)</f>
         <v>0.144304368919364</v>
       </c>
-      <c r="AH4" s="35">
+      <c r="AH4" s="37">
         <f>AVERAGE($B2:AH2)</f>
         <v>0.144611356265896</v>
       </c>
-      <c r="AI4" s="35">
+      <c r="AI4" s="37">
         <f>AVERAGE($B2:AI2)</f>
         <v>0.144900285533219</v>
       </c>
-      <c r="AJ4" s="35">
+      <c r="AJ4" s="37">
         <f>AVERAGE($B2:AJ2)</f>
         <v>0.142857142857143</v>
       </c>
-      <c r="AK4" s="35">
+      <c r="AK4" s="37">
         <f>AVERAGE($B2:AK2)</f>
         <v>0.143100358422939</v>
       </c>
-      <c r="AL4" s="35">
+      <c r="AL4" s="37">
         <f>AVERAGE($B2:AL2)</f>
         <v>0.143330427201395</v>
       </c>
-      <c r="AM4" s="35">
+      <c r="AM4" s="37">
         <f>AVERAGE($B2:AM2)</f>
         <v>0.143548387096774</v>
       </c>
-      <c r="AN4" s="35">
+      <c r="AN4" s="37">
         <f>AVERAGE($B2:AN2)</f>
         <v>0.143755169561621</v>
       </c>
-      <c r="AO4" s="35">
+      <c r="AO4" s="37">
         <f>AVERAGE($B2:AO2)</f>
         <v>0.143951612903226</v>
       </c>
-      <c r="AP4" s="35">
+      <c r="AP4" s="37">
         <f>AVERAGE($B2:AP2)</f>
         <v>0.144138473642801</v>
       </c>
-      <c r="AQ4" s="35">
+      <c r="AQ4" s="37">
         <f>AVERAGE($B2:AQ2)</f>
-        <v>0.140706605222734</v>
-      </c>
-      <c r="AR4" s="35">
+        <v>0.142857142857143</v>
+      </c>
+      <c r="AR4" s="37">
         <f>AVERAGE($B2:AR2)</f>
-        <v>0.137434358589647</v>
-      </c>
-    </row>
-    <row r="5" spans="1:44">
+        <v>0.13953488372093</v>
+      </c>
+      <c r="AS4" s="37">
+        <f>AVERAGE($B2:AS2)</f>
+        <v>0.136363636363636</v>
+      </c>
+      <c r="AT4" s="37">
+        <f>AVERAGE($B2:AT2)</f>
+        <v>0.133333333333333</v>
+      </c>
+      <c r="AU4" s="37">
+        <f>AVERAGE($B2:AU2)</f>
+        <v>0.130434782608696</v>
+      </c>
+      <c r="AV4" s="37">
+        <f>AVERAGE($B2:AV2)</f>
+        <v>0.127659574468085</v>
+      </c>
+      <c r="AW4" s="37">
+        <f>AVERAGE($B2:AW2)</f>
+        <v>0.125</v>
+      </c>
+      <c r="AX4" s="37">
+        <f>AVERAGE($B2:AX2)</f>
+        <v>0.122448979591837</v>
+      </c>
+      <c r="AY4" s="37">
+        <f>AVERAGE($B2:AY2)</f>
+        <v>0.12</v>
+      </c>
+      <c r="AZ4" s="37">
+        <f>AVERAGE($B2:AZ2)</f>
+        <v>0.117647058823529</v>
+      </c>
+      <c r="BA4" s="37">
+        <f>AVERAGE($B2:BA2)</f>
+        <v>0.115384615384615</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="37">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
-      <c r="C5" s="35">
-        <f t="shared" ref="C5:AR5" si="0">B5</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="D5" s="35">
+      <c r="C5" s="37">
+        <f t="shared" ref="C5:BA5" si="0">B5</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="D5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="I5" s="35">
+      <c r="I5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="J5" s="35">
+      <c r="J5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="L5" s="35">
+      <c r="L5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="M5" s="35">
+      <c r="M5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="N5" s="35">
+      <c r="N5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="O5" s="35">
+      <c r="O5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="P5" s="35">
+      <c r="P5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Q5" s="35">
+      <c r="Q5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="R5" s="35">
+      <c r="R5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="S5" s="35">
+      <c r="S5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="T5" s="35">
+      <c r="T5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="U5" s="35">
+      <c r="U5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="V5" s="35">
+      <c r="V5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="W5" s="35">
+      <c r="W5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="X5" s="35">
+      <c r="X5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Y5" s="35">
+      <c r="Y5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="Z5" s="35">
+      <c r="Z5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AA5" s="35">
+      <c r="AA5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AB5" s="35">
+      <c r="AB5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AC5" s="35">
+      <c r="AC5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AD5" s="35">
+      <c r="AD5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AE5" s="35">
+      <c r="AE5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AF5" s="35">
+      <c r="AF5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AG5" s="35">
+      <c r="AG5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AH5" s="35">
+      <c r="AH5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AI5" s="35">
+      <c r="AI5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AJ5" s="35">
+      <c r="AJ5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AK5" s="35">
+      <c r="AK5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AL5" s="35">
+      <c r="AL5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AM5" s="35">
+      <c r="AM5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AN5" s="35">
+      <c r="AN5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AO5" s="35">
+      <c r="AO5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AP5" s="35">
+      <c r="AP5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AQ5" s="35">
+      <c r="AQ5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-      <c r="AR5" s="35">
+      <c r="AR5" s="37">
         <f t="shared" si="0"/>
         <v>0.153846153846154</v>
       </c>
-    </row>
-    <row r="6" spans="1:44">
+      <c r="AS5" s="37">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AT5" s="37">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AU5" s="37">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AV5" s="37">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AW5" s="37">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AX5" s="37">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AY5" s="37">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AZ5" s="37">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="BA5" s="37">
+        <f t="shared" si="0"/>
+        <v>0.153846153846154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:53">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="35">
-        <f t="shared" ref="B6:AR6" si="1">B5-B2</f>
+      <c r="B6" s="37">
+        <f t="shared" ref="B6:BA6" si="1">B5-B2</f>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000521381928996006</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="37">
         <f t="shared" si="1"/>
         <v>0.080051368497053</v>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="37">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="J6" s="35">
+      <c r="J6" s="37">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="K6" s="35">
+      <c r="K6" s="37">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="L6" s="35">
+      <c r="L6" s="37">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="M6" s="35">
+      <c r="M6" s="37">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="N6" s="35">
+      <c r="N6" s="37">
         <f t="shared" si="1"/>
         <v>-0.00123429011213699</v>
       </c>
-      <c r="O6" s="35">
+      <c r="O6" s="37">
         <f t="shared" si="1"/>
         <v>0.0843288175958981</v>
       </c>
-      <c r="P6" s="35">
+      <c r="P6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="Q6" s="35">
+      <c r="Q6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="R6" s="35">
+      <c r="R6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="S6" s="35">
+      <c r="S6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="T6" s="35">
+      <c r="T6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="U6" s="35">
+      <c r="U6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000215470803706014</v>
       </c>
-      <c r="V6" s="35">
+      <c r="V6" s="37">
         <f t="shared" si="1"/>
         <v>0.0782159017453137</v>
       </c>
-      <c r="W6" s="35">
+      <c r="W6" s="37">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="X6" s="35">
+      <c r="X6" s="37">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="Y6" s="35">
+      <c r="Y6" s="37">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="Z6" s="35">
+      <c r="Z6" s="37">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="AA6" s="35">
+      <c r="AA6" s="37">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="AB6" s="35">
+      <c r="AB6" s="37">
         <f t="shared" si="1"/>
         <v>-0.002185683514797</v>
       </c>
-      <c r="AC6" s="35">
+      <c r="AC6" s="37">
         <f t="shared" si="1"/>
         <v>0.0900371780118617</v>
       </c>
-      <c r="AD6" s="35">
+      <c r="AD6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AE6" s="35">
+      <c r="AE6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AF6" s="35">
+      <c r="AF6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AG6" s="35">
+      <c r="AG6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AH6" s="35">
+      <c r="AH6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AI6" s="35">
+      <c r="AI6" s="37">
         <f t="shared" si="1"/>
         <v>-0.000588797508757011</v>
       </c>
-      <c r="AJ6" s="35">
+      <c r="AJ6" s="37">
         <f t="shared" si="1"/>
         <v>0.0804558619756189</v>
       </c>
-      <c r="AK6" s="35">
+      <c r="AK6" s="37">
         <f t="shared" si="1"/>
         <v>0.00223325062034799</v>
       </c>
-      <c r="AL6" s="35">
+      <c r="AL6" s="37">
         <f t="shared" si="1"/>
         <v>0.00223325062034799</v>
       </c>
-      <c r="AM6" s="35">
+      <c r="AM6" s="37">
         <f t="shared" si="1"/>
         <v>0.00223325062034799</v>
       </c>
-      <c r="AN6" s="35">
+      <c r="AN6" s="37">
         <f t="shared" si="1"/>
         <v>0.00223325062034799</v>
       </c>
-      <c r="AO6" s="35">
+      <c r="AO6" s="37">
         <f t="shared" si="1"/>
         <v>0.00223325062034799</v>
       </c>
-      <c r="AP6" s="35">
+      <c r="AP6" s="37">
         <f t="shared" si="1"/>
         <v>0.00223325062034754</v>
       </c>
-      <c r="AQ6" s="35">
+      <c r="AQ6" s="37">
         <f t="shared" si="1"/>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="AR6" s="35">
+        <v>0.0635235732009927</v>
+      </c>
+      <c r="AR6" s="37">
         <f t="shared" si="1"/>
         <v>0.153846153846154</v>
       </c>
+      <c r="AS6" s="37">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AT6" s="37">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AU6" s="37">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AV6" s="37">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AW6" s="37">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AX6" s="37">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AY6" s="37">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="AZ6" s="37">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="BA6" s="37">
+        <f t="shared" si="1"/>
+        <v>0.153846153846154</v>
+      </c>
     </row>
     <row r="7" hidden="1"/>
-    <row r="8" hidden="1" spans="1:44">
+    <row r="8" hidden="1" spans="1:53">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:44">
+    <row r="9" hidden="1" spans="1:53">
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
@@ -3051,25 +3249,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:44">
+    <row r="10" hidden="1" spans="1:53">
       <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="37">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D10" s="6">
         <v>50</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="37">
         <f>AVERAGE(F$10:F10)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="37">
         <f t="shared" ref="F10:F20" si="2">G10/B10</f>
         <v>0</v>
       </c>
@@ -3084,25 +3282,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:44">
+    <row r="11" hidden="1" spans="1:53">
       <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="6">
         <v>50</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="37">
         <f>C10</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D11" s="6">
         <v>25</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="37">
         <f>AVERAGE(F$10:F11)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3118,12 +3316,12 @@
       </c>
     </row>
     <row r="12" hidden="1"/>
-    <row r="13" hidden="1" spans="1:44">
+    <row r="13" hidden="1" spans="1:53">
       <c r="A13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:44">
+    <row r="14" hidden="1" spans="1:53">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
@@ -3155,14 +3353,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:44">
+    <row r="15" hidden="1" spans="1:53">
       <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="6">
         <v>257</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3170,11 +3368,11 @@
         <f t="shared" ref="D10:D20" si="4">ROUND(B15*C15,0)</f>
         <v>40</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="37">
         <f>AVERAGE(F$15:F15)</f>
         <v>0.066147859922179</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="37">
         <f t="shared" si="2"/>
         <v>0.066147859922179</v>
       </c>
@@ -3185,7 +3383,7 @@
       <c r="H15" s="6">
         <v>240</v>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="39">
         <f t="shared" ref="I15:I20" si="5">MIN($J$14*D15,J15)</f>
         <v>257</v>
       </c>
@@ -3193,14 +3391,14 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:44">
+    <row r="16" hidden="1" spans="1:53">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="6">
         <v>390</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="37">
         <f t="shared" ref="C16:C20" si="6">C15</f>
         <v>0.153846153846154</v>
       </c>
@@ -3208,11 +3406,11 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="37">
         <f>AVERAGE(F$15:F16)</f>
         <v>0.071535468422628</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="37">
         <f t="shared" si="2"/>
         <v>0.0769230769230769</v>
       </c>
@@ -3223,7 +3421,7 @@
       <c r="H16" s="6">
         <v>360</v>
       </c>
-      <c r="I16" s="37">
+      <c r="I16" s="39">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
@@ -3238,7 +3436,7 @@
       <c r="B17" s="6">
         <v>484</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="37">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -3246,11 +3444,11 @@
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="37">
         <f>AVERAGE(F$15:F17)</f>
         <v>0.0752385216481432</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="37">
         <f t="shared" si="2"/>
         <v>0.0826446280991736</v>
       </c>
@@ -3261,7 +3459,7 @@
       <c r="H17" s="6">
         <v>444</v>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="39">
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
@@ -3276,7 +3474,7 @@
       <c r="B18" s="6">
         <v>240</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="37">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -3284,11 +3482,11 @@
         <f t="shared" si="4"/>
         <v>37</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="37">
         <f>AVERAGE(F$15:F18)</f>
         <v>0.0751788912361074</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="37">
         <f t="shared" si="2"/>
         <v>0.075</v>
       </c>
@@ -3299,7 +3497,7 @@
       <c r="H18" s="6">
         <v>222</v>
       </c>
-      <c r="I18" s="37">
+      <c r="I18" s="39">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
@@ -3314,7 +3512,7 @@
       <c r="B19" s="6">
         <v>271</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="37">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -3322,11 +3520,11 @@
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="37">
         <f>AVERAGE(F$15:F19)</f>
         <v>0.0741652532102881</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="37">
         <f t="shared" si="2"/>
         <v>0.0701107011070111</v>
       </c>
@@ -3337,7 +3535,7 @@
       <c r="H19" s="6">
         <v>252</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="39">
         <f t="shared" si="5"/>
         <v>271</v>
       </c>
@@ -3352,7 +3550,7 @@
       <c r="B20" s="6">
         <v>278</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="37">
         <f t="shared" si="6"/>
         <v>0.153846153846154</v>
       </c>
@@ -3360,11 +3558,11 @@
         <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="37">
         <f>AVERAGE(F$15:F20)</f>
         <v>0.073794785349101</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="37">
         <f t="shared" si="2"/>
         <v>0.0719424460431655</v>
       </c>
@@ -3375,7 +3573,7 @@
       <c r="H20" s="6">
         <v>258</v>
       </c>
-      <c r="I20" s="37">
+      <c r="I20" s="39">
         <f t="shared" si="5"/>
         <v>278</v>
       </c>
@@ -3384,17 +3582,17 @@
       </c>
     </row>
     <row r="21" hidden="1" spans="1:10">
-      <c r="C21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
+      <c r="C21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
     </row>
     <row r="22" hidden="1" spans="1:10">
       <c r="A22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
+      <c r="C22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
     </row>
     <row r="23" hidden="1" spans="1:10">
       <c r="A23" s="6" t="s">
@@ -3435,7 +3633,7 @@
       <c r="B24" s="6">
         <v>440</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="37">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3443,11 +3641,11 @@
         <f t="shared" ref="D24:D28" si="7">ROUND(B24*C24,0)</f>
         <v>68</v>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="37">
         <f>AVERAGE(F$24:F24)</f>
         <v>0.0727272727272727</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="37">
         <f t="shared" ref="F24:F28" si="8">G24/B24</f>
         <v>0.0727272727272727</v>
       </c>
@@ -3458,7 +3656,7 @@
       <c r="H24" s="6">
         <v>408</v>
       </c>
-      <c r="I24" s="37">
+      <c r="I24" s="39">
         <f t="shared" ref="I24:I28" si="10">MIN($J$23*D24,J24)</f>
         <v>440</v>
       </c>
@@ -3473,7 +3671,7 @@
       <c r="B25" s="6">
         <v>378</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="37">
         <f t="shared" ref="C25:C28" si="11">C24</f>
         <v>0.153846153846154</v>
       </c>
@@ -3481,11 +3679,11 @@
         <f t="shared" si="7"/>
         <v>58</v>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="37">
         <f>AVERAGE(F$24:F25)</f>
         <v>0.076046176046176</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="37">
         <f t="shared" si="8"/>
         <v>0.0793650793650794</v>
       </c>
@@ -3496,7 +3694,7 @@
       <c r="H25" s="6">
         <v>348</v>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="39">
         <f t="shared" si="10"/>
         <v>378</v>
       </c>
@@ -3511,7 +3709,7 @@
       <c r="B26" s="6">
         <v>209</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="37">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -3519,11 +3717,11 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="E26" s="35">
+      <c r="E26" s="37">
         <f>AVERAGE(F$24:F26)</f>
         <v>0.0778106883370041</v>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="37">
         <f t="shared" si="8"/>
         <v>0.0813397129186603</v>
       </c>
@@ -3534,7 +3732,7 @@
       <c r="H26" s="6">
         <v>192</v>
       </c>
-      <c r="I26" s="37">
+      <c r="I26" s="39">
         <f t="shared" si="10"/>
         <v>209</v>
       </c>
@@ -3549,7 +3747,7 @@
       <c r="B27" s="6">
         <v>62</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="37">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -3557,11 +3755,11 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="37">
         <f>AVERAGE(F$24:F27)</f>
         <v>0.0664225323817854</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="37">
         <f t="shared" si="8"/>
         <v>0.032258064516129</v>
       </c>
@@ -3572,7 +3770,7 @@
       <c r="H27" s="6">
         <v>60</v>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="39">
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
@@ -3587,7 +3785,7 @@
       <c r="B28" s="6">
         <v>464</v>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="37">
         <f t="shared" si="11"/>
         <v>0.153846153846154</v>
       </c>
@@ -3595,11 +3793,11 @@
         <f t="shared" si="7"/>
         <v>71</v>
       </c>
-      <c r="E28" s="35">
+      <c r="E28" s="37">
         <f>AVERAGE(F$24:F28)</f>
         <v>0.0695173362502559</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="37">
         <f t="shared" si="8"/>
         <v>0.0818965517241379</v>
       </c>
@@ -3610,7 +3808,7 @@
       <c r="H28" s="6">
         <v>426</v>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="39">
         <f t="shared" si="10"/>
         <v>464</v>
       </c>
@@ -3619,9 +3817,9 @@
       </c>
     </row>
     <row r="29" hidden="1" spans="1:10">
-      <c r="C29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
+      <c r="C29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
     </row>
     <row r="30" hidden="1" spans="1:10">
       <c r="A30" s="6" t="s">
@@ -3667,7 +3865,7 @@
       <c r="B32" s="6">
         <v>132</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="37">
         <f t="shared" ref="C32:C35" si="12">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3675,11 +3873,11 @@
         <f t="shared" ref="D32:D35" si="13">ROUND(B32*C32,0)</f>
         <v>20</v>
       </c>
-      <c r="E32" s="35">
+      <c r="E32" s="37">
         <f>AVERAGE(F$32:F32)</f>
         <v>0.0909090909090909</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="37">
         <f t="shared" ref="F32:F35" si="14">G32/B32</f>
         <v>0.0909090909090909</v>
       </c>
@@ -3690,7 +3888,7 @@
       <c r="H32" s="6">
         <v>120</v>
       </c>
-      <c r="I32" s="37">
+      <c r="I32" s="39">
         <f t="shared" ref="I32:I35" si="16">MIN($J$31*D32,J32)</f>
         <v>132</v>
       </c>
@@ -3705,7 +3903,7 @@
       <c r="B33" s="6">
         <v>30</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="37">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -3713,11 +3911,11 @@
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="37">
         <f>AVERAGE(F$32:F33)</f>
         <v>0.0454545454545455</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -3728,7 +3926,7 @@
       <c r="H33" s="6">
         <v>30</v>
       </c>
-      <c r="I33" s="37">
+      <c r="I33" s="39">
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
@@ -3743,7 +3941,7 @@
       <c r="B34" s="6">
         <v>395</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="37">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -3751,11 +3949,11 @@
         <f t="shared" si="13"/>
         <v>61</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="37">
         <f>AVERAGE(F$32:F34)</f>
         <v>0.0547756041426928</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="37">
         <f t="shared" si="14"/>
         <v>0.0734177215189873</v>
       </c>
@@ -3766,7 +3964,7 @@
       <c r="H34" s="6">
         <v>366</v>
       </c>
-      <c r="I34" s="37">
+      <c r="I34" s="39">
         <f t="shared" si="16"/>
         <v>395</v>
       </c>
@@ -3781,7 +3979,7 @@
       <c r="B35" s="6">
         <v>66</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="37">
         <f t="shared" si="12"/>
         <v>0.153846153846154</v>
       </c>
@@ -3789,11 +3987,11 @@
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="37">
         <f>AVERAGE(F$32:F35)</f>
         <v>0.0638089758342923</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="37">
         <f t="shared" si="14"/>
         <v>0.0909090909090909</v>
       </c>
@@ -3804,7 +4002,7 @@
       <c r="H35" s="6">
         <v>60</v>
       </c>
-      <c r="I35" s="37">
+      <c r="I35" s="39">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
@@ -3812,15 +4010,16 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="36" hidden="1"/>
+    <row r="37" hidden="1" spans="1:10">
       <c r="A37" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="C37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+    </row>
+    <row r="38" hidden="1" spans="1:10">
       <c r="A38" s="33" t="s">
         <v>7</v>
       </c>
@@ -3852,7 +4051,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" hidden="1" spans="1:10">
       <c r="A39" s="33" t="s">
         <v>37</v>
       </c>
@@ -3860,7 +4059,7 @@
         <f>100+148</f>
         <v>248</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="37">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3868,37 +4067,37 @@
         <f>ROUND(B39*C39,0)</f>
         <v>38</v>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="37">
         <f>AVERAGE(F$39:F39)</f>
-        <v>0.0120967741935484</v>
-      </c>
-      <c r="F39" s="35">
+        <v>0.0806451612903226</v>
+      </c>
+      <c r="F39" s="37">
         <f>G39/B39</f>
-        <v>0.0120967741935484</v>
+        <v>0.0806451612903226</v>
       </c>
       <c r="G39" s="6">
         <f>I39-H39</f>
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H39" s="6">
         <v>228</v>
       </c>
-      <c r="I39" s="38">
+      <c r="I39" s="39">
         <f>MIN($J$38*D39,J39)</f>
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="J39" s="6">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="40" hidden="1" spans="1:10">
       <c r="A40" s="33" t="s">
         <v>38</v>
       </c>
       <c r="B40" s="6">
         <v>40</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C40" s="37">
         <f>4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3906,11 +4105,11 @@
         <f>ROUND(B40*C40,0)</f>
         <v>6</v>
       </c>
-      <c r="E40" s="35">
+      <c r="E40" s="37">
         <f>AVERAGE(F$39:F40)</f>
-        <v>0.0560483870967742</v>
-      </c>
-      <c r="F40" s="35">
+        <v>0.0903225806451613</v>
+      </c>
+      <c r="F40" s="37">
         <f>G40/B40</f>
         <v>0.1</v>
       </c>
@@ -3921,7 +4120,7 @@
       <c r="H40" s="6">
         <v>36</v>
       </c>
-      <c r="I40" s="37">
+      <c r="I40" s="39">
         <f>MIN($J$38*D40,J40)</f>
         <v>40</v>
       </c>
@@ -3934,9 +4133,9 @@
       <c r="A42" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
+      <c r="C42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
     </row>
     <row r="43" hidden="1" spans="1:10">
       <c r="A43" s="6" t="s">
@@ -3978,7 +4177,7 @@
         <f>212+52+63+30</f>
         <v>357</v>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="37">
         <f t="shared" ref="C44:C49" si="17">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -3986,11 +4185,11 @@
         <f>ROUND(B44*C44,0)</f>
         <v>55</v>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="37">
         <f>AVERAGE(F$44:F44)</f>
         <v>0.0756302521008403</v>
       </c>
-      <c r="F44" s="35">
+      <c r="F44" s="37">
         <f>G44/B44</f>
         <v>0.0756302521008403</v>
       </c>
@@ -4001,7 +4200,7 @@
       <c r="H44" s="6">
         <v>330</v>
       </c>
-      <c r="I44" s="37">
+      <c r="I44" s="39">
         <f>MIN($J$43*D44,J44)</f>
         <v>357</v>
       </c>
@@ -4015,9 +4214,9 @@
       <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
+      <c r="C46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
     </row>
     <row r="47" hidden="1" spans="1:10">
       <c r="A47" s="6" t="s">
@@ -4058,7 +4257,7 @@
       <c r="B48" s="6">
         <v>523</v>
       </c>
-      <c r="C48" s="35">
+      <c r="C48" s="37">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
@@ -4066,11 +4265,11 @@
         <f t="shared" ref="D48:D54" si="18">ROUND(B48*C48,0)</f>
         <v>80</v>
       </c>
-      <c r="E48" s="35">
+      <c r="E48" s="37">
         <f>AVERAGE(F$48:F48)</f>
         <v>0.0822179732313576</v>
       </c>
-      <c r="F48" s="35">
+      <c r="F48" s="37">
         <f t="shared" ref="F48:F54" si="19">G48/B48</f>
         <v>0.0822179732313576</v>
       </c>
@@ -4081,7 +4280,7 @@
       <c r="H48" s="6">
         <v>480</v>
       </c>
-      <c r="I48" s="37">
+      <c r="I48" s="39">
         <f t="shared" ref="I48:I54" si="21">MIN($J$47*D48,J48)</f>
         <v>523</v>
       </c>
@@ -4096,7 +4295,7 @@
       <c r="B49" s="6">
         <v>434</v>
       </c>
-      <c r="C49" s="35">
+      <c r="C49" s="37">
         <f t="shared" si="17"/>
         <v>0.153846153846154</v>
       </c>
@@ -4104,11 +4303,11 @@
         <f t="shared" si="18"/>
         <v>67</v>
       </c>
-      <c r="E49" s="35">
+      <c r="E49" s="37">
         <f>AVERAGE(F$48:F49)</f>
         <v>0.0779753460626834</v>
       </c>
-      <c r="F49" s="35">
+      <c r="F49" s="37">
         <f t="shared" si="19"/>
         <v>0.0737327188940092</v>
       </c>
@@ -4119,7 +4318,7 @@
       <c r="H49" s="6">
         <v>402</v>
       </c>
-      <c r="I49" s="37">
+      <c r="I49" s="39">
         <f t="shared" si="21"/>
         <v>434</v>
       </c>
@@ -4135,7 +4334,7 @@
         <f>26+83</f>
         <v>109</v>
       </c>
-      <c r="C50" s="35">
+      <c r="C50" s="37">
         <f t="shared" ref="C50:C60" si="22">4/26</f>
         <v>0.153846153846154</v>
       </c>
@@ -4143,11 +4342,11 @@
         <f t="shared" si="18"/>
         <v>17</v>
       </c>
-      <c r="E50" s="35">
+      <c r="E50" s="37">
         <f>AVERAGE(F$48:F50)</f>
         <v>0.0733902918705351</v>
       </c>
-      <c r="F50" s="35">
+      <c r="F50" s="37">
         <f t="shared" si="19"/>
         <v>0.0642201834862385</v>
       </c>
@@ -4158,7 +4357,7 @@
       <c r="H50" s="6">
         <v>102</v>
       </c>
-      <c r="I50" s="37">
+      <c r="I50" s="39">
         <f t="shared" si="21"/>
         <v>109</v>
       </c>
@@ -4167,18 +4366,18 @@
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="C51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-      <c r="I51" s="38"/>
+      <c r="C51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="I51" s="40"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
+      <c r="C52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="6" t="s">
@@ -4213,13 +4412,13 @@
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="39" t="s">
+      <c r="A54" s="34" t="s">
         <v>45</v>
       </c>
       <c r="B54" s="6">
         <v>999</v>
       </c>
-      <c r="C54" s="35">
+      <c r="C54" s="37">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
@@ -4227,11 +4426,11 @@
         <f t="shared" ref="D54:D60" si="23">ROUND(B54*C54,0)</f>
         <v>154</v>
       </c>
-      <c r="E54" s="35">
+      <c r="E54" s="37">
         <f>AVERAGE(F$54:F54)</f>
         <v>0</v>
       </c>
-      <c r="F54" s="35">
+      <c r="F54" s="37">
         <f t="shared" ref="F54:F60" si="24">G54/B54</f>
         <v>0</v>
       </c>
@@ -4239,7 +4438,7 @@
         <f t="shared" ref="G54:G60" si="25">I54-H54</f>
         <v>0</v>
       </c>
-      <c r="I54" s="38">
+      <c r="I54" s="40">
         <f t="shared" ref="I54:I60" si="26">MIN($J$53*D54,J54)</f>
         <v>0</v>
       </c>
@@ -4248,188 +4447,188 @@
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="39" t="s">
+      <c r="A55" s="34" t="s">
         <v>46</v>
       </c>
       <c r="B55" s="6">
-        <v>999</v>
-      </c>
-      <c r="C55" s="35">
+        <v>937</v>
+      </c>
+      <c r="C55" s="37">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="23"/>
-        <v>154</v>
-      </c>
-      <c r="E55" s="35">
+        <v>144</v>
+      </c>
+      <c r="E55" s="37">
         <f>AVERAGE(F$54:F55)</f>
-        <v>0</v>
-      </c>
-      <c r="F55" s="35">
+        <v>0.0768409818569904</v>
+      </c>
+      <c r="F55" s="37">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>0.153681963713981</v>
       </c>
       <c r="G55" s="6">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="38">
+        <v>144</v>
+      </c>
+      <c r="I55" s="39">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J55" s="6">
-        <v>0</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="39" t="s">
+      <c r="A56" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B56" s="6">
-        <v>999</v>
-      </c>
-      <c r="C56" s="35">
+        <v>360</v>
+      </c>
+      <c r="C56" s="37">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D56" s="6">
         <f t="shared" si="23"/>
-        <v>154</v>
-      </c>
-      <c r="E56" s="35">
+        <v>55</v>
+      </c>
+      <c r="E56" s="37">
         <f>AVERAGE(F$54:F56)</f>
-        <v>0</v>
-      </c>
-      <c r="F56" s="35">
+        <v>0.10215324716392</v>
+      </c>
+      <c r="F56" s="37">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>0.152777777777778</v>
       </c>
       <c r="G56" s="6">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="38">
+        <v>55</v>
+      </c>
+      <c r="I56" s="39">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J56" s="6">
-        <v>0</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="39" t="s">
+      <c r="A57" s="34" t="s">
         <v>48</v>
       </c>
       <c r="B57" s="6">
-        <v>999</v>
-      </c>
-      <c r="C57" s="35">
+        <v>345</v>
+      </c>
+      <c r="C57" s="37">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" si="23"/>
-        <v>154</v>
-      </c>
-      <c r="E57" s="35">
+        <v>53</v>
+      </c>
+      <c r="E57" s="37">
         <f>AVERAGE(F$54:F57)</f>
-        <v>0</v>
-      </c>
-      <c r="F57" s="35">
+        <v>0.115020732474389</v>
+      </c>
+      <c r="F57" s="37">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>0.153623188405797</v>
       </c>
       <c r="G57" s="6">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="38">
+        <v>53</v>
+      </c>
+      <c r="I57" s="39">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J57" s="6">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="40" t="s">
+      <c r="A58" s="35" t="s">
         <v>49</v>
       </c>
       <c r="B58" s="6">
-        <v>999</v>
-      </c>
-      <c r="C58" s="35">
+        <v>738</v>
+      </c>
+      <c r="C58" s="37">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="23"/>
-        <v>154</v>
-      </c>
-      <c r="E58" s="35">
+        <v>114</v>
+      </c>
+      <c r="E58" s="37">
         <f>AVERAGE(F$54:F58)</f>
-        <v>0</v>
-      </c>
-      <c r="F58" s="35">
+        <v>0.122910894922601</v>
+      </c>
+      <c r="F58" s="37">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>0.154471544715447</v>
       </c>
       <c r="G58" s="6">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="38">
+        <v>114</v>
+      </c>
+      <c r="I58" s="39">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="J58" s="6">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="40" t="s">
+      <c r="A59" s="35" t="s">
         <v>50</v>
       </c>
       <c r="B59" s="6">
-        <v>999</v>
-      </c>
-      <c r="C59" s="35">
+        <v>441</v>
+      </c>
+      <c r="C59" s="37">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" si="23"/>
-        <v>154</v>
-      </c>
-      <c r="E59" s="35">
+        <v>68</v>
+      </c>
+      <c r="E59" s="37">
         <f>AVERAGE(F$54:F59)</f>
-        <v>0</v>
-      </c>
-      <c r="F59" s="35">
+        <v>0.128124914325145</v>
+      </c>
+      <c r="F59" s="37">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>0.154195011337868</v>
       </c>
       <c r="G59" s="6">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="38">
+        <v>68</v>
+      </c>
+      <c r="I59" s="39">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J59" s="6">
-        <v>0</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="40" t="s">
+      <c r="A60" s="35" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="6">
         <v>999</v>
       </c>
-      <c r="C60" s="35">
+      <c r="C60" s="37">
         <f t="shared" si="22"/>
         <v>0.153846153846154</v>
       </c>
@@ -4437,11 +4636,11 @@
         <f t="shared" si="23"/>
         <v>154</v>
       </c>
-      <c r="E60" s="35">
+      <c r="E60" s="37">
         <f>AVERAGE(F$54:F60)</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="35">
+        <v>0.109821355135839</v>
+      </c>
+      <c r="F60" s="37">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -4449,7 +4648,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I60" s="38">
+      <c r="I60" s="40">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
@@ -4462,7 +4661,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A41:AR46 I39:I40 C39:G40 K38:AR40 A38:I38 A3:AR37 AQ2:AR2 A2:AH2 A1:AR1 A47:I47 K48:AH48 A48:G50 I48:I50 B58:AR60 A57:AR57 K54:AR56 A55:I56 B54:I54 A51:AR53" formulaRange="1"/>
+    <ignoredError sqref="A60:I60 K57:BA60 C57:I59 K55:AR56 C55:I55 C56:H56 A55:A59 A1:BA53 A54:I54 K54:BA54" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4470,7 +4669,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="10.7777777777778" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="10.7777777777778" style="6" customWidth="1"/>
@@ -4752,7 +4951,7 @@
       </c>
     </row>
     <row r="21" hidden="1"/>
-    <row r="22" spans="1:14">
+    <row r="22" hidden="1" spans="1:14">
       <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
@@ -4784,7 +4983,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" hidden="1" spans="1:14">
       <c r="A23" s="6" t="s">
         <v>42</v>
       </c>
@@ -4825,7 +5024,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" hidden="1" spans="1:14">
       <c r="A24" s="6" t="s">
         <v>43</v>
       </c>
@@ -4867,7 +5066,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" hidden="1" spans="1:14">
       <c r="C25" s="6" t="s">
         <v>119</v>
       </c>
@@ -4902,19 +5101,19 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" hidden="1" spans="1:14">
       <c r="A26" s="33" t="s">
         <v>37</v>
       </c>
       <c r="B26" s="6">
         <f>SUM(C26:D26)</f>
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="C26" s="6">
         <v>100</v>
       </c>
       <c r="D26" s="6">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>130</v>
@@ -4944,7 +5143,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" hidden="1" spans="1:14">
       <c r="A27" s="33" t="s">
         <v>38</v>
       </c>
@@ -4977,6 +5176,73 @@
       </c>
       <c r="N27" s="32" t="s">
         <v>146</v>
+      </c>
+    </row>
+    <row r="28" hidden="1"/>
+    <row r="29" spans="1:14">
+      <c r="A29" s="34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6">
+        <v>203</v>
+      </c>
+      <c r="C30" s="6">
+        <f>B30-(51-39)</f>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="6">
+        <v>177</v>
+      </c>
+      <c r="C31" s="6">
+        <f>B31-(33-24)</f>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="6">
+        <v>61</v>
+      </c>
+      <c r="C32" s="6">
+        <f>B32-(26-10)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="6">
+        <v>144</v>
+      </c>
+      <c r="C33" s="6">
+        <f>B33-(32-4)</f>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="6">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="35" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -4618,7 +4618,7 @@
         <v>68</v>
       </c>
       <c r="J59" s="6">
-        <v>137</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -4661,7 +4661,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A60:I60 K57:BA60 C57:I59 K55:AR56 C55:I55 C56:H56 A55:A59 A1:BA53 A54:I54 K54:BA54" formulaRange="1"/>
+    <ignoredError sqref="K54:BA54 A54:I54 A1:BA53 A55:A59 C56:H56 C55:I55 K55:AR56 C57:I59 K57:BA60 A60:I60" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5237,7 +5237,7 @@
         <v>50</v>
       </c>
       <c r="B34" s="6">
-        <v>137</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:3">
